--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127153536</v>
+        <v>127164710</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>80114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,47 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539859</v>
+        <v>540011</v>
       </c>
       <c r="R2" t="n">
-        <v>7001178</v>
+        <v>7001079</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +770,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127160294</v>
+        <v>127162096</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,7 +838,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540092</v>
+        <v>540104</v>
       </c>
       <c r="R3" t="n">
-        <v>7001341</v>
+        <v>7001431</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,6 +885,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på två sälgar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,12 +916,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127158784</v>
+        <v>127160294</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>80114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,32 +950,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540039</v>
+        <v>540092</v>
       </c>
       <c r="R4" t="n">
         <v>7001341</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,26 +1012,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1033,22 +1033,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,47 +1066,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127161646</v>
+        <v>127162017</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1115,13 +1106,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540139</v>
+        <v>540111</v>
       </c>
       <c r="R5" t="n">
-        <v>7001452</v>
+        <v>7001420</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,11 +1144,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1170,6 +1156,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,38 +1193,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127162418</v>
+        <v>127161646</v>
       </c>
       <c r="B6" t="n">
-        <v>98694</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1227,13 +1242,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540127</v>
+        <v>540139</v>
       </c>
       <c r="R6" t="n">
-        <v>7001264</v>
+        <v>7001452</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,6 +1278,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,38 +1314,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127162096</v>
+        <v>127162604</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>98353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1334,13 +1354,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540104</v>
+        <v>540240</v>
       </c>
       <c r="R7" t="n">
-        <v>7001431</v>
+        <v>7001210</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,11 +1392,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på två sälgar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1385,31 +1400,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1426,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127162017</v>
+        <v>127163443</v>
       </c>
       <c r="B8" t="n">
-        <v>80118</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,42 +1427,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540111</v>
+        <v>540255</v>
       </c>
       <c r="R8" t="n">
-        <v>7001420</v>
+        <v>7001070</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,31 +1502,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1553,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127162604</v>
+        <v>127162418</v>
       </c>
       <c r="B9" t="n">
-        <v>98278</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,27 +1529,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1593,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540240</v>
+        <v>540127</v>
       </c>
       <c r="R9" t="n">
-        <v>7001210</v>
+        <v>7001264</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1639,6 +1604,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1655,10 +1625,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127164710</v>
+        <v>127153536</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,42 +1636,47 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540011</v>
+        <v>539859</v>
       </c>
       <c r="R10" t="n">
-        <v>7001079</v>
+        <v>7001178</v>
       </c>
       <c r="S10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1735,7 +1710,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,26 +1725,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1787,50 +1742,55 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127163443</v>
+        <v>127158784</v>
       </c>
       <c r="B11" t="n">
-        <v>98384</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540255</v>
+        <v>540039</v>
       </c>
       <c r="R11" t="n">
-        <v>7001070</v>
+        <v>7001341</v>
       </c>
       <c r="S11" t="n">
         <v>11</v>
@@ -1860,11 +1820,26 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1873,6 +1848,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1889,47 +1889,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127160359</v>
+        <v>127162375</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540139</v>
+        <v>540115</v>
       </c>
       <c r="R12" t="n">
-        <v>7001298</v>
+        <v>7001309</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1971,24 +1971,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,62 +2010,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127162375</v>
+        <v>127154593</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>80114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540115</v>
+        <v>539874</v>
       </c>
       <c r="R13" t="n">
-        <v>7001309</v>
+        <v>7001234</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2109,7 +2090,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,6 +2105,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2141,10 +2142,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127154593</v>
+        <v>127160359</v>
       </c>
       <c r="B14" t="n">
-        <v>80083</v>
+        <v>57817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,42 +2153,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539874</v>
+        <v>540139</v>
       </c>
       <c r="R14" t="n">
-        <v>7001234</v>
+        <v>7001298</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2214,14 +2224,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
+          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2236,26 +2256,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2276,7 +2276,7 @@
         <v>127155767</v>
       </c>
       <c r="B15" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2546,10 +2546,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127160480</v>
+        <v>127161347</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2575,19 +2575,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540188</v>
+        <v>540157</v>
       </c>
       <c r="R17" t="n">
-        <v>7001269</v>
+        <v>7001411</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2617,6 +2622,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2668,10 +2678,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127161347</v>
+        <v>127160480</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,24 +2707,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540157</v>
+        <v>540188</v>
       </c>
       <c r="R18" t="n">
-        <v>7001411</v>
+        <v>7001269</v>
       </c>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2744,11 +2749,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127152848</v>
+        <v>127160270</v>
       </c>
       <c r="B19" t="n">
-        <v>98278</v>
+        <v>98457</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2811,48 +2811,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539832</v>
+        <v>540095</v>
       </c>
       <c r="R19" t="n">
-        <v>7001265</v>
+        <v>7001315</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2916,48 +2907,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127153666</v>
+        <v>127163626</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539888</v>
+        <v>540307</v>
       </c>
       <c r="R20" t="n">
-        <v>7001166</v>
+        <v>7001050</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2989,6 +2994,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3001,26 +3011,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3038,48 +3028,62 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127163769</v>
+        <v>127152848</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540285</v>
+        <v>539832</v>
       </c>
       <c r="R21" t="n">
-        <v>7001071</v>
+        <v>7001265</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3123,26 +3127,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3160,50 +3144,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127160270</v>
+        <v>127164774</v>
       </c>
       <c r="B22" t="n">
-        <v>98382</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540095</v>
+        <v>540022</v>
       </c>
       <c r="R22" t="n">
-        <v>7001315</v>
+        <v>7001093</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3250,6 +3229,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3267,62 +3266,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127163626</v>
+        <v>127153666</v>
       </c>
       <c r="B23" t="n">
-        <v>98384</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540307</v>
+        <v>539888</v>
       </c>
       <c r="R23" t="n">
-        <v>7001050</v>
+        <v>7001166</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3354,11 +3339,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3371,6 +3351,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127164774</v>
+        <v>127163769</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3423,13 +3423,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540022</v>
+        <v>540285</v>
       </c>
       <c r="R24" t="n">
-        <v>7001093</v>
+        <v>7001071</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3510,67 +3510,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127155997</v>
+        <v>127163495</v>
       </c>
       <c r="B25" t="n">
-        <v>98278</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>539924</v>
+        <v>540258</v>
       </c>
       <c r="R25" t="n">
-        <v>7001238</v>
+        <v>7001065</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3613,7 +3594,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3634,7 +3635,7 @@
         <v>127158356</v>
       </c>
       <c r="B26" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3758,48 +3759,67 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127163495</v>
+        <v>127155997</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540258</v>
+        <v>539924</v>
       </c>
       <c r="R27" t="n">
-        <v>7001065</v>
+        <v>7001238</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3842,27 +3862,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3883,7 +3883,7 @@
         <v>127153641</v>
       </c>
       <c r="B28" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>127153581</v>
       </c>
       <c r="B29" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127153018</v>
+        <v>127160821</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>80114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4145,37 +4145,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539829</v>
+        <v>540188</v>
       </c>
       <c r="R30" t="n">
-        <v>7001270</v>
+        <v>7001373</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4207,6 +4212,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en upplyft liggande levande sälg.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4223,22 +4233,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4256,67 +4266,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127153897</v>
+        <v>127153018</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539873</v>
+        <v>539829</v>
       </c>
       <c r="R31" t="n">
-        <v>7001197</v>
+        <v>7001270</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4348,11 +4339,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4365,6 +4351,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4382,50 +4388,64 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127160821</v>
+        <v>127153897</v>
       </c>
       <c r="B32" t="n">
-        <v>80083</v>
+        <v>98436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540188</v>
+        <v>539873</v>
       </c>
       <c r="R32" t="n">
-        <v>7001373</v>
+        <v>7001197</v>
       </c>
       <c r="S32" t="n">
         <v>12</v>
@@ -4462,7 +4482,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en upplyft liggande levande sälg.</t>
+          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4477,26 +4497,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127158834</v>
+        <v>127161738</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>80114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4525,37 +4525,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540033</v>
+        <v>540129</v>
       </c>
       <c r="R33" t="n">
-        <v>7001311</v>
+        <v>7001452</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4587,6 +4592,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4603,22 +4613,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4639,7 +4649,7 @@
         <v>127161580</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4768,10 +4778,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127161738</v>
+        <v>127164937</v>
       </c>
       <c r="B35" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4804,17 +4814,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540129</v>
+        <v>539990</v>
       </c>
       <c r="R35" t="n">
-        <v>7001452</v>
+        <v>7001113</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4848,7 +4858,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4900,10 +4910,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127164937</v>
+        <v>127158834</v>
       </c>
       <c r="B36" t="n">
-        <v>80083</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4911,39 +4921,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539990</v>
+        <v>540033</v>
       </c>
       <c r="R36" t="n">
-        <v>7001113</v>
+        <v>7001311</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4978,11 +4983,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4999,22 +4999,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5035,7 +5035,7 @@
         <v>127163212</v>
       </c>
       <c r="B37" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127153765</v>
+        <v>127164541</v>
       </c>
       <c r="B38" t="n">
-        <v>80083</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5150,42 +5150,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539879</v>
+        <v>540113</v>
       </c>
       <c r="R38" t="n">
-        <v>7001196</v>
+        <v>7001087</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5217,11 +5212,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5238,22 +5228,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5274,7 +5264,7 @@
         <v>127154714</v>
       </c>
       <c r="B39" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5403,10 +5393,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127164541</v>
+        <v>127164835</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>80114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5414,34 +5404,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540113</v>
+        <v>539992</v>
       </c>
       <c r="R40" t="n">
-        <v>7001087</v>
+        <v>7001093</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5476,6 +5471,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5492,22 +5492,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127164835</v>
+        <v>127153765</v>
       </c>
       <c r="B41" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5556,22 +5556,22 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539992</v>
+        <v>539879</v>
       </c>
       <c r="R41" t="n">
-        <v>7001093</v>
+        <v>7001196</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+          <t>Fertil lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5657,62 +5657,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127158031</v>
+        <v>127163137</v>
       </c>
       <c r="B42" t="n">
-        <v>98278</v>
+        <v>98436</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540047</v>
+        <v>540285</v>
       </c>
       <c r="R42" t="n">
-        <v>7001245</v>
+        <v>7001126</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5744,11 +5735,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Vid en bäck på en gammal väg.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5757,11 +5743,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5781,7 +5762,7 @@
         <v>127162701</v>
       </c>
       <c r="B43" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5888,7 +5869,7 @@
         <v>127162532</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6007,38 +5988,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127163137</v>
+        <v>127164613</v>
       </c>
       <c r="B45" t="n">
-        <v>98361</v>
+        <v>80114</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6047,13 +6028,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540285</v>
+        <v>540079</v>
       </c>
       <c r="R45" t="n">
-        <v>7001126</v>
+        <v>7001087</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6093,6 +6074,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6109,10 +6115,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127163976</v>
+        <v>127158031</v>
       </c>
       <c r="B46" t="n">
-        <v>98384</v>
+        <v>98353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6120,24 +6126,33 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -6145,17 +6160,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540285</v>
+        <v>540047</v>
       </c>
       <c r="R46" t="n">
-        <v>7001072</v>
+        <v>7001245</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6187,6 +6202,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Vid en bäck på en gammal väg.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6195,6 +6215,11 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6211,38 +6236,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127164613</v>
+        <v>127163976</v>
       </c>
       <c r="B47" t="n">
-        <v>80083</v>
+        <v>98459</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6251,13 +6276,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540079</v>
+        <v>540285</v>
       </c>
       <c r="R47" t="n">
-        <v>7001087</v>
+        <v>7001072</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6297,31 +6322,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6338,38 +6338,52 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127152890</v>
+        <v>127153495</v>
       </c>
       <c r="B48" t="n">
-        <v>98382</v>
+        <v>98436</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6378,10 +6392,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539829</v>
+        <v>539858</v>
       </c>
       <c r="R48" t="n">
-        <v>7001270</v>
+        <v>7001193</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6414,6 +6428,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6445,52 +6464,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127153495</v>
+        <v>127152890</v>
       </c>
       <c r="B49" t="n">
-        <v>98361</v>
+        <v>98457</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6499,10 +6504,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539858</v>
+        <v>539829</v>
       </c>
       <c r="R49" t="n">
-        <v>7001193</v>
+        <v>7001270</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6535,11 +6540,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6574,7 +6574,7 @@
         <v>127153809</v>
       </c>
       <c r="B50" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>127160120</v>
       </c>
       <c r="B51" t="n">
-        <v>98694</v>
+        <v>98769</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>127164902</v>
       </c>
       <c r="B52" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6907,10 +6907,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127161775</v>
+        <v>127162675</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6942,13 +6942,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540092</v>
+        <v>540237</v>
       </c>
       <c r="R53" t="n">
-        <v>7001443</v>
+        <v>7001188</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7029,62 +7029,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127163731</v>
+        <v>127161775</v>
       </c>
       <c r="B54" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540303</v>
+        <v>540092</v>
       </c>
       <c r="R54" t="n">
-        <v>7001059</v>
+        <v>7001443</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7128,6 +7114,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7145,10 +7151,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127164425</v>
+        <v>127159734</v>
       </c>
       <c r="B55" t="n">
-        <v>98382</v>
+        <v>98353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7156,39 +7162,44 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540128</v>
+        <v>540115</v>
       </c>
       <c r="R55" t="n">
-        <v>7001058</v>
+        <v>7001344</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -7234,7 +7245,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7252,10 +7263,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127160489</v>
+        <v>127156042</v>
       </c>
       <c r="B56" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7280,25 +7291,39 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540171</v>
+        <v>539924</v>
       </c>
       <c r="R56" t="n">
-        <v>7001276</v>
+        <v>7001238</v>
       </c>
       <c r="S56" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7341,7 +7366,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7359,10 +7384,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127156042</v>
+        <v>127162577</v>
       </c>
       <c r="B57" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7387,39 +7412,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539924</v>
+        <v>540238</v>
       </c>
       <c r="R57" t="n">
-        <v>7001238</v>
+        <v>7001222</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7459,11 +7470,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7480,10 +7486,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127159734</v>
+        <v>127160489</v>
       </c>
       <c r="B58" t="n">
-        <v>98278</v>
+        <v>98459</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7491,21 +7497,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7514,24 +7520,19 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540115</v>
+        <v>540171</v>
       </c>
       <c r="R58" t="n">
-        <v>7001344</v>
+        <v>7001276</v>
       </c>
       <c r="S58" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7574,7 +7575,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7592,48 +7593,62 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127162675</v>
+        <v>127163731</v>
       </c>
       <c r="B59" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540237</v>
+        <v>540303</v>
       </c>
       <c r="R59" t="n">
-        <v>7001188</v>
+        <v>7001059</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7677,26 +7692,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7714,10 +7709,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127162577</v>
+        <v>127164425</v>
       </c>
       <c r="B60" t="n">
-        <v>98384</v>
+        <v>98457</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7725,42 +7720,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540238</v>
+        <v>540128</v>
       </c>
       <c r="R60" t="n">
-        <v>7001222</v>
+        <v>7001058</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7800,6 +7795,11 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7816,10 +7816,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127155182</v>
+        <v>127156085</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7845,21 +7845,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539891</v>
+        <v>539948</v>
       </c>
       <c r="R61" t="n">
-        <v>7001292</v>
+        <v>7001204</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7892,11 +7887,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7948,10 +7938,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127153134</v>
+        <v>127155182</v>
       </c>
       <c r="B62" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7959,32 +7949,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7993,10 +7978,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539827</v>
+        <v>539891</v>
       </c>
       <c r="R62" t="n">
-        <v>7001225</v>
+        <v>7001292</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8033,7 +8018,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8062,12 +8047,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8085,48 +8070,67 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127156085</v>
+        <v>127158943</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539948</v>
+        <v>540039</v>
       </c>
       <c r="R63" t="n">
-        <v>7001204</v>
+        <v>7001317</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8158,6 +8162,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -8170,26 +8179,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8207,47 +8196,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127158943</v>
+        <v>127153134</v>
       </c>
       <c r="B64" t="n">
-        <v>98361</v>
+        <v>57654</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -8257,17 +8237,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540039</v>
+        <v>539827</v>
       </c>
       <c r="R64" t="n">
-        <v>7001317</v>
+        <v>7001225</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8301,7 +8281,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8316,6 +8296,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8336,7 +8336,7 @@
         <v>127163069</v>
       </c>
       <c r="B65" t="n">
-        <v>91241</v>
+        <v>91315</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>127160440</v>
       </c>
       <c r="B66" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>127160736</v>
       </c>
       <c r="B67" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>127160774</v>
       </c>
       <c r="B68" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>127162146</v>
       </c>
       <c r="B69" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8928,10 +8928,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127162549</v>
+        <v>127155980</v>
       </c>
       <c r="B70" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8956,25 +8956,39 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540212</v>
+        <v>539933</v>
       </c>
       <c r="R70" t="n">
-        <v>7001230</v>
+        <v>7001238</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9014,6 +9028,11 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9030,10 +9049,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127164741</v>
+        <v>127162549</v>
       </c>
       <c r="B71" t="n">
-        <v>98278</v>
+        <v>98459</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9041,21 +9060,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9066,17 +9085,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540004</v>
+        <v>540212</v>
       </c>
       <c r="R71" t="n">
-        <v>7001090</v>
+        <v>7001230</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9132,10 +9151,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127155980</v>
+        <v>127164741</v>
       </c>
       <c r="B72" t="n">
-        <v>98384</v>
+        <v>98353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9143,56 +9162,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>539933</v>
+        <v>540004</v>
       </c>
       <c r="R72" t="n">
-        <v>7001238</v>
+        <v>7001090</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9232,11 +9237,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9253,53 +9253,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127153185</v>
+        <v>127159827</v>
       </c>
       <c r="B73" t="n">
-        <v>98694</v>
+        <v>80114</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>539835</v>
+        <v>540122</v>
       </c>
       <c r="R73" t="n">
-        <v>7001233</v>
+        <v>7001326</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9343,6 +9343,26 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9360,53 +9380,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127159827</v>
+        <v>127153185</v>
       </c>
       <c r="B74" t="n">
-        <v>80083</v>
+        <v>98769</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540122</v>
+        <v>539835</v>
       </c>
       <c r="R74" t="n">
-        <v>7001326</v>
+        <v>7001233</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9450,26 +9470,6 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9490,7 +9490,7 @@
         <v>127158202</v>
       </c>
       <c r="B75" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>127154622</v>
       </c>
       <c r="B76" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>127162730</v>
       </c>
       <c r="B77" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>127163162</v>
       </c>
       <c r="B78" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>127156896</v>
       </c>
       <c r="B79" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10081,10 +10081,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127157972</v>
+        <v>127160558</v>
       </c>
       <c r="B80" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10092,47 +10092,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540038</v>
+        <v>540205</v>
       </c>
       <c r="R80" t="n">
-        <v>7001245</v>
+        <v>7001321</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10164,11 +10154,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10195,12 +10180,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -10218,10 +10203,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127160558</v>
+        <v>127157972</v>
       </c>
       <c r="B81" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10229,37 +10214,47 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540205</v>
+        <v>540038</v>
       </c>
       <c r="R81" t="n">
-        <v>7001321</v>
+        <v>7001245</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10291,6 +10286,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10317,12 +10317,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10343,7 +10343,7 @@
         <v>127161443</v>
       </c>
       <c r="B82" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>127154216</v>
       </c>
       <c r="B83" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>127155895</v>
       </c>
       <c r="B84" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10719,58 +10719,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127155804</v>
+        <v>127164354</v>
       </c>
       <c r="B85" t="n">
-        <v>98382</v>
+        <v>79011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>539886</v>
+        <v>540166</v>
       </c>
       <c r="R85" t="n">
-        <v>7001291</v>
+        <v>7001045</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10810,6 +10800,31 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10826,10 +10841,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127160670</v>
+        <v>127163738</v>
       </c>
       <c r="B86" t="n">
-        <v>98384</v>
+        <v>98457</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10837,33 +10852,24 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -10871,17 +10877,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540195</v>
+        <v>540308</v>
       </c>
       <c r="R86" t="n">
-        <v>7001331</v>
+        <v>7001066</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10913,11 +10919,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10926,11 +10927,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10947,10 +10943,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127163738</v>
+        <v>127160670</v>
       </c>
       <c r="B87" t="n">
-        <v>98382</v>
+        <v>98459</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10958,24 +10954,33 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -10983,17 +10988,17 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540308</v>
+        <v>540195</v>
       </c>
       <c r="R87" t="n">
-        <v>7001066</v>
+        <v>7001331</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11025,6 +11030,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -11033,6 +11043,11 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11049,48 +11064,58 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127164354</v>
+        <v>127155804</v>
       </c>
       <c r="B88" t="n">
-        <v>78980</v>
+        <v>98457</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540166</v>
+        <v>539886</v>
       </c>
       <c r="R88" t="n">
-        <v>7001045</v>
+        <v>7001291</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11130,31 +11155,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11174,7 +11174,7 @@
         <v>127159714</v>
       </c>
       <c r="B89" t="n">
-        <v>98359</v>
+        <v>98434</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11307,10 +11307,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127157226</v>
+        <v>127157856</v>
       </c>
       <c r="B90" t="n">
-        <v>98384</v>
+        <v>98342</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11318,26 +11318,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11350,6 +11350,7 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11361,13 +11362,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539976</v>
+        <v>539984</v>
       </c>
       <c r="R90" t="n">
-        <v>7001240</v>
+        <v>7001243</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11394,17 +11395,33 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11428,10 +11445,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127157856</v>
+        <v>127157226</v>
       </c>
       <c r="B91" t="n">
-        <v>98267</v>
+        <v>98459</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11439,26 +11456,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11471,7 +11488,6 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11483,13 +11499,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>539984</v>
+        <v>539976</v>
       </c>
       <c r="R91" t="n">
-        <v>7001243</v>
+        <v>7001240</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11516,33 +11532,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>127159972</v>
       </c>
       <c r="B92" t="n">
-        <v>98359</v>
+        <v>98434</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>127155729</v>
       </c>
       <c r="B93" t="n">
-        <v>98267</v>
+        <v>98342</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>127174668</v>
       </c>
       <c r="B94" t="n">
-        <v>90790</v>
+        <v>90864</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>127157050</v>
       </c>
       <c r="B95" t="n">
-        <v>98267</v>
+        <v>98342</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12069,67 +12069,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127160071</v>
+        <v>127160214</v>
       </c>
       <c r="B96" t="n">
-        <v>98361</v>
+        <v>80114</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540115</v>
+        <v>540081</v>
       </c>
       <c r="R96" t="n">
-        <v>7001289</v>
+        <v>7001299</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12161,11 +12142,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12178,6 +12154,26 @@
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12195,48 +12191,67 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127160214</v>
+        <v>127160071</v>
       </c>
       <c r="B97" t="n">
-        <v>80083</v>
+        <v>98436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540081</v>
+        <v>540115</v>
       </c>
       <c r="R97" t="n">
-        <v>7001299</v>
+        <v>7001289</v>
       </c>
       <c r="S97" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12268,6 +12283,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12280,26 +12300,6 @@
       <c r="AH97" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12320,7 +12320,7 @@
         <v>127155870</v>
       </c>
       <c r="B98" t="n">
-        <v>98267</v>
+        <v>98342</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>127164256</v>
       </c>
       <c r="B99" t="n">
-        <v>98267</v>
+        <v>98342</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>127157299</v>
       </c>
       <c r="B100" t="n">
-        <v>98267</v>
+        <v>98342</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>127162786</v>
       </c>
       <c r="B101" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127164710</v>
+        <v>127160294</v>
       </c>
       <c r="B2" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540011</v>
+        <v>540092</v>
       </c>
       <c r="R2" t="n">
-        <v>7001079</v>
+        <v>7001341</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,11 +753,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -784,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127162096</v>
+        <v>127164710</v>
       </c>
       <c r="B3" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,22 +833,22 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540104</v>
+        <v>540011</v>
       </c>
       <c r="R3" t="n">
-        <v>7001431</v>
+        <v>7001079</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127160294</v>
+        <v>127162096</v>
       </c>
       <c r="B4" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +965,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -979,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540092</v>
+        <v>540104</v>
       </c>
       <c r="R4" t="n">
-        <v>7001341</v>
+        <v>7001431</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,6 +1012,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på två sälgar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1069,7 +1069,7 @@
         <v>127162017</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>80152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127161646</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,53 +1314,58 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127162604</v>
+        <v>127153536</v>
       </c>
       <c r="B7" t="n">
-        <v>98353</v>
+        <v>57654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540240</v>
+        <v>539859</v>
       </c>
       <c r="R7" t="n">
-        <v>7001210</v>
+        <v>7001178</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1392,6 +1397,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1400,6 +1410,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1416,50 +1431,55 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127163443</v>
+        <v>127158784</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540255</v>
+        <v>540039</v>
       </c>
       <c r="R8" t="n">
-        <v>7001070</v>
+        <v>7001341</v>
       </c>
       <c r="S8" t="n">
         <v>11</v>
@@ -1489,11 +1509,26 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1502,6 +1537,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1518,10 +1578,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127162418</v>
+        <v>127163443</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98465</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,42 +1589,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540127</v>
+        <v>540255</v>
       </c>
       <c r="R9" t="n">
-        <v>7001264</v>
+        <v>7001070</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1604,11 +1664,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1625,58 +1680,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127153536</v>
+        <v>127162604</v>
       </c>
       <c r="B10" t="n">
-        <v>57654</v>
+        <v>98359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539859</v>
+        <v>540240</v>
       </c>
       <c r="R10" t="n">
-        <v>7001178</v>
+        <v>7001210</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,11 +1758,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1721,11 +1766,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1742,43 +1782,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127158784</v>
+        <v>127162418</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>98775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1787,13 +1822,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540039</v>
+        <v>540127</v>
       </c>
       <c r="R11" t="n">
-        <v>7001341</v>
+        <v>7001264</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,26 +1855,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1852,26 +1872,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1889,62 +1889,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127162375</v>
+        <v>127154593</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540115</v>
+        <v>539874</v>
       </c>
       <c r="R12" t="n">
-        <v>7001309</v>
+        <v>7001234</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1978,7 +1969,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1993,6 +1984,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2010,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127154593</v>
+        <v>127160359</v>
       </c>
       <c r="B13" t="n">
-        <v>80114</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,42 +2032,51 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539874</v>
+        <v>540139</v>
       </c>
       <c r="R13" t="n">
-        <v>7001234</v>
+        <v>7001298</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2083,14 +2103,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
+          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2105,26 +2135,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2142,42 +2152,47 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127160359</v>
+        <v>127155767</v>
       </c>
       <c r="B14" t="n">
-        <v>57817</v>
+        <v>98359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2187,17 +2202,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540139</v>
+        <v>539895</v>
       </c>
       <c r="R14" t="n">
-        <v>7001298</v>
+        <v>7001284</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2224,24 +2239,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2273,37 +2278,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155767</v>
+        <v>127162375</v>
       </c>
       <c r="B15" t="n">
-        <v>98353</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2313,27 +2318,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539895</v>
+        <v>540115</v>
       </c>
       <c r="R15" t="n">
-        <v>7001284</v>
+        <v>7001309</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2399,10 +2399,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127159187</v>
+        <v>127160480</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2410,47 +2410,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540057</v>
+        <v>540188</v>
       </c>
       <c r="R16" t="n">
-        <v>7001353</v>
+        <v>7001269</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2477,26 +2467,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2523,12 +2498,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2549,7 +2524,7 @@
         <v>127161347</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2678,10 +2653,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127160480</v>
+        <v>127159187</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,37 +2664,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540188</v>
+        <v>540057</v>
       </c>
       <c r="R18" t="n">
-        <v>7001269</v>
+        <v>7001353</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2746,11 +2731,26 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2800,53 +2800,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127160270</v>
+        <v>127153666</v>
       </c>
       <c r="B19" t="n">
-        <v>98457</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540095</v>
+        <v>539888</v>
       </c>
       <c r="R19" t="n">
-        <v>7001315</v>
+        <v>7001166</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2890,6 +2885,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2907,62 +2922,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127163626</v>
+        <v>127164774</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540307</v>
+        <v>540022</v>
       </c>
       <c r="R20" t="n">
-        <v>7001050</v>
+        <v>7001093</v>
       </c>
       <c r="S20" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2994,11 +2995,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3011,6 +3007,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3028,62 +3044,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127152848</v>
+        <v>127163769</v>
       </c>
       <c r="B21" t="n">
-        <v>98353</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539832</v>
+        <v>540285</v>
       </c>
       <c r="R21" t="n">
-        <v>7001265</v>
+        <v>7001071</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3127,6 +3129,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3144,48 +3166,62 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127164774</v>
+        <v>127163626</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>98465</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540022</v>
+        <v>540307</v>
       </c>
       <c r="R22" t="n">
-        <v>7001093</v>
+        <v>7001050</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3217,6 +3253,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3229,26 +3270,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3266,48 +3287,62 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127153666</v>
+        <v>127152848</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>98359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539888</v>
+        <v>539832</v>
       </c>
       <c r="R23" t="n">
-        <v>7001166</v>
+        <v>7001265</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3351,26 +3386,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3388,48 +3403,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127163769</v>
+        <v>127160270</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>98463</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540285</v>
+        <v>540095</v>
       </c>
       <c r="R24" t="n">
-        <v>7001071</v>
+        <v>7001315</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3473,26 +3493,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3510,48 +3510,67 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127163495</v>
+        <v>127155997</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>98359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540258</v>
+        <v>539924</v>
       </c>
       <c r="R25" t="n">
-        <v>7001065</v>
+        <v>7001238</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3594,27 +3613,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3635,7 +3634,7 @@
         <v>127158356</v>
       </c>
       <c r="B26" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,67 +3758,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127155997</v>
+        <v>127163495</v>
       </c>
       <c r="B27" t="n">
-        <v>98353</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539924</v>
+        <v>540258</v>
       </c>
       <c r="R27" t="n">
-        <v>7001238</v>
+        <v>7001065</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3862,7 +3842,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3880,53 +3880,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153641</v>
+        <v>127153018</v>
       </c>
       <c r="B28" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539864</v>
+        <v>539829</v>
       </c>
       <c r="R28" t="n">
-        <v>7001177</v>
+        <v>7001270</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3974,22 +3969,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4007,38 +4002,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153581</v>
+        <v>127153641</v>
       </c>
       <c r="B29" t="n">
-        <v>80114</v>
+        <v>80146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4047,13 +4042,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539872</v>
+        <v>539864</v>
       </c>
       <c r="R29" t="n">
-        <v>7001176</v>
+        <v>7001177</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4134,10 +4129,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127160821</v>
+        <v>127153581</v>
       </c>
       <c r="B30" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4170,14 +4165,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540188</v>
+        <v>539872</v>
       </c>
       <c r="R30" t="n">
-        <v>7001373</v>
+        <v>7001176</v>
       </c>
       <c r="S30" t="n">
         <v>12</v>
@@ -4210,11 +4205,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en upplyft liggande levande sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4266,10 +4256,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127153018</v>
+        <v>127160821</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4277,37 +4267,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539829</v>
+        <v>540188</v>
       </c>
       <c r="R31" t="n">
-        <v>7001270</v>
+        <v>7001373</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4339,6 +4334,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en upplyft liggande levande sälg.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4355,22 +4355,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4391,7 +4391,7 @@
         <v>127153897</v>
       </c>
       <c r="B32" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>127161738</v>
       </c>
       <c r="B33" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>127161580</v>
       </c>
       <c r="B34" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>127164937</v>
       </c>
       <c r="B35" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>127158834</v>
       </c>
       <c r="B36" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>127163212</v>
       </c>
       <c r="B37" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127164541</v>
+        <v>127164835</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5150,34 +5150,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540113</v>
+        <v>539992</v>
       </c>
       <c r="R38" t="n">
-        <v>7001087</v>
+        <v>7001093</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5212,6 +5217,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5228,22 +5238,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5261,10 +5271,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127154714</v>
+        <v>127153765</v>
       </c>
       <c r="B39" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5292,7 +5302,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5301,13 +5311,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539872</v>
+        <v>539879</v>
       </c>
       <c r="R39" t="n">
-        <v>7001243</v>
+        <v>7001196</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5341,7 +5351,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Lunglav på 3 gamla sälgar.</t>
+          <t>Fertil lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5393,10 +5403,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127164835</v>
+        <v>127164541</v>
       </c>
       <c r="B40" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5404,39 +5414,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539992</v>
+        <v>540113</v>
       </c>
       <c r="R40" t="n">
-        <v>7001093</v>
+        <v>7001087</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5471,11 +5476,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Växer här på en grov gammal sälg (värdeträd).</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5492,22 +5492,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153765</v>
+        <v>127154714</v>
       </c>
       <c r="B41" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5565,13 +5565,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539879</v>
+        <v>539872</v>
       </c>
       <c r="R41" t="n">
-        <v>7001196</v>
+        <v>7001243</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg.</t>
+          <t>Lunglav på 3 gamla sälgar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5657,53 +5657,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127163137</v>
+        <v>127162532</v>
       </c>
       <c r="B42" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540285</v>
+        <v>540214</v>
       </c>
       <c r="R42" t="n">
-        <v>7001126</v>
+        <v>7001228</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5743,6 +5738,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5759,38 +5779,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127162701</v>
+        <v>127164613</v>
       </c>
       <c r="B43" t="n">
-        <v>98457</v>
+        <v>80117</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5799,13 +5819,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540246</v>
+        <v>540079</v>
       </c>
       <c r="R43" t="n">
-        <v>7001169</v>
+        <v>7001087</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5849,6 +5869,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5866,48 +5906,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127162532</v>
+        <v>127162701</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>98463</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540214</v>
+        <v>540246</v>
       </c>
       <c r="R44" t="n">
-        <v>7001228</v>
+        <v>7001169</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5951,26 +5996,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5988,38 +6013,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127164613</v>
+        <v>127163976</v>
       </c>
       <c r="B45" t="n">
-        <v>80114</v>
+        <v>98465</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6028,13 +6053,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540079</v>
+        <v>540285</v>
       </c>
       <c r="R45" t="n">
-        <v>7001087</v>
+        <v>7001072</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6074,31 +6099,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6118,7 +6118,7 @@
         <v>127158031</v>
       </c>
       <c r="B46" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6236,38 +6236,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127163976</v>
+        <v>127163137</v>
       </c>
       <c r="B47" t="n">
-        <v>98459</v>
+        <v>98442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6279,7 +6279,7 @@
         <v>540285</v>
       </c>
       <c r="R47" t="n">
-        <v>7001072</v>
+        <v>7001126</v>
       </c>
       <c r="S47" t="n">
         <v>7</v>
@@ -6338,67 +6338,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127153495</v>
+        <v>127160120</v>
       </c>
       <c r="B48" t="n">
-        <v>98436</v>
+        <v>98775</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539858</v>
+        <v>540106</v>
       </c>
       <c r="R48" t="n">
-        <v>7001193</v>
+        <v>7001289</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6428,11 +6414,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6464,38 +6445,52 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127152890</v>
+        <v>127153495</v>
       </c>
       <c r="B49" t="n">
-        <v>98457</v>
+        <v>98442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6504,10 +6499,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539829</v>
+        <v>539858</v>
       </c>
       <c r="R49" t="n">
-        <v>7001270</v>
+        <v>7001193</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6540,6 +6535,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6571,10 +6571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127153809</v>
+        <v>127164902</v>
       </c>
       <c r="B50" t="n">
-        <v>80150</v>
+        <v>98465</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6582,42 +6582,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539890</v>
+        <v>539989</v>
       </c>
       <c r="R50" t="n">
-        <v>7001195</v>
+        <v>7001089</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6657,31 +6657,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6698,10 +6673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127160120</v>
+        <v>127152890</v>
       </c>
       <c r="B51" t="n">
-        <v>98769</v>
+        <v>98463</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6709,42 +6684,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219880</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540106</v>
+        <v>539829</v>
       </c>
       <c r="R51" t="n">
-        <v>7001289</v>
+        <v>7001270</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6805,10 +6780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127164902</v>
+        <v>127153809</v>
       </c>
       <c r="B52" t="n">
-        <v>98459</v>
+        <v>80153</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6816,42 +6791,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539989</v>
+        <v>539890</v>
       </c>
       <c r="R52" t="n">
-        <v>7001089</v>
+        <v>7001195</v>
       </c>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6891,6 +6866,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6907,45 +6907,55 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127162675</v>
+        <v>127159734</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>98359</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540237</v>
+        <v>540115</v>
       </c>
       <c r="R53" t="n">
-        <v>7001188</v>
+        <v>7001344</v>
       </c>
       <c r="S53" t="n">
         <v>11</v>
@@ -6991,27 +7001,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7029,48 +7019,67 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127161775</v>
+        <v>127156042</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>98465</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540092</v>
+        <v>539924</v>
       </c>
       <c r="R54" t="n">
-        <v>7001443</v>
+        <v>7001238</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7113,27 +7122,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7151,10 +7140,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127159734</v>
+        <v>127162577</v>
       </c>
       <c r="B55" t="n">
-        <v>98353</v>
+        <v>98465</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7162,21 +7151,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7185,24 +7174,19 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540115</v>
+        <v>540238</v>
       </c>
       <c r="R55" t="n">
-        <v>7001344</v>
+        <v>7001222</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7242,11 +7226,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7263,10 +7242,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127156042</v>
+        <v>127160489</v>
       </c>
       <c r="B56" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7291,39 +7270,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539924</v>
+        <v>540171</v>
       </c>
       <c r="R56" t="n">
-        <v>7001238</v>
+        <v>7001276</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7366,7 +7331,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7384,10 +7349,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127162577</v>
+        <v>127164425</v>
       </c>
       <c r="B57" t="n">
-        <v>98459</v>
+        <v>98463</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7395,42 +7360,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540238</v>
+        <v>540128</v>
       </c>
       <c r="R57" t="n">
-        <v>7001222</v>
+        <v>7001058</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7470,6 +7435,11 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7486,53 +7456,62 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127160489</v>
+        <v>127163731</v>
       </c>
       <c r="B58" t="n">
-        <v>98459</v>
+        <v>98442</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540171</v>
+        <v>540303</v>
       </c>
       <c r="R58" t="n">
-        <v>7001276</v>
+        <v>7001059</v>
       </c>
       <c r="S58" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7593,62 +7572,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127163731</v>
+        <v>127162675</v>
       </c>
       <c r="B59" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540303</v>
+        <v>540237</v>
       </c>
       <c r="R59" t="n">
-        <v>7001059</v>
+        <v>7001188</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7692,6 +7657,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7709,53 +7694,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127164425</v>
+        <v>127161775</v>
       </c>
       <c r="B60" t="n">
-        <v>98457</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540128</v>
+        <v>540092</v>
       </c>
       <c r="R60" t="n">
-        <v>7001058</v>
+        <v>7001443</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7799,6 +7779,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
         <v>127156085</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>127155182</v>
       </c>
       <c r="B62" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>127158943</v>
       </c>
       <c r="B63" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>127163069</v>
       </c>
       <c r="B65" t="n">
-        <v>91315</v>
+        <v>91321</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8460,38 +8460,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127160440</v>
+        <v>127160736</v>
       </c>
       <c r="B66" t="n">
-        <v>91773</v>
+        <v>98463</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540128</v>
+        <v>540193</v>
       </c>
       <c r="R66" t="n">
-        <v>7001287</v>
+        <v>7001357</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8538,11 +8538,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8555,26 +8550,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8592,38 +8567,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127160736</v>
+        <v>127160440</v>
       </c>
       <c r="B67" t="n">
-        <v>98457</v>
+        <v>91779</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8632,13 +8607,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540193</v>
+        <v>540128</v>
       </c>
       <c r="R67" t="n">
-        <v>7001357</v>
+        <v>7001287</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8670,6 +8645,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8682,6 +8662,26 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8702,7 +8702,7 @@
         <v>127160774</v>
       </c>
       <c r="B68" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8821,10 +8821,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127162146</v>
+        <v>127164741</v>
       </c>
       <c r="B69" t="n">
-        <v>98457</v>
+        <v>98359</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8832,42 +8832,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540106</v>
+        <v>540004</v>
       </c>
       <c r="R69" t="n">
-        <v>7001407</v>
+        <v>7001090</v>
       </c>
       <c r="S69" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8907,11 +8907,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8931,7 +8926,7 @@
         <v>127155980</v>
       </c>
       <c r="B70" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9052,7 +9047,7 @@
         <v>127162549</v>
       </c>
       <c r="B71" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9151,10 +9146,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127164741</v>
+        <v>127162146</v>
       </c>
       <c r="B72" t="n">
-        <v>98353</v>
+        <v>98463</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9162,42 +9157,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540004</v>
+        <v>540106</v>
       </c>
       <c r="R72" t="n">
-        <v>7001090</v>
+        <v>7001407</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9237,6 +9232,11 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9253,53 +9253,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127159827</v>
+        <v>127153185</v>
       </c>
       <c r="B73" t="n">
-        <v>80114</v>
+        <v>98775</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540122</v>
+        <v>539835</v>
       </c>
       <c r="R73" t="n">
-        <v>7001326</v>
+        <v>7001233</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9343,26 +9343,6 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9380,53 +9360,53 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127153185</v>
+        <v>127158202</v>
       </c>
       <c r="B74" t="n">
-        <v>98769</v>
+        <v>91343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>539835</v>
+        <v>540038</v>
       </c>
       <c r="R74" t="n">
-        <v>7001233</v>
+        <v>7001306</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9458,6 +9438,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikliga mängder död ved.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9470,6 +9455,16 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9487,10 +9482,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127158202</v>
+        <v>127159827</v>
       </c>
       <c r="B75" t="n">
-        <v>91337</v>
+        <v>80117</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9498,27 +9493,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9527,13 +9522,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540038</v>
+        <v>540122</v>
       </c>
       <c r="R75" t="n">
-        <v>7001306</v>
+        <v>7001326</v>
       </c>
       <c r="S75" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9565,11 +9560,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På fyndplatsen finns rikliga mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9584,14 +9574,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9612,7 +9612,7 @@
         <v>127154622</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9731,10 +9731,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127162730</v>
+        <v>127163162</v>
       </c>
       <c r="B77" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9759,16 +9759,7 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9776,17 +9767,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540258</v>
+        <v>540247</v>
       </c>
       <c r="R77" t="n">
-        <v>7001179</v>
+        <v>7001094</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9826,11 +9817,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9847,10 +9833,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127163162</v>
+        <v>127162730</v>
       </c>
       <c r="B78" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9875,7 +9861,16 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9883,17 +9878,17 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540247</v>
+        <v>540258</v>
       </c>
       <c r="R78" t="n">
-        <v>7001094</v>
+        <v>7001179</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9933,6 +9928,11 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9949,53 +9949,67 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127156896</v>
+        <v>127154216</v>
       </c>
       <c r="B79" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539983</v>
+        <v>539858</v>
       </c>
       <c r="R79" t="n">
-        <v>7001163</v>
+        <v>7001227</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10029,7 +10043,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Långväxta och fertila bålar på flera granar.</t>
+          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10044,26 +10058,6 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10081,10 +10075,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127160558</v>
+        <v>127156896</v>
       </c>
       <c r="B80" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10110,19 +10104,24 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540205</v>
+        <v>539983</v>
       </c>
       <c r="R80" t="n">
-        <v>7001321</v>
+        <v>7001163</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10152,6 +10151,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10203,10 +10207,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127157972</v>
+        <v>127161443</v>
       </c>
       <c r="B81" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10214,47 +10218,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540038</v>
+        <v>540137</v>
       </c>
       <c r="R81" t="n">
-        <v>7001245</v>
+        <v>7001432</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10288,7 +10282,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10317,12 +10311,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10340,10 +10334,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127161443</v>
+        <v>127160558</v>
       </c>
       <c r="B82" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10375,13 +10369,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540137</v>
+        <v>540205</v>
       </c>
       <c r="R82" t="n">
-        <v>7001432</v>
+        <v>7001321</v>
       </c>
       <c r="S82" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10411,11 +10405,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10467,47 +10456,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127154216</v>
+        <v>127157972</v>
       </c>
       <c r="B83" t="n">
-        <v>98436</v>
+        <v>57654</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -10517,17 +10497,17 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>539858</v>
+        <v>540038</v>
       </c>
       <c r="R83" t="n">
-        <v>7001227</v>
+        <v>7001245</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10561,7 +10541,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
+          <t>Färska och äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10576,6 +10556,26 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10596,7 +10596,7 @@
         <v>127155895</v>
       </c>
       <c r="B84" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>127164354</v>
       </c>
       <c r="B85" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10841,10 +10841,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127163738</v>
+        <v>127160670</v>
       </c>
       <c r="B86" t="n">
-        <v>98457</v>
+        <v>98465</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10852,24 +10852,33 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -10877,17 +10886,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540308</v>
+        <v>540195</v>
       </c>
       <c r="R86" t="n">
-        <v>7001066</v>
+        <v>7001331</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10919,6 +10928,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10927,6 +10941,11 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10943,10 +10962,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127160670</v>
+        <v>127155804</v>
       </c>
       <c r="B87" t="n">
-        <v>98459</v>
+        <v>98463</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10954,48 +10973,44 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540195</v>
+        <v>539886</v>
       </c>
       <c r="R87" t="n">
-        <v>7001331</v>
+        <v>7001291</v>
       </c>
       <c r="S87" t="n">
         <v>9</v>
@@ -11030,11 +11045,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -11043,11 +11053,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11064,10 +11069,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127155804</v>
+        <v>127163738</v>
       </c>
       <c r="B88" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11095,27 +11100,22 @@
       <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>539886</v>
+        <v>540308</v>
       </c>
       <c r="R88" t="n">
-        <v>7001291</v>
+        <v>7001066</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>127159714</v>
       </c>
       <c r="B89" t="n">
-        <v>98434</v>
+        <v>98440</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11307,10 +11307,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127157856</v>
+        <v>127157226</v>
       </c>
       <c r="B90" t="n">
-        <v>98342</v>
+        <v>98465</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11318,26 +11318,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11350,7 +11350,6 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11362,13 +11361,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539984</v>
+        <v>539976</v>
       </c>
       <c r="R90" t="n">
-        <v>7001243</v>
+        <v>7001240</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11395,33 +11394,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11445,10 +11428,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127157226</v>
+        <v>127157856</v>
       </c>
       <c r="B91" t="n">
-        <v>98459</v>
+        <v>98348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11456,26 +11439,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11488,6 +11471,7 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11499,13 +11483,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>539976</v>
+        <v>539984</v>
       </c>
       <c r="R91" t="n">
-        <v>7001240</v>
+        <v>7001243</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11532,17 +11516,33 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>127159972</v>
       </c>
       <c r="B92" t="n">
-        <v>98434</v>
+        <v>98440</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>127155729</v>
       </c>
       <c r="B93" t="n">
-        <v>98342</v>
+        <v>98348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>127174668</v>
       </c>
       <c r="B94" t="n">
-        <v>90864</v>
+        <v>90870</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>127157050</v>
       </c>
       <c r="B95" t="n">
-        <v>98342</v>
+        <v>98348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12069,48 +12069,67 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127160214</v>
+        <v>127160071</v>
       </c>
       <c r="B96" t="n">
-        <v>80114</v>
+        <v>98442</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540081</v>
+        <v>540115</v>
       </c>
       <c r="R96" t="n">
-        <v>7001299</v>
+        <v>7001289</v>
       </c>
       <c r="S96" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12142,6 +12161,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12154,26 +12178,6 @@
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12191,67 +12195,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127160071</v>
+        <v>127160214</v>
       </c>
       <c r="B97" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540115</v>
+        <v>540081</v>
       </c>
       <c r="R97" t="n">
-        <v>7001289</v>
+        <v>7001299</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12283,11 +12268,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12300,6 +12280,26 @@
       <c r="AH97" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -12320,7 +12320,7 @@
         <v>127155870</v>
       </c>
       <c r="B98" t="n">
-        <v>98342</v>
+        <v>98348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>127164256</v>
       </c>
       <c r="B99" t="n">
-        <v>98342</v>
+        <v>98348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>127157299</v>
       </c>
       <c r="B100" t="n">
-        <v>98342</v>
+        <v>98348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>127162786</v>
       </c>
       <c r="B101" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127160294</v>
+        <v>127162017</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>80152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540092</v>
+        <v>540111</v>
       </c>
       <c r="R2" t="n">
-        <v>7001341</v>
+        <v>7001420</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -779,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127164710</v>
+        <v>127153536</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,42 +813,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540011</v>
+        <v>539859</v>
       </c>
       <c r="R3" t="n">
-        <v>7001079</v>
+        <v>7001178</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,26 +902,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127162096</v>
+        <v>127158784</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,27 +930,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540104</v>
+        <v>540039</v>
       </c>
       <c r="R4" t="n">
-        <v>7001431</v>
+        <v>7001341</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,14 +997,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127162017</v>
+        <v>127162604</v>
       </c>
       <c r="B5" t="n">
-        <v>80152</v>
+        <v>98359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,27 +1077,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540111</v>
+        <v>540240</v>
       </c>
       <c r="R5" t="n">
-        <v>7001420</v>
+        <v>7001210</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1152,31 +1152,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1314,58 +1289,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153536</v>
+        <v>127163443</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>98465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539859</v>
+        <v>540255</v>
       </c>
       <c r="R7" t="n">
-        <v>7001178</v>
+        <v>7001070</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1397,11 +1367,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1410,11 +1375,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1431,43 +1391,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127158784</v>
+        <v>127162418</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>98775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1476,13 +1431,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540039</v>
+        <v>540127</v>
       </c>
       <c r="R8" t="n">
-        <v>7001341</v>
+        <v>7001264</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,26 +1464,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1541,26 +1481,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1578,38 +1498,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127163443</v>
+        <v>127164710</v>
       </c>
       <c r="B9" t="n">
-        <v>98465</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1618,13 +1538,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540255</v>
+        <v>540011</v>
       </c>
       <c r="R9" t="n">
-        <v>7001070</v>
+        <v>7001079</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1656,6 +1576,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1664,6 +1589,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1680,38 +1630,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127162604</v>
+        <v>127162096</v>
       </c>
       <c r="B10" t="n">
-        <v>98359</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1720,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540240</v>
+        <v>540104</v>
       </c>
       <c r="R10" t="n">
-        <v>7001210</v>
+        <v>7001431</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1758,6 +1708,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på två sälgar.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1766,6 +1721,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1782,38 +1762,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127162418</v>
+        <v>127160294</v>
       </c>
       <c r="B11" t="n">
-        <v>98775</v>
+        <v>80117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1822,10 +1802,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540127</v>
+        <v>540092</v>
       </c>
       <c r="R11" t="n">
-        <v>7001264</v>
+        <v>7001341</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1872,6 +1852,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1889,38 +1889,52 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127154593</v>
+        <v>127155767</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>98359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1929,13 +1943,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539874</v>
+        <v>539895</v>
       </c>
       <c r="R12" t="n">
-        <v>7001234</v>
+        <v>7001284</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1969,7 +1983,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,26 +1998,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2021,47 +2015,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127160359</v>
+        <v>127162375</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2070,13 +2064,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540139</v>
+        <v>540115</v>
       </c>
       <c r="R13" t="n">
-        <v>7001298</v>
+        <v>7001309</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2103,24 +2097,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2152,52 +2136,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127155767</v>
+        <v>127154593</v>
       </c>
       <c r="B14" t="n">
-        <v>98359</v>
+        <v>80117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2206,13 +2176,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539895</v>
+        <v>539874</v>
       </c>
       <c r="R14" t="n">
-        <v>7001284</v>
+        <v>7001234</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2246,7 +2216,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,6 +2231,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2278,47 +2268,47 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127162375</v>
+        <v>127160359</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2327,13 +2317,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540115</v>
+        <v>540139</v>
       </c>
       <c r="R15" t="n">
-        <v>7001309</v>
+        <v>7001298</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2360,14 +2350,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2399,7 +2399,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127160480</v>
+        <v>127161347</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2428,19 +2428,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540188</v>
+        <v>540157</v>
       </c>
       <c r="R16" t="n">
-        <v>7001269</v>
+        <v>7001411</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2470,6 +2475,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2521,7 +2531,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127161347</v>
+        <v>127160480</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2550,24 +2560,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540157</v>
+        <v>540188</v>
       </c>
       <c r="R17" t="n">
-        <v>7001411</v>
+        <v>7001269</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2597,11 +2602,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2800,48 +2800,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127153666</v>
+        <v>127160270</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>98463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539888</v>
+        <v>540095</v>
       </c>
       <c r="R19" t="n">
-        <v>7001166</v>
+        <v>7001315</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2885,26 +2890,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2922,48 +2907,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127164774</v>
+        <v>127163626</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>98465</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540022</v>
+        <v>540307</v>
       </c>
       <c r="R20" t="n">
-        <v>7001093</v>
+        <v>7001050</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2995,6 +2994,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3007,26 +3011,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3044,48 +3028,62 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127163769</v>
+        <v>127152848</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540285</v>
+        <v>539832</v>
       </c>
       <c r="R21" t="n">
-        <v>7001071</v>
+        <v>7001265</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3129,26 +3127,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3166,62 +3144,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127163626</v>
+        <v>127164774</v>
       </c>
       <c r="B22" t="n">
-        <v>98465</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540307</v>
+        <v>540022</v>
       </c>
       <c r="R22" t="n">
-        <v>7001050</v>
+        <v>7001093</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3253,11 +3217,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3270,6 +3229,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3287,62 +3266,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127152848</v>
+        <v>127153666</v>
       </c>
       <c r="B23" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539832</v>
+        <v>539888</v>
       </c>
       <c r="R23" t="n">
-        <v>7001265</v>
+        <v>7001166</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3386,6 +3351,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3403,53 +3388,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127160270</v>
+        <v>127163769</v>
       </c>
       <c r="B24" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540095</v>
+        <v>540285</v>
       </c>
       <c r="R24" t="n">
-        <v>7001315</v>
+        <v>7001071</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3493,6 +3473,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3510,64 +3510,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127155997</v>
+        <v>127158356</v>
       </c>
       <c r="B25" t="n">
-        <v>98359</v>
+        <v>91325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>539924</v>
+        <v>540032</v>
       </c>
       <c r="R25" t="n">
-        <v>7001238</v>
+        <v>7001287</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3613,7 +3599,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3631,50 +3637,64 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127158356</v>
+        <v>127155997</v>
       </c>
       <c r="B26" t="n">
-        <v>91325</v>
+        <v>98359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540032</v>
+        <v>539924</v>
       </c>
       <c r="R26" t="n">
-        <v>7001287</v>
+        <v>7001238</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3720,27 +3740,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4514,53 +4514,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127161738</v>
+        <v>127163212</v>
       </c>
       <c r="B33" t="n">
-        <v>80117</v>
+        <v>98465</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540129</v>
+        <v>540253</v>
       </c>
       <c r="R33" t="n">
-        <v>7001452</v>
+        <v>7001109</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4592,11 +4592,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4609,26 +4604,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4646,7 +4621,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127161580</v>
+        <v>127161738</v>
       </c>
       <c r="B34" t="n">
         <v>80117</v>
@@ -4677,7 +4652,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4686,13 +4661,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540152</v>
+        <v>540129</v>
       </c>
       <c r="R34" t="n">
-        <v>7001464</v>
+        <v>7001452</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4726,7 +4701,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4778,7 +4753,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127164937</v>
+        <v>127161580</v>
       </c>
       <c r="B35" t="n">
         <v>80117</v>
@@ -4809,19 +4784,19 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539990</v>
+        <v>540152</v>
       </c>
       <c r="R35" t="n">
-        <v>7001113</v>
+        <v>7001464</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4858,7 +4833,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
+          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5032,38 +5007,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127163212</v>
+        <v>127164937</v>
       </c>
       <c r="B37" t="n">
-        <v>98465</v>
+        <v>80117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5072,13 +5047,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540253</v>
+        <v>539990</v>
       </c>
       <c r="R37" t="n">
-        <v>7001109</v>
+        <v>7001113</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5110,6 +5085,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5122,6 +5102,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5139,7 +5139,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127164835</v>
+        <v>127154714</v>
       </c>
       <c r="B38" t="n">
         <v>80117</v>
@@ -5175,17 +5175,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539992</v>
+        <v>539872</v>
       </c>
       <c r="R38" t="n">
-        <v>7001093</v>
+        <v>7001243</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+          <t>Lunglav på 3 gamla sälgar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5271,7 +5271,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153765</v>
+        <v>127164835</v>
       </c>
       <c r="B39" t="n">
         <v>80117</v>
@@ -5302,22 +5302,22 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539879</v>
+        <v>539992</v>
       </c>
       <c r="R39" t="n">
-        <v>7001196</v>
+        <v>7001093</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg.</t>
+          <t>Växer här på en grov gammal sälg (värdeträd).</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5403,10 +5403,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127164541</v>
+        <v>127153765</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5414,37 +5414,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540113</v>
+        <v>539879</v>
       </c>
       <c r="R40" t="n">
-        <v>7001087</v>
+        <v>7001196</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5476,6 +5481,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5492,22 +5502,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5525,10 +5535,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127154714</v>
+        <v>127164541</v>
       </c>
       <c r="B41" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5536,42 +5546,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539872</v>
+        <v>540113</v>
       </c>
       <c r="R41" t="n">
-        <v>7001243</v>
+        <v>7001087</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5603,11 +5608,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 gamla sälgar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5624,22 +5624,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127162701</v>
+        <v>127163976</v>
       </c>
       <c r="B44" t="n">
-        <v>98463</v>
+        <v>98465</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5946,13 +5946,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540246</v>
+        <v>540285</v>
       </c>
       <c r="R44" t="n">
-        <v>7001169</v>
+        <v>7001072</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5992,11 +5992,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6013,10 +6008,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127163976</v>
+        <v>127162701</v>
       </c>
       <c r="B45" t="n">
-        <v>98465</v>
+        <v>98463</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6024,21 +6019,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6053,13 +6048,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540285</v>
+        <v>540246</v>
       </c>
       <c r="R45" t="n">
-        <v>7001072</v>
+        <v>7001169</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6099,6 +6094,11 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6338,10 +6338,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127160120</v>
+        <v>127153809</v>
       </c>
       <c r="B48" t="n">
-        <v>98775</v>
+        <v>80153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6349,42 +6349,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219880</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540106</v>
+        <v>539890</v>
       </c>
       <c r="R48" t="n">
-        <v>7001289</v>
+        <v>7001195</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6428,6 +6428,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6445,52 +6465,38 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127153495</v>
+        <v>127152890</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>98463</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6499,10 +6505,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539858</v>
+        <v>539829</v>
       </c>
       <c r="R49" t="n">
-        <v>7001193</v>
+        <v>7001270</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6535,11 +6541,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6571,10 +6572,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127164902</v>
+        <v>127160120</v>
       </c>
       <c r="B50" t="n">
-        <v>98465</v>
+        <v>98775</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6582,42 +6583,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>219880</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539989</v>
+        <v>540106</v>
       </c>
       <c r="R50" t="n">
-        <v>7001089</v>
+        <v>7001289</v>
       </c>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6657,6 +6658,11 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6673,10 +6679,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127152890</v>
+        <v>127164902</v>
       </c>
       <c r="B51" t="n">
-        <v>98463</v>
+        <v>98465</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6684,42 +6690,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539829</v>
+        <v>539989</v>
       </c>
       <c r="R51" t="n">
-        <v>7001270</v>
+        <v>7001089</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6759,11 +6765,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6780,38 +6781,52 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127153809</v>
+        <v>127153495</v>
       </c>
       <c r="B52" t="n">
-        <v>80153</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6820,13 +6835,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539890</v>
+        <v>539858</v>
       </c>
       <c r="R52" t="n">
-        <v>7001195</v>
+        <v>7001193</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6858,6 +6873,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6870,26 +6890,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6907,55 +6907,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127159734</v>
+        <v>127162675</v>
       </c>
       <c r="B53" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540115</v>
+        <v>540237</v>
       </c>
       <c r="R53" t="n">
-        <v>7001344</v>
+        <v>7001188</v>
       </c>
       <c r="S53" t="n">
         <v>11</v>
@@ -7001,7 +6991,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7019,67 +7029,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127156042</v>
+        <v>127161775</v>
       </c>
       <c r="B54" t="n">
-        <v>98465</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539924</v>
+        <v>540092</v>
       </c>
       <c r="R54" t="n">
-        <v>7001238</v>
+        <v>7001443</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7122,7 +7113,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7140,10 +7151,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127162577</v>
+        <v>127164425</v>
       </c>
       <c r="B55" t="n">
-        <v>98465</v>
+        <v>98463</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7151,42 +7162,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540238</v>
+        <v>540128</v>
       </c>
       <c r="R55" t="n">
-        <v>7001222</v>
+        <v>7001058</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7226,6 +7237,11 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7242,10 +7258,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127160489</v>
+        <v>127159734</v>
       </c>
       <c r="B56" t="n">
-        <v>98465</v>
+        <v>98359</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7253,21 +7269,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7276,19 +7292,24 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540171</v>
+        <v>540115</v>
       </c>
       <c r="R56" t="n">
-        <v>7001276</v>
+        <v>7001344</v>
       </c>
       <c r="S56" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7331,7 +7352,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7349,10 +7370,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127164425</v>
+        <v>127156042</v>
       </c>
       <c r="B57" t="n">
-        <v>98463</v>
+        <v>98465</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7360,42 +7381,56 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540128</v>
+        <v>539924</v>
       </c>
       <c r="R57" t="n">
-        <v>7001058</v>
+        <v>7001238</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7438,7 +7473,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7456,62 +7491,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127163731</v>
+        <v>127162577</v>
       </c>
       <c r="B58" t="n">
-        <v>98442</v>
+        <v>98465</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540303</v>
+        <v>540238</v>
       </c>
       <c r="R58" t="n">
-        <v>7001059</v>
+        <v>7001222</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7551,11 +7577,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7572,48 +7593,62 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127162675</v>
+        <v>127163731</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540237</v>
+        <v>540303</v>
       </c>
       <c r="R59" t="n">
-        <v>7001188</v>
+        <v>7001059</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7657,26 +7692,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7694,48 +7709,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127161775</v>
+        <v>127160489</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>98465</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540092</v>
+        <v>540171</v>
       </c>
       <c r="R60" t="n">
-        <v>7001443</v>
+        <v>7001276</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7779,26 +7799,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8460,38 +8460,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127160736</v>
+        <v>127160440</v>
       </c>
       <c r="B66" t="n">
-        <v>98463</v>
+        <v>91779</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540193</v>
+        <v>540128</v>
       </c>
       <c r="R66" t="n">
-        <v>7001357</v>
+        <v>7001287</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8538,6 +8538,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8550,6 +8555,26 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8567,38 +8592,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127160440</v>
+        <v>127160736</v>
       </c>
       <c r="B67" t="n">
-        <v>91779</v>
+        <v>98463</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8607,13 +8632,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540128</v>
+        <v>540193</v>
       </c>
       <c r="R67" t="n">
-        <v>7001287</v>
+        <v>7001357</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8645,11 +8670,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8662,26 +8682,6 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8699,48 +8699,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127160774</v>
+        <v>127162146</v>
       </c>
       <c r="B68" t="n">
-        <v>80117</v>
+        <v>98463</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540203</v>
+        <v>540106</v>
       </c>
       <c r="R68" t="n">
-        <v>7001394</v>
+        <v>7001407</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8784,26 +8789,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8821,10 +8806,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127164741</v>
+        <v>127155980</v>
       </c>
       <c r="B69" t="n">
-        <v>98359</v>
+        <v>98465</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8832,42 +8817,56 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540004</v>
+        <v>539933</v>
       </c>
       <c r="R69" t="n">
-        <v>7001090</v>
+        <v>7001238</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8907,6 +8906,11 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8923,7 +8927,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127155980</v>
+        <v>127162549</v>
       </c>
       <c r="B70" t="n">
         <v>98465</v>
@@ -8951,39 +8955,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539933</v>
+        <v>540212</v>
       </c>
       <c r="R70" t="n">
-        <v>7001238</v>
+        <v>7001230</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9023,11 +9013,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9044,10 +9029,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127162549</v>
+        <v>127164741</v>
       </c>
       <c r="B71" t="n">
-        <v>98465</v>
+        <v>98359</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9055,21 +9040,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9080,17 +9065,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540212</v>
+        <v>540004</v>
       </c>
       <c r="R71" t="n">
-        <v>7001230</v>
+        <v>7001090</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9146,53 +9131,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127162146</v>
+        <v>127160774</v>
       </c>
       <c r="B72" t="n">
-        <v>98463</v>
+        <v>80117</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540106</v>
+        <v>540203</v>
       </c>
       <c r="R72" t="n">
-        <v>7001407</v>
+        <v>7001394</v>
       </c>
       <c r="S72" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9236,6 +9216,26 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9253,53 +9253,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127153185</v>
+        <v>127158202</v>
       </c>
       <c r="B73" t="n">
-        <v>98775</v>
+        <v>91343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>539835</v>
+        <v>540038</v>
       </c>
       <c r="R73" t="n">
-        <v>7001233</v>
+        <v>7001306</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9331,6 +9331,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikliga mängder död ved.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9343,6 +9348,16 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9360,10 +9375,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127158202</v>
+        <v>127159827</v>
       </c>
       <c r="B74" t="n">
-        <v>91343</v>
+        <v>80117</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9371,27 +9386,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9400,13 +9415,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540038</v>
+        <v>540122</v>
       </c>
       <c r="R74" t="n">
-        <v>7001306</v>
+        <v>7001326</v>
       </c>
       <c r="S74" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9438,11 +9453,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På fyndplatsen finns rikliga mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9457,14 +9467,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9482,53 +9502,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127159827</v>
+        <v>127153185</v>
       </c>
       <c r="B75" t="n">
-        <v>80117</v>
+        <v>98775</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540122</v>
+        <v>539835</v>
       </c>
       <c r="R75" t="n">
-        <v>7001326</v>
+        <v>7001233</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9572,26 +9592,6 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9731,7 +9731,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127163162</v>
+        <v>127162730</v>
       </c>
       <c r="B77" t="n">
         <v>98359</v>
@@ -9759,7 +9759,16 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9767,17 +9776,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540247</v>
+        <v>540258</v>
       </c>
       <c r="R77" t="n">
-        <v>7001094</v>
+        <v>7001179</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9817,6 +9826,11 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9833,7 +9847,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127162730</v>
+        <v>127163162</v>
       </c>
       <c r="B78" t="n">
         <v>98359</v>
@@ -9861,16 +9875,7 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9878,17 +9883,17 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540258</v>
+        <v>540247</v>
       </c>
       <c r="R78" t="n">
-        <v>7001179</v>
+        <v>7001094</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9928,11 +9933,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9949,67 +9949,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127154216</v>
+        <v>127161443</v>
       </c>
       <c r="B79" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539858</v>
+        <v>540137</v>
       </c>
       <c r="R79" t="n">
-        <v>7001227</v>
+        <v>7001432</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10043,7 +10024,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10058,6 +10039,26 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10207,7 +10208,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127161443</v>
+        <v>127160558</v>
       </c>
       <c r="B81" t="n">
         <v>79014</v>
@@ -10242,13 +10243,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540137</v>
+        <v>540205</v>
       </c>
       <c r="R81" t="n">
-        <v>7001432</v>
+        <v>7001321</v>
       </c>
       <c r="S81" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10278,11 +10279,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10334,10 +10330,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127160558</v>
+        <v>127157972</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10345,37 +10341,47 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540205</v>
+        <v>540038</v>
       </c>
       <c r="R82" t="n">
-        <v>7001321</v>
+        <v>7001245</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10407,6 +10413,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10433,12 +10444,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10456,38 +10467,47 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127157972</v>
+        <v>127154216</v>
       </c>
       <c r="B83" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -10497,17 +10517,17 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540038</v>
+        <v>539858</v>
       </c>
       <c r="R83" t="n">
-        <v>7001245</v>
+        <v>7001227</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10541,7 +10561,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
+          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10556,26 +10576,6 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10719,48 +10719,58 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127164354</v>
+        <v>127155804</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>98463</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540166</v>
+        <v>539886</v>
       </c>
       <c r="R85" t="n">
-        <v>7001045</v>
+        <v>7001291</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10800,31 +10810,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10841,10 +10826,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127160670</v>
+        <v>127163738</v>
       </c>
       <c r="B86" t="n">
-        <v>98465</v>
+        <v>98463</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10852,33 +10837,24 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -10886,17 +10862,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540195</v>
+        <v>540308</v>
       </c>
       <c r="R86" t="n">
-        <v>7001331</v>
+        <v>7001066</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10928,11 +10904,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10941,11 +10912,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10962,10 +10928,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127155804</v>
+        <v>127160670</v>
       </c>
       <c r="B87" t="n">
-        <v>98463</v>
+        <v>98465</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10973,44 +10939,48 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>539886</v>
+        <v>540195</v>
       </c>
       <c r="R87" t="n">
-        <v>7001291</v>
+        <v>7001331</v>
       </c>
       <c r="S87" t="n">
         <v>9</v>
@@ -11045,6 +11015,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -11053,6 +11028,11 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11069,53 +11049,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127163738</v>
+        <v>127164354</v>
       </c>
       <c r="B88" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540308</v>
+        <v>540166</v>
       </c>
       <c r="R88" t="n">
-        <v>7001066</v>
+        <v>7001045</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11155,6 +11130,31 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11307,10 +11307,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127157226</v>
+        <v>127157856</v>
       </c>
       <c r="B90" t="n">
-        <v>98465</v>
+        <v>98348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11318,26 +11318,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11350,6 +11350,7 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11361,13 +11362,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539976</v>
+        <v>539984</v>
       </c>
       <c r="R90" t="n">
-        <v>7001240</v>
+        <v>7001243</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11394,17 +11395,33 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11428,10 +11445,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127157856</v>
+        <v>127157226</v>
       </c>
       <c r="B91" t="n">
-        <v>98348</v>
+        <v>98465</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11439,26 +11456,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11471,7 +11488,6 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11483,13 +11499,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>539984</v>
+        <v>539976</v>
       </c>
       <c r="R91" t="n">
-        <v>7001243</v>
+        <v>7001240</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11516,33 +11532,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12069,67 +12069,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127160071</v>
+        <v>127160214</v>
       </c>
       <c r="B96" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540115</v>
+        <v>540081</v>
       </c>
       <c r="R96" t="n">
-        <v>7001289</v>
+        <v>7001299</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12161,11 +12142,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12178,6 +12154,26 @@
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12195,48 +12191,67 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127160214</v>
+        <v>127160071</v>
       </c>
       <c r="B97" t="n">
-        <v>80117</v>
+        <v>98442</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540081</v>
+        <v>540115</v>
       </c>
       <c r="R97" t="n">
-        <v>7001299</v>
+        <v>7001289</v>
       </c>
       <c r="S97" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12268,6 +12283,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12280,26 +12300,6 @@
       <c r="AH97" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127162017</v>
+        <v>127164710</v>
       </c>
       <c r="B2" t="n">
-        <v>80152</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -711,14 +711,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540111</v>
+        <v>540011</v>
       </c>
       <c r="R2" t="n">
-        <v>7001420</v>
+        <v>7001079</v>
       </c>
       <c r="S2" t="n">
         <v>16</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,58 +807,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127153536</v>
+        <v>127162017</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>80152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539859</v>
+        <v>540111</v>
       </c>
       <c r="R3" t="n">
-        <v>7001178</v>
+        <v>7001420</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,11 +885,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -902,6 +897,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127158784</v>
+        <v>127162096</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,32 +945,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540039</v>
+        <v>540104</v>
       </c>
       <c r="R4" t="n">
-        <v>7001341</v>
+        <v>7001431</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,24 +1007,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+          <t>Fertil lunglav på två sälgar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,38 +1066,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127162604</v>
+        <v>127160294</v>
       </c>
       <c r="B5" t="n">
-        <v>98359</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540240</v>
+        <v>540092</v>
       </c>
       <c r="R5" t="n">
-        <v>7001210</v>
+        <v>7001341</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1152,6 +1152,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1168,59 +1193,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127161646</v>
+        <v>127153536</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540139</v>
+        <v>539859</v>
       </c>
       <c r="R6" t="n">
-        <v>7001452</v>
+        <v>7001178</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1278,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,50 +1310,55 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127163443</v>
+        <v>127158784</v>
       </c>
       <c r="B7" t="n">
-        <v>98465</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540255</v>
+        <v>540039</v>
       </c>
       <c r="R7" t="n">
-        <v>7001070</v>
+        <v>7001341</v>
       </c>
       <c r="S7" t="n">
         <v>11</v>
@@ -1362,11 +1388,26 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1375,6 +1416,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1391,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127162418</v>
+        <v>127162604</v>
       </c>
       <c r="B8" t="n">
-        <v>98775</v>
+        <v>98359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,27 +1468,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1431,10 +1497,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540127</v>
+        <v>540240</v>
       </c>
       <c r="R8" t="n">
-        <v>7001264</v>
+        <v>7001210</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1477,11 +1543,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1498,53 +1559,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127164710</v>
+        <v>127161646</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540011</v>
+        <v>540139</v>
       </c>
       <c r="R9" t="n">
-        <v>7001079</v>
+        <v>7001452</v>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1578,7 +1648,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,26 +1663,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1630,53 +1680,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127162096</v>
+        <v>127163443</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>98465</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540104</v>
+        <v>540255</v>
       </c>
       <c r="R10" t="n">
-        <v>7001431</v>
+        <v>7001070</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,11 +1758,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på två sälgar.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1721,31 +1766,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1762,38 +1782,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127160294</v>
+        <v>127162418</v>
       </c>
       <c r="B11" t="n">
-        <v>80117</v>
+        <v>98775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1802,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540092</v>
+        <v>540127</v>
       </c>
       <c r="R11" t="n">
-        <v>7001341</v>
+        <v>7001264</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1852,26 +1872,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -4514,53 +4514,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127163212</v>
+        <v>127161738</v>
       </c>
       <c r="B33" t="n">
-        <v>98465</v>
+        <v>80117</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540253</v>
+        <v>540129</v>
       </c>
       <c r="R33" t="n">
-        <v>7001109</v>
+        <v>7001452</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4592,6 +4592,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4604,6 +4609,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4621,7 +4646,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127161738</v>
+        <v>127161580</v>
       </c>
       <c r="B34" t="n">
         <v>80117</v>
@@ -4652,7 +4677,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4661,13 +4686,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540129</v>
+        <v>540152</v>
       </c>
       <c r="R34" t="n">
-        <v>7001452</v>
+        <v>7001464</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4701,7 +4726,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4753,10 +4778,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127161580</v>
+        <v>127158834</v>
       </c>
       <c r="B35" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4764,39 +4789,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540152</v>
+        <v>540033</v>
       </c>
       <c r="R35" t="n">
-        <v>7001464</v>
+        <v>7001311</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4831,11 +4851,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4852,22 +4867,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4885,10 +4900,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127158834</v>
+        <v>127164937</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4896,34 +4911,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540033</v>
+        <v>539990</v>
       </c>
       <c r="R36" t="n">
-        <v>7001311</v>
+        <v>7001113</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4958,6 +4978,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4974,22 +4999,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5007,38 +5032,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127164937</v>
+        <v>127163212</v>
       </c>
       <c r="B37" t="n">
-        <v>80117</v>
+        <v>98465</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5047,13 +5072,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539990</v>
+        <v>540253</v>
       </c>
       <c r="R37" t="n">
-        <v>7001113</v>
+        <v>7001109</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5085,11 +5110,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5102,26 +5122,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5657,48 +5657,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127162532</v>
+        <v>127162701</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>98463</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540214</v>
+        <v>540246</v>
       </c>
       <c r="R42" t="n">
-        <v>7001228</v>
+        <v>7001169</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5742,26 +5747,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5779,53 +5764,62 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127164613</v>
+        <v>127158031</v>
       </c>
       <c r="B43" t="n">
-        <v>80117</v>
+        <v>98359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540079</v>
+        <v>540047</v>
       </c>
       <c r="R43" t="n">
-        <v>7001087</v>
+        <v>7001245</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5857,6 +5851,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Vid en bäck på en gammal väg.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5869,26 +5868,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5906,38 +5885,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127163976</v>
+        <v>127163137</v>
       </c>
       <c r="B44" t="n">
-        <v>98465</v>
+        <v>98442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5949,7 +5928,7 @@
         <v>540285</v>
       </c>
       <c r="R44" t="n">
-        <v>7001072</v>
+        <v>7001126</v>
       </c>
       <c r="S44" t="n">
         <v>7</v>
@@ -6008,10 +5987,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127162701</v>
+        <v>127163976</v>
       </c>
       <c r="B45" t="n">
-        <v>98463</v>
+        <v>98465</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6019,21 +5998,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6048,13 +6027,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540246</v>
+        <v>540285</v>
       </c>
       <c r="R45" t="n">
-        <v>7001169</v>
+        <v>7001072</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6094,11 +6073,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6115,62 +6089,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127158031</v>
+        <v>127162532</v>
       </c>
       <c r="B46" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540047</v>
+        <v>540214</v>
       </c>
       <c r="R46" t="n">
-        <v>7001245</v>
+        <v>7001228</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6202,11 +6162,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Vid en bäck på en gammal väg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6219,6 +6174,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6236,38 +6211,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127163137</v>
+        <v>127164613</v>
       </c>
       <c r="B47" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6276,13 +6251,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540285</v>
+        <v>540079</v>
       </c>
       <c r="R47" t="n">
-        <v>7001126</v>
+        <v>7001087</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6322,6 +6297,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -7938,10 +7938,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127155182</v>
+        <v>127153134</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7949,27 +7949,32 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7978,10 +7983,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539891</v>
+        <v>539827</v>
       </c>
       <c r="R62" t="n">
-        <v>7001292</v>
+        <v>7001225</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8018,7 +8023,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8047,12 +8052,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8070,67 +8075,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127158943</v>
+        <v>127155182</v>
       </c>
       <c r="B63" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540039</v>
+        <v>539891</v>
       </c>
       <c r="R63" t="n">
-        <v>7001317</v>
+        <v>7001292</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8164,7 +8155,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8179,6 +8170,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8196,38 +8207,47 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127153134</v>
+        <v>127158943</v>
       </c>
       <c r="B64" t="n">
-        <v>57654</v>
+        <v>98442</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -8237,17 +8257,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539827</v>
+        <v>540039</v>
       </c>
       <c r="R64" t="n">
-        <v>7001225</v>
+        <v>7001317</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8281,7 +8301,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8296,26 +8316,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8460,38 +8460,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127160440</v>
+        <v>127160736</v>
       </c>
       <c r="B66" t="n">
-        <v>91779</v>
+        <v>98463</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540128</v>
+        <v>540193</v>
       </c>
       <c r="R66" t="n">
-        <v>7001287</v>
+        <v>7001357</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8538,11 +8538,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8555,26 +8550,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8592,38 +8567,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127160736</v>
+        <v>127160440</v>
       </c>
       <c r="B67" t="n">
-        <v>98463</v>
+        <v>91779</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8632,13 +8607,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540193</v>
+        <v>540128</v>
       </c>
       <c r="R67" t="n">
-        <v>7001357</v>
+        <v>7001287</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8670,6 +8645,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8682,6 +8662,26 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8699,10 +8699,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127162146</v>
+        <v>127162549</v>
       </c>
       <c r="B68" t="n">
-        <v>98463</v>
+        <v>98465</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8710,27 +8710,27 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8739,13 +8739,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540106</v>
+        <v>540212</v>
       </c>
       <c r="R68" t="n">
-        <v>7001407</v>
+        <v>7001230</v>
       </c>
       <c r="S68" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8785,11 +8785,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8806,10 +8801,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127155980</v>
+        <v>127164741</v>
       </c>
       <c r="B69" t="n">
-        <v>98465</v>
+        <v>98359</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8817,56 +8812,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539933</v>
+        <v>540004</v>
       </c>
       <c r="R69" t="n">
-        <v>7001238</v>
+        <v>7001090</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8906,11 +8887,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8927,10 +8903,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127162549</v>
+        <v>127162146</v>
       </c>
       <c r="B70" t="n">
-        <v>98465</v>
+        <v>98463</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8938,27 +8914,27 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8967,13 +8943,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540212</v>
+        <v>540106</v>
       </c>
       <c r="R70" t="n">
-        <v>7001230</v>
+        <v>7001407</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9013,6 +8989,11 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9029,10 +9010,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127164741</v>
+        <v>127155980</v>
       </c>
       <c r="B71" t="n">
-        <v>98359</v>
+        <v>98465</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9040,42 +9021,56 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540004</v>
+        <v>539933</v>
       </c>
       <c r="R71" t="n">
-        <v>7001090</v>
+        <v>7001238</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9115,6 +9110,11 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9253,53 +9253,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127158202</v>
+        <v>127153185</v>
       </c>
       <c r="B73" t="n">
-        <v>91343</v>
+        <v>98775</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540038</v>
+        <v>539835</v>
       </c>
       <c r="R73" t="n">
-        <v>7001306</v>
+        <v>7001233</v>
       </c>
       <c r="S73" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9331,11 +9331,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På fyndplatsen finns rikliga mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9348,16 +9343,6 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9375,10 +9360,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127159827</v>
+        <v>127158202</v>
       </c>
       <c r="B74" t="n">
-        <v>80117</v>
+        <v>91343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9386,27 +9371,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9415,13 +9400,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540122</v>
+        <v>540038</v>
       </c>
       <c r="R74" t="n">
-        <v>7001326</v>
+        <v>7001306</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9453,6 +9438,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikliga mängder död ved.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9467,24 +9457,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9502,53 +9482,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127153185</v>
+        <v>127159827</v>
       </c>
       <c r="B75" t="n">
-        <v>98775</v>
+        <v>80117</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>539835</v>
+        <v>540122</v>
       </c>
       <c r="R75" t="n">
-        <v>7001233</v>
+        <v>7001326</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9592,6 +9572,26 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10719,58 +10719,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127155804</v>
+        <v>127164354</v>
       </c>
       <c r="B85" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>539886</v>
+        <v>540166</v>
       </c>
       <c r="R85" t="n">
-        <v>7001291</v>
+        <v>7001045</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10810,6 +10800,31 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10826,10 +10841,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127163738</v>
+        <v>127160670</v>
       </c>
       <c r="B86" t="n">
-        <v>98463</v>
+        <v>98465</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10837,24 +10852,33 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -10862,17 +10886,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540308</v>
+        <v>540195</v>
       </c>
       <c r="R86" t="n">
-        <v>7001066</v>
+        <v>7001331</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10904,6 +10928,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10912,6 +10941,11 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10928,10 +10962,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127160670</v>
+        <v>127155804</v>
       </c>
       <c r="B87" t="n">
-        <v>98465</v>
+        <v>98463</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10939,48 +10973,44 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540195</v>
+        <v>539886</v>
       </c>
       <c r="R87" t="n">
-        <v>7001331</v>
+        <v>7001291</v>
       </c>
       <c r="S87" t="n">
         <v>9</v>
@@ -11015,11 +11045,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -11028,11 +11053,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11049,48 +11069,53 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127164354</v>
+        <v>127163738</v>
       </c>
       <c r="B88" t="n">
-        <v>79014</v>
+        <v>98463</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540166</v>
+        <v>540308</v>
       </c>
       <c r="R88" t="n">
-        <v>7001045</v>
+        <v>7001066</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11130,31 +11155,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127164710</v>
+        <v>127153536</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540011</v>
+        <v>539859</v>
       </c>
       <c r="R2" t="n">
-        <v>7001079</v>
+        <v>7001178</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,26 +775,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,38 +792,43 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127162017</v>
+        <v>127158784</v>
       </c>
       <c r="B3" t="n">
-        <v>80152</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -847,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540111</v>
+        <v>540039</v>
       </c>
       <c r="R3" t="n">
-        <v>7001420</v>
+        <v>7001341</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,11 +870,26 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,22 +906,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,38 +939,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127162096</v>
+        <v>127161646</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,13 +988,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540104</v>
+        <v>540139</v>
       </c>
       <c r="R4" t="n">
-        <v>7001431</v>
+        <v>7001452</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,26 +1043,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1193,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153536</v>
+        <v>127164710</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,47 +1198,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539859</v>
+        <v>540011</v>
       </c>
       <c r="R6" t="n">
-        <v>7001178</v>
+        <v>7001079</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1278,7 +1267,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,6 +1282,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1310,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127158784</v>
+        <v>127162096</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,32 +1330,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1355,13 +1359,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540039</v>
+        <v>540104</v>
       </c>
       <c r="R7" t="n">
-        <v>7001341</v>
+        <v>7001431</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,24 +1392,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+          <t>Fertil lunglav på två sälgar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,22 +1418,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1457,10 +1451,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127162604</v>
+        <v>127162017</v>
       </c>
       <c r="B8" t="n">
-        <v>98359</v>
+        <v>80152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,27 +1462,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1497,13 +1491,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540240</v>
+        <v>540111</v>
       </c>
       <c r="R8" t="n">
-        <v>7001210</v>
+        <v>7001420</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1543,6 +1537,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1559,47 +1578,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127161646</v>
+        <v>127162604</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1608,13 +1618,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540139</v>
+        <v>540240</v>
       </c>
       <c r="R9" t="n">
-        <v>7001452</v>
+        <v>7001210</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1646,11 +1656,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1659,11 +1664,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1683,7 +1683,7 @@
         <v>127163443</v>
       </c>
       <c r="B10" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>127162418</v>
       </c>
       <c r="B11" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,47 +1889,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127155767</v>
+        <v>127160359</v>
       </c>
       <c r="B12" t="n">
-        <v>98359</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1939,17 +1934,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539895</v>
+        <v>540139</v>
       </c>
       <c r="R12" t="n">
-        <v>7001284</v>
+        <v>7001298</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1976,14 +1971,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,7 +2023,7 @@
         <v>127162375</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,38 +2141,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127154593</v>
+        <v>127155767</v>
       </c>
       <c r="B14" t="n">
-        <v>80117</v>
+        <v>98360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2176,13 +2195,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539874</v>
+        <v>539895</v>
       </c>
       <c r="R14" t="n">
-        <v>7001234</v>
+        <v>7001284</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2216,7 +2235,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,26 +2250,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2268,10 +2267,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127160359</v>
+        <v>127154593</v>
       </c>
       <c r="B15" t="n">
-        <v>57817</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2279,51 +2278,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540139</v>
+        <v>539874</v>
       </c>
       <c r="R15" t="n">
-        <v>7001298</v>
+        <v>7001234</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2350,24 +2340,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2382,6 +2362,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127161347</v>
+        <v>127160480</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2428,24 +2428,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540157</v>
+        <v>540188</v>
       </c>
       <c r="R16" t="n">
-        <v>7001411</v>
+        <v>7001269</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2475,11 +2470,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2531,7 +2521,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127160480</v>
+        <v>127161347</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2560,19 +2550,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540188</v>
+        <v>540157</v>
       </c>
       <c r="R17" t="n">
-        <v>7001269</v>
+        <v>7001411</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2602,6 +2597,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2803,7 +2803,7 @@
         <v>127160270</v>
       </c>
       <c r="B19" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2907,62 +2907,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127163626</v>
+        <v>127153666</v>
       </c>
       <c r="B20" t="n">
-        <v>98465</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540307</v>
+        <v>539888</v>
       </c>
       <c r="R20" t="n">
-        <v>7001050</v>
+        <v>7001166</v>
       </c>
       <c r="S20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2994,11 +2980,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3011,6 +2992,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3028,59 +3029,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127152848</v>
+        <v>127164774</v>
       </c>
       <c r="B21" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539832</v>
+        <v>540022</v>
       </c>
       <c r="R21" t="n">
-        <v>7001265</v>
+        <v>7001093</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3127,6 +3114,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3144,7 +3151,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127164774</v>
+        <v>127163769</v>
       </c>
       <c r="B22" t="n">
         <v>79014</v>
@@ -3179,13 +3186,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540022</v>
+        <v>540285</v>
       </c>
       <c r="R22" t="n">
-        <v>7001093</v>
+        <v>7001071</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3266,48 +3273,62 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127153666</v>
+        <v>127163626</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>98466</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539888</v>
+        <v>540307</v>
       </c>
       <c r="R23" t="n">
-        <v>7001166</v>
+        <v>7001050</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3339,6 +3360,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3351,26 +3377,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3388,48 +3394,62 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127163769</v>
+        <v>127152848</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540285</v>
+        <v>539832</v>
       </c>
       <c r="R24" t="n">
-        <v>7001071</v>
+        <v>7001265</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3473,26 +3493,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3513,7 +3513,7 @@
         <v>127158356</v>
       </c>
       <c r="B25" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127155997</v>
       </c>
       <c r="B26" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>127153897</v>
       </c>
       <c r="B32" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4778,10 +4778,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127158834</v>
+        <v>127164937</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4789,34 +4789,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540033</v>
+        <v>539990</v>
       </c>
       <c r="R35" t="n">
-        <v>7001311</v>
+        <v>7001113</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4851,6 +4856,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4867,22 +4877,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4900,10 +4910,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127164937</v>
+        <v>127158834</v>
       </c>
       <c r="B36" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4911,39 +4921,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539990</v>
+        <v>540033</v>
       </c>
       <c r="R36" t="n">
-        <v>7001113</v>
+        <v>7001311</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4978,11 +4983,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4999,22 +4999,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5035,7 +5035,7 @@
         <v>127163212</v>
       </c>
       <c r="B37" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127154714</v>
+        <v>127164541</v>
       </c>
       <c r="B38" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5150,42 +5150,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539872</v>
+        <v>540113</v>
       </c>
       <c r="R38" t="n">
-        <v>7001243</v>
+        <v>7001087</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5217,11 +5212,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 gamla sälgar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5238,22 +5228,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5271,7 +5261,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127164835</v>
+        <v>127154714</v>
       </c>
       <c r="B39" t="n">
         <v>80117</v>
@@ -5307,17 +5297,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539992</v>
+        <v>539872</v>
       </c>
       <c r="R39" t="n">
-        <v>7001093</v>
+        <v>7001243</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5351,7 +5341,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+          <t>Lunglav på 3 gamla sälgar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5403,7 +5393,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153765</v>
+        <v>127164835</v>
       </c>
       <c r="B40" t="n">
         <v>80117</v>
@@ -5434,22 +5424,22 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539879</v>
+        <v>539992</v>
       </c>
       <c r="R40" t="n">
-        <v>7001196</v>
+        <v>7001093</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5483,7 +5473,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg.</t>
+          <t>Växer här på en grov gammal sälg (värdeträd).</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5535,10 +5525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127164541</v>
+        <v>127153765</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5546,37 +5536,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540113</v>
+        <v>539879</v>
       </c>
       <c r="R41" t="n">
-        <v>7001087</v>
+        <v>7001196</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5608,6 +5603,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5624,22 +5624,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5657,53 +5657,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127162701</v>
+        <v>127162532</v>
       </c>
       <c r="B42" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540246</v>
+        <v>540214</v>
       </c>
       <c r="R42" t="n">
-        <v>7001169</v>
+        <v>7001228</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5747,6 +5742,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5764,62 +5779,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127158031</v>
+        <v>127164613</v>
       </c>
       <c r="B43" t="n">
-        <v>98359</v>
+        <v>80117</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540047</v>
+        <v>540079</v>
       </c>
       <c r="R43" t="n">
-        <v>7001245</v>
+        <v>7001087</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5851,11 +5857,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Vid en bäck på en gammal väg.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5868,6 +5869,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5888,7 +5909,7 @@
         <v>127163137</v>
       </c>
       <c r="B44" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5987,10 +6008,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127163976</v>
+        <v>127158031</v>
       </c>
       <c r="B45" t="n">
-        <v>98465</v>
+        <v>98360</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5998,24 +6019,33 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -6023,17 +6053,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540285</v>
+        <v>540047</v>
       </c>
       <c r="R45" t="n">
-        <v>7001072</v>
+        <v>7001245</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6065,6 +6095,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Vid en bäck på en gammal väg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6073,6 +6108,11 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6089,48 +6129,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127162532</v>
+        <v>127163976</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>98466</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540214</v>
+        <v>540285</v>
       </c>
       <c r="R46" t="n">
-        <v>7001228</v>
+        <v>7001072</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6170,31 +6215,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6211,38 +6231,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127164613</v>
+        <v>127162701</v>
       </c>
       <c r="B47" t="n">
-        <v>80117</v>
+        <v>98464</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6251,13 +6271,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540079</v>
+        <v>540246</v>
       </c>
       <c r="R47" t="n">
-        <v>7001087</v>
+        <v>7001169</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6301,26 +6321,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6465,38 +6465,52 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127152890</v>
+        <v>127153495</v>
       </c>
       <c r="B49" t="n">
-        <v>98463</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6505,10 +6519,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539829</v>
+        <v>539858</v>
       </c>
       <c r="R49" t="n">
-        <v>7001270</v>
+        <v>7001193</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6541,6 +6555,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6575,7 +6594,7 @@
         <v>127160120</v>
       </c>
       <c r="B50" t="n">
-        <v>98775</v>
+        <v>98776</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6682,7 +6701,7 @@
         <v>127164902</v>
       </c>
       <c r="B51" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6781,52 +6800,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127153495</v>
+        <v>127152890</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>98464</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6835,10 +6840,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539858</v>
+        <v>539829</v>
       </c>
       <c r="R52" t="n">
-        <v>7001193</v>
+        <v>7001270</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6871,11 +6876,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7151,10 +7151,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127164425</v>
+        <v>127159734</v>
       </c>
       <c r="B55" t="n">
-        <v>98463</v>
+        <v>98360</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7162,39 +7162,44 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540128</v>
+        <v>540115</v>
       </c>
       <c r="R55" t="n">
-        <v>7001058</v>
+        <v>7001344</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -7240,7 +7245,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7258,10 +7263,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127159734</v>
+        <v>127156042</v>
       </c>
       <c r="B56" t="n">
-        <v>98359</v>
+        <v>98466</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7269,24 +7274,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7299,17 +7313,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540115</v>
+        <v>539924</v>
       </c>
       <c r="R56" t="n">
-        <v>7001344</v>
+        <v>7001238</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7370,10 +7384,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127156042</v>
+        <v>127162577</v>
       </c>
       <c r="B57" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7398,39 +7412,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539924</v>
+        <v>540238</v>
       </c>
       <c r="R57" t="n">
-        <v>7001238</v>
+        <v>7001222</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7470,11 +7470,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7491,10 +7486,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127162577</v>
+        <v>127160489</v>
       </c>
       <c r="B58" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7531,13 +7526,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540238</v>
+        <v>540171</v>
       </c>
       <c r="R58" t="n">
-        <v>7001222</v>
+        <v>7001276</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7577,6 +7572,11 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7593,47 +7593,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127163731</v>
+        <v>127164425</v>
       </c>
       <c r="B59" t="n">
-        <v>98442</v>
+        <v>98464</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7642,13 +7633,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540303</v>
+        <v>540128</v>
       </c>
       <c r="R59" t="n">
-        <v>7001059</v>
+        <v>7001058</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7709,53 +7700,62 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127160489</v>
+        <v>127163731</v>
       </c>
       <c r="B60" t="n">
-        <v>98465</v>
+        <v>98443</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540171</v>
+        <v>540303</v>
       </c>
       <c r="R60" t="n">
-        <v>7001276</v>
+        <v>7001059</v>
       </c>
       <c r="S60" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7816,10 +7816,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127156085</v>
+        <v>127153134</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7827,34 +7827,44 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539948</v>
+        <v>539827</v>
       </c>
       <c r="R61" t="n">
-        <v>7001204</v>
+        <v>7001225</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7889,6 +7899,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7915,12 +7930,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7938,38 +7953,47 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127153134</v>
+        <v>127158943</v>
       </c>
       <c r="B62" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -7979,17 +8003,17 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539827</v>
+        <v>540039</v>
       </c>
       <c r="R62" t="n">
-        <v>7001225</v>
+        <v>7001317</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8023,7 +8047,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8038,26 +8062,6 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8075,7 +8079,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127155182</v>
+        <v>127156085</v>
       </c>
       <c r="B63" t="n">
         <v>79014</v>
@@ -8104,21 +8108,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539891</v>
+        <v>539948</v>
       </c>
       <c r="R63" t="n">
-        <v>7001292</v>
+        <v>7001204</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8151,11 +8150,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8207,67 +8201,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127158943</v>
+        <v>127155182</v>
       </c>
       <c r="B64" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540039</v>
+        <v>539891</v>
       </c>
       <c r="R64" t="n">
-        <v>7001317</v>
+        <v>7001292</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8301,7 +8281,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8316,6 +8296,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8336,7 +8336,7 @@
         <v>127163069</v>
       </c>
       <c r="B65" t="n">
-        <v>91321</v>
+        <v>91322</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8460,38 +8460,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127160736</v>
+        <v>127160440</v>
       </c>
       <c r="B66" t="n">
-        <v>98463</v>
+        <v>91780</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540193</v>
+        <v>540128</v>
       </c>
       <c r="R66" t="n">
-        <v>7001357</v>
+        <v>7001287</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8538,6 +8538,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8550,6 +8555,26 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8567,38 +8592,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127160440</v>
+        <v>127160736</v>
       </c>
       <c r="B67" t="n">
-        <v>91779</v>
+        <v>98464</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8607,13 +8632,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540128</v>
+        <v>540193</v>
       </c>
       <c r="R67" t="n">
-        <v>7001287</v>
+        <v>7001357</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8645,11 +8670,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8662,26 +8682,6 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8699,53 +8699,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127162549</v>
+        <v>127160774</v>
       </c>
       <c r="B68" t="n">
-        <v>98465</v>
+        <v>80117</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540212</v>
+        <v>540203</v>
       </c>
       <c r="R68" t="n">
-        <v>7001230</v>
+        <v>7001394</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8785,6 +8780,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Salix caprea</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8801,10 +8821,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127164741</v>
+        <v>127155980</v>
       </c>
       <c r="B69" t="n">
-        <v>98359</v>
+        <v>98466</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8812,42 +8832,56 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540004</v>
+        <v>539933</v>
       </c>
       <c r="R69" t="n">
-        <v>7001090</v>
+        <v>7001238</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8887,6 +8921,11 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8903,10 +8942,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127162146</v>
+        <v>127162549</v>
       </c>
       <c r="B70" t="n">
-        <v>98463</v>
+        <v>98466</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8914,27 +8953,27 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8943,13 +8982,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540106</v>
+        <v>540212</v>
       </c>
       <c r="R70" t="n">
-        <v>7001407</v>
+        <v>7001230</v>
       </c>
       <c r="S70" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8989,11 +9028,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9010,10 +9044,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127155980</v>
+        <v>127164741</v>
       </c>
       <c r="B71" t="n">
-        <v>98465</v>
+        <v>98360</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9021,56 +9055,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>539933</v>
+        <v>540004</v>
       </c>
       <c r="R71" t="n">
-        <v>7001238</v>
+        <v>7001090</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9110,11 +9130,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9131,48 +9146,53 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127160774</v>
+        <v>127162146</v>
       </c>
       <c r="B72" t="n">
-        <v>80117</v>
+        <v>98464</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540203</v>
+        <v>540106</v>
       </c>
       <c r="R72" t="n">
-        <v>7001394</v>
+        <v>7001407</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9216,26 +9236,6 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -9253,53 +9253,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127153185</v>
+        <v>127159827</v>
       </c>
       <c r="B73" t="n">
-        <v>98775</v>
+        <v>80117</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>539835</v>
+        <v>540122</v>
       </c>
       <c r="R73" t="n">
-        <v>7001233</v>
+        <v>7001326</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9343,6 +9343,26 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9363,7 +9383,7 @@
         <v>127158202</v>
       </c>
       <c r="B74" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9482,53 +9502,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127159827</v>
+        <v>127153185</v>
       </c>
       <c r="B75" t="n">
-        <v>80117</v>
+        <v>98776</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540122</v>
+        <v>539835</v>
       </c>
       <c r="R75" t="n">
-        <v>7001326</v>
+        <v>7001233</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9572,26 +9592,6 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9609,48 +9609,62 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127154622</v>
+        <v>127162730</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>539897</v>
+        <v>540258</v>
       </c>
       <c r="R76" t="n">
-        <v>7001240</v>
+        <v>7001179</v>
       </c>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9694,26 +9708,6 @@
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9731,62 +9725,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127162730</v>
+        <v>127154622</v>
       </c>
       <c r="B77" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540258</v>
+        <v>539897</v>
       </c>
       <c r="R77" t="n">
-        <v>7001179</v>
+        <v>7001240</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9830,6 +9810,26 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9850,7 +9850,7 @@
         <v>127163162</v>
       </c>
       <c r="B78" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9949,48 +9949,67 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127161443</v>
+        <v>127155895</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540137</v>
+        <v>539912</v>
       </c>
       <c r="R79" t="n">
-        <v>7001432</v>
+        <v>7001269</v>
       </c>
       <c r="S79" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10024,7 +10043,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
+          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10039,26 +10058,6 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10208,7 +10207,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127160558</v>
+        <v>127161443</v>
       </c>
       <c r="B81" t="n">
         <v>79014</v>
@@ -10243,13 +10242,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540205</v>
+        <v>540137</v>
       </c>
       <c r="R81" t="n">
-        <v>7001321</v>
+        <v>7001432</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10279,6 +10278,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10330,10 +10334,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127157972</v>
+        <v>127160558</v>
       </c>
       <c r="B82" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10341,47 +10345,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540038</v>
+        <v>540205</v>
       </c>
       <c r="R82" t="n">
-        <v>7001245</v>
+        <v>7001321</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10413,11 +10407,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10444,12 +10433,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10467,47 +10456,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127154216</v>
+        <v>127157972</v>
       </c>
       <c r="B83" t="n">
-        <v>98442</v>
+        <v>57654</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -10517,17 +10497,17 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>539858</v>
+        <v>540038</v>
       </c>
       <c r="R83" t="n">
-        <v>7001227</v>
+        <v>7001245</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10561,7 +10541,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
+          <t>Färska och äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10576,6 +10556,26 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10593,37 +10593,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127155895</v>
+        <v>127154216</v>
       </c>
       <c r="B84" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -10647,10 +10647,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>539912</v>
+        <v>539858</v>
       </c>
       <c r="R84" t="n">
-        <v>7001269</v>
+        <v>7001227</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
+          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10719,48 +10719,62 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127164354</v>
+        <v>127160670</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>98466</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540166</v>
+        <v>540195</v>
       </c>
       <c r="R85" t="n">
-        <v>7001045</v>
+        <v>7001331</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10792,6 +10806,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10804,26 +10823,6 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10841,10 +10840,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127160670</v>
+        <v>127155804</v>
       </c>
       <c r="B86" t="n">
-        <v>98465</v>
+        <v>98464</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10852,48 +10851,44 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540195</v>
+        <v>539886</v>
       </c>
       <c r="R86" t="n">
-        <v>7001331</v>
+        <v>7001291</v>
       </c>
       <c r="S86" t="n">
         <v>9</v>
@@ -10928,11 +10923,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10941,11 +10931,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10962,10 +10947,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127155804</v>
+        <v>127163738</v>
       </c>
       <c r="B87" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10993,27 +10978,22 @@
       <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>539886</v>
+        <v>540308</v>
       </c>
       <c r="R87" t="n">
-        <v>7001291</v>
+        <v>7001066</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11069,53 +11049,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127163738</v>
+        <v>127164354</v>
       </c>
       <c r="B88" t="n">
-        <v>98463</v>
+        <v>79014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540308</v>
+        <v>540166</v>
       </c>
       <c r="R88" t="n">
-        <v>7001066</v>
+        <v>7001045</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11155,6 +11130,31 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11174,7 +11174,7 @@
         <v>127159714</v>
       </c>
       <c r="B89" t="n">
-        <v>98440</v>
+        <v>98441</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>127157856</v>
       </c>
       <c r="B90" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>127157226</v>
       </c>
       <c r="B91" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>127159972</v>
       </c>
       <c r="B92" t="n">
-        <v>98440</v>
+        <v>98441</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>127155729</v>
       </c>
       <c r="B93" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>127174668</v>
       </c>
       <c r="B94" t="n">
-        <v>90870</v>
+        <v>90871</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>127157050</v>
       </c>
       <c r="B95" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>127160071</v>
       </c>
       <c r="B97" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>127155870</v>
       </c>
       <c r="B98" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>127164256</v>
       </c>
       <c r="B99" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>127157299</v>
       </c>
       <c r="B100" t="n">
-        <v>98348</v>
+        <v>98349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>127162786</v>
       </c>
       <c r="B101" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127153536</v>
+        <v>127162096</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,47 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539859</v>
+        <v>540104</v>
       </c>
       <c r="R2" t="n">
-        <v>7001178</v>
+        <v>7001431</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
+          <t>Fertil lunglav på två sälgar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +770,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,43 +807,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127158784</v>
+        <v>127162017</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>80152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540039</v>
+        <v>540111</v>
       </c>
       <c r="R3" t="n">
-        <v>7001341</v>
+        <v>7001420</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,26 +880,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -906,22 +901,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,47 +934,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127161646</v>
+        <v>127160294</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -988,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540139</v>
+        <v>540092</v>
       </c>
       <c r="R4" t="n">
-        <v>7001452</v>
+        <v>7001341</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,11 +1012,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1043,6 +1024,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,7 +1061,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127160294</v>
+        <v>127164710</v>
       </c>
       <c r="B5" t="n">
         <v>80117</v>
@@ -1096,17 +1097,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540092</v>
+        <v>540011</v>
       </c>
       <c r="R5" t="n">
-        <v>7001341</v>
+        <v>7001079</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,6 +1139,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1164,12 +1170,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1193,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127164710</v>
+        <v>127153536</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,42 +1204,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540011</v>
+        <v>539859</v>
       </c>
       <c r="R6" t="n">
-        <v>7001079</v>
+        <v>7001178</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,7 +1278,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,26 +1293,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,10 +1310,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127162096</v>
+        <v>127158784</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,27 +1321,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1359,13 +1355,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540104</v>
+        <v>540039</v>
       </c>
       <c r="R7" t="n">
-        <v>7001431</v>
+        <v>7001341</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1392,14 +1388,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,22 +1424,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1451,38 +1457,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127162017</v>
+        <v>127161646</v>
       </c>
       <c r="B8" t="n">
-        <v>80152</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1491,13 +1506,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540111</v>
+        <v>540139</v>
       </c>
       <c r="R8" t="n">
-        <v>7001420</v>
+        <v>7001452</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1529,6 +1544,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1541,26 +1561,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2020,62 +2020,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127162375</v>
+        <v>127154593</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540115</v>
+        <v>539874</v>
       </c>
       <c r="R13" t="n">
-        <v>7001309</v>
+        <v>7001234</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2109,7 +2100,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,6 +2115,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2141,37 +2152,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127155767</v>
+        <v>127162375</v>
       </c>
       <c r="B14" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2181,27 +2192,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539895</v>
+        <v>540115</v>
       </c>
       <c r="R14" t="n">
-        <v>7001284</v>
+        <v>7001309</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2235,7 +2241,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2267,38 +2273,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127154593</v>
+        <v>127155767</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>98360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2307,13 +2327,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539874</v>
+        <v>539895</v>
       </c>
       <c r="R15" t="n">
-        <v>7001234</v>
+        <v>7001284</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2347,7 +2367,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2362,26 +2382,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127158356</v>
+        <v>127163495</v>
       </c>
       <c r="B25" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3521,42 +3521,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540032</v>
+        <v>540258</v>
       </c>
       <c r="R25" t="n">
-        <v>7001287</v>
+        <v>7001065</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3614,12 +3609,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3637,64 +3632,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127155997</v>
+        <v>127158356</v>
       </c>
       <c r="B26" t="n">
-        <v>98360</v>
+        <v>91326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539924</v>
+        <v>540032</v>
       </c>
       <c r="R26" t="n">
-        <v>7001238</v>
+        <v>7001287</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3740,7 +3721,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3758,48 +3759,67 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127163495</v>
+        <v>127155997</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540258</v>
+        <v>539924</v>
       </c>
       <c r="R27" t="n">
-        <v>7001065</v>
+        <v>7001238</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3842,27 +3862,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3880,48 +3880,67 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153018</v>
+        <v>127153897</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539829</v>
+        <v>539873</v>
       </c>
       <c r="R28" t="n">
-        <v>7001270</v>
+        <v>7001197</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3953,6 +3972,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3965,26 +3989,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4002,53 +4006,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153641</v>
+        <v>127153018</v>
       </c>
       <c r="B29" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539864</v>
+        <v>539829</v>
       </c>
       <c r="R29" t="n">
-        <v>7001177</v>
+        <v>7001270</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4096,22 +4095,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4129,38 +4128,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127153581</v>
+        <v>127153641</v>
       </c>
       <c r="B30" t="n">
-        <v>80117</v>
+        <v>80146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4169,13 +4168,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539872</v>
+        <v>539864</v>
       </c>
       <c r="R30" t="n">
-        <v>7001176</v>
+        <v>7001177</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4256,7 +4255,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127160821</v>
+        <v>127153581</v>
       </c>
       <c r="B31" t="n">
         <v>80117</v>
@@ -4292,14 +4291,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540188</v>
+        <v>539872</v>
       </c>
       <c r="R31" t="n">
-        <v>7001373</v>
+        <v>7001176</v>
       </c>
       <c r="S31" t="n">
         <v>12</v>
@@ -4332,11 +4331,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en upplyft liggande levande sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4388,64 +4382,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127153897</v>
+        <v>127160821</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539873</v>
+        <v>540188</v>
       </c>
       <c r="R32" t="n">
-        <v>7001197</v>
+        <v>7001373</v>
       </c>
       <c r="S32" t="n">
         <v>12</v>
@@ -4482,7 +4462,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
+          <t>På en upplyft liggande levande sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4497,6 +4477,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -6338,38 +6338,52 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127153809</v>
+        <v>127153495</v>
       </c>
       <c r="B48" t="n">
-        <v>80153</v>
+        <v>98443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6378,13 +6392,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539890</v>
+        <v>539858</v>
       </c>
       <c r="R48" t="n">
-        <v>7001195</v>
+        <v>7001193</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6416,6 +6430,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6428,26 +6447,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6465,67 +6464,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127153495</v>
+        <v>127160120</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>98776</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539858</v>
+        <v>540106</v>
       </c>
       <c r="R49" t="n">
-        <v>7001193</v>
+        <v>7001289</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6555,11 +6540,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6591,10 +6571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127160120</v>
+        <v>127164902</v>
       </c>
       <c r="B50" t="n">
-        <v>98776</v>
+        <v>98466</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6602,42 +6582,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540106</v>
+        <v>539989</v>
       </c>
       <c r="R50" t="n">
-        <v>7001289</v>
+        <v>7001089</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6677,11 +6657,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6698,10 +6673,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127164902</v>
+        <v>127152890</v>
       </c>
       <c r="B51" t="n">
-        <v>98466</v>
+        <v>98464</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6709,42 +6684,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539989</v>
+        <v>539829</v>
       </c>
       <c r="R51" t="n">
-        <v>7001089</v>
+        <v>7001270</v>
       </c>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6784,6 +6759,11 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6800,10 +6780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127152890</v>
+        <v>127153809</v>
       </c>
       <c r="B52" t="n">
-        <v>98464</v>
+        <v>80153</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6811,27 +6791,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6840,13 +6820,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539829</v>
+        <v>539890</v>
       </c>
       <c r="R52" t="n">
-        <v>7001270</v>
+        <v>7001195</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6890,6 +6870,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7151,58 +7151,62 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127159734</v>
+        <v>127163731</v>
       </c>
       <c r="B55" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540115</v>
+        <v>540303</v>
       </c>
       <c r="R55" t="n">
-        <v>7001344</v>
+        <v>7001059</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7245,7 +7249,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7263,10 +7267,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127156042</v>
+        <v>127159734</v>
       </c>
       <c r="B56" t="n">
-        <v>98466</v>
+        <v>98360</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7274,33 +7278,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7313,17 +7308,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539924</v>
+        <v>540115</v>
       </c>
       <c r="R56" t="n">
-        <v>7001238</v>
+        <v>7001344</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7384,7 +7379,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127162577</v>
+        <v>127156042</v>
       </c>
       <c r="B57" t="n">
         <v>98466</v>
@@ -7412,25 +7407,39 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540238</v>
+        <v>539924</v>
       </c>
       <c r="R57" t="n">
-        <v>7001222</v>
+        <v>7001238</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7470,6 +7479,11 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7486,7 +7500,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127160489</v>
+        <v>127162577</v>
       </c>
       <c r="B58" t="n">
         <v>98466</v>
@@ -7526,13 +7540,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540171</v>
+        <v>540238</v>
       </c>
       <c r="R58" t="n">
-        <v>7001276</v>
+        <v>7001222</v>
       </c>
       <c r="S58" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7572,11 +7586,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7593,10 +7602,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127164425</v>
+        <v>127160489</v>
       </c>
       <c r="B59" t="n">
-        <v>98464</v>
+        <v>98466</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7604,42 +7613,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540128</v>
+        <v>540171</v>
       </c>
       <c r="R59" t="n">
-        <v>7001058</v>
+        <v>7001276</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7700,47 +7709,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127163731</v>
+        <v>127164425</v>
       </c>
       <c r="B60" t="n">
-        <v>98443</v>
+        <v>98464</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7749,13 +7749,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540303</v>
+        <v>540128</v>
       </c>
       <c r="R60" t="n">
-        <v>7001059</v>
+        <v>7001058</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7816,38 +7816,47 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127153134</v>
+        <v>127158943</v>
       </c>
       <c r="B61" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7857,17 +7866,17 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539827</v>
+        <v>540039</v>
       </c>
       <c r="R61" t="n">
-        <v>7001225</v>
+        <v>7001317</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7901,7 +7910,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7916,26 +7925,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7953,67 +7942,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127158943</v>
+        <v>127156085</v>
       </c>
       <c r="B62" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540039</v>
+        <v>539948</v>
       </c>
       <c r="R62" t="n">
-        <v>7001317</v>
+        <v>7001204</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8045,11 +8015,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8062,6 +8027,26 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8079,7 +8064,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127156085</v>
+        <v>127155182</v>
       </c>
       <c r="B63" t="n">
         <v>79014</v>
@@ -8108,16 +8093,21 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539948</v>
+        <v>539891</v>
       </c>
       <c r="R63" t="n">
-        <v>7001204</v>
+        <v>7001292</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8150,6 +8140,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8201,10 +8196,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127155182</v>
+        <v>127153134</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8212,27 +8207,32 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539891</v>
+        <v>539827</v>
       </c>
       <c r="R64" t="n">
-        <v>7001292</v>
+        <v>7001225</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127162096</v>
+        <v>127153536</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540104</v>
+        <v>539859</v>
       </c>
       <c r="R2" t="n">
-        <v>7001431</v>
+        <v>7001178</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,26 +775,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,32 +792,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127162017</v>
+        <v>127164710</v>
       </c>
       <c r="B3" t="n">
-        <v>80152</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -843,14 +828,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540111</v>
+        <v>540011</v>
       </c>
       <c r="R3" t="n">
-        <v>7001420</v>
+        <v>7001079</v>
       </c>
       <c r="S3" t="n">
         <v>16</v>
@@ -883,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +924,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127160294</v>
+        <v>127162096</v>
       </c>
       <c r="B4" t="n">
         <v>80117</v>
@@ -965,7 +955,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540092</v>
+        <v>540104</v>
       </c>
       <c r="R4" t="n">
-        <v>7001341</v>
+        <v>7001431</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,6 +1002,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på två sälgar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1038,12 +1033,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,7 +1056,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127164710</v>
+        <v>127160294</v>
       </c>
       <c r="B5" t="n">
         <v>80117</v>
@@ -1097,17 +1092,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540011</v>
+        <v>540092</v>
       </c>
       <c r="R5" t="n">
-        <v>7001079</v>
+        <v>7001341</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,11 +1134,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1170,12 +1160,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1193,58 +1183,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127153536</v>
+        <v>127162017</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>80152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539859</v>
+        <v>540111</v>
       </c>
       <c r="R6" t="n">
-        <v>7001178</v>
+        <v>7001420</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1276,11 +1261,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1293,6 +1273,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1457,47 +1457,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127161646</v>
+        <v>127162604</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1506,13 +1497,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540139</v>
+        <v>540240</v>
       </c>
       <c r="R8" t="n">
-        <v>7001452</v>
+        <v>7001210</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1544,11 +1535,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1557,11 +1543,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1578,10 +1559,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127162604</v>
+        <v>127163443</v>
       </c>
       <c r="B9" t="n">
-        <v>98360</v>
+        <v>98466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,21 +1570,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1614,17 +1595,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540240</v>
+        <v>540255</v>
       </c>
       <c r="R9" t="n">
-        <v>7001210</v>
+        <v>7001070</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1680,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127163443</v>
+        <v>127162418</v>
       </c>
       <c r="B10" t="n">
-        <v>98466</v>
+        <v>98776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,42 +1672,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>219880</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540255</v>
+        <v>540127</v>
       </c>
       <c r="R10" t="n">
-        <v>7001070</v>
+        <v>7001264</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1766,6 +1747,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1782,38 +1768,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127162418</v>
+        <v>127161646</v>
       </c>
       <c r="B11" t="n">
-        <v>98776</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1822,13 +1817,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540127</v>
+        <v>540139</v>
       </c>
       <c r="R11" t="n">
-        <v>7001264</v>
+        <v>7001452</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1858,6 +1853,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,10 +1889,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127160359</v>
+        <v>127154593</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,51 +1900,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540139</v>
+        <v>539874</v>
       </c>
       <c r="R12" t="n">
-        <v>7001298</v>
+        <v>7001234</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1971,24 +1962,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2003,6 +1984,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2020,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127154593</v>
+        <v>127160359</v>
       </c>
       <c r="B13" t="n">
-        <v>80117</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,42 +2032,51 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539874</v>
+        <v>540139</v>
       </c>
       <c r="R13" t="n">
-        <v>7001234</v>
+        <v>7001298</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2093,14 +2103,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
+          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2115,26 +2135,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2152,37 +2152,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127162375</v>
+        <v>127155767</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2192,22 +2192,27 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540115</v>
+        <v>539895</v>
       </c>
       <c r="R14" t="n">
-        <v>7001309</v>
+        <v>7001284</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2241,7 +2246,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2273,37 +2278,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155767</v>
+        <v>127162375</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2313,27 +2318,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539895</v>
+        <v>540115</v>
       </c>
       <c r="R15" t="n">
-        <v>7001284</v>
+        <v>7001309</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2399,7 +2399,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127160480</v>
+        <v>127161347</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2428,19 +2428,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540188</v>
+        <v>540157</v>
       </c>
       <c r="R16" t="n">
-        <v>7001269</v>
+        <v>7001411</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2470,6 +2475,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2521,7 +2531,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127161347</v>
+        <v>127160480</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2550,24 +2560,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540157</v>
+        <v>540188</v>
       </c>
       <c r="R17" t="n">
-        <v>7001411</v>
+        <v>7001269</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2597,11 +2602,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2800,50 +2800,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127160270</v>
+        <v>127164774</v>
       </c>
       <c r="B19" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540095</v>
+        <v>540022</v>
       </c>
       <c r="R19" t="n">
-        <v>7001315</v>
+        <v>7001093</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2890,6 +2885,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3029,7 +3044,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127164774</v>
+        <v>127163769</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -3064,13 +3079,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540022</v>
+        <v>540285</v>
       </c>
       <c r="R21" t="n">
-        <v>7001093</v>
+        <v>7001071</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3151,48 +3166,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127163769</v>
+        <v>127160270</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540285</v>
+        <v>540095</v>
       </c>
       <c r="R22" t="n">
-        <v>7001071</v>
+        <v>7001315</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3236,26 +3256,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127163495</v>
+        <v>127158356</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3521,37 +3521,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540258</v>
+        <v>540032</v>
       </c>
       <c r="R25" t="n">
-        <v>7001065</v>
+        <v>7001287</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3609,12 +3614,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3632,10 +3637,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127158356</v>
+        <v>127163495</v>
       </c>
       <c r="B26" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3643,42 +3648,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540032</v>
+        <v>540258</v>
       </c>
       <c r="R26" t="n">
-        <v>7001287</v>
+        <v>7001065</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3736,12 +3736,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3880,67 +3880,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153897</v>
+        <v>127153018</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539873</v>
+        <v>539829</v>
       </c>
       <c r="R28" t="n">
-        <v>7001197</v>
+        <v>7001270</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3972,11 +3953,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3989,6 +3965,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4006,48 +4002,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153018</v>
+        <v>127153641</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539829</v>
+        <v>539864</v>
       </c>
       <c r="R29" t="n">
-        <v>7001270</v>
+        <v>7001177</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4095,22 +4096,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4128,38 +4129,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127153641</v>
+        <v>127153581</v>
       </c>
       <c r="B30" t="n">
-        <v>80146</v>
+        <v>80117</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4168,13 +4169,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539864</v>
+        <v>539872</v>
       </c>
       <c r="R30" t="n">
-        <v>7001177</v>
+        <v>7001176</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4255,7 +4256,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127153581</v>
+        <v>127160821</v>
       </c>
       <c r="B31" t="n">
         <v>80117</v>
@@ -4291,14 +4292,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539872</v>
+        <v>540188</v>
       </c>
       <c r="R31" t="n">
-        <v>7001176</v>
+        <v>7001373</v>
       </c>
       <c r="S31" t="n">
         <v>12</v>
@@ -4331,6 +4332,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en upplyft liggande levande sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4382,50 +4388,64 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127160821</v>
+        <v>127153897</v>
       </c>
       <c r="B32" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540188</v>
+        <v>539873</v>
       </c>
       <c r="R32" t="n">
-        <v>7001373</v>
+        <v>7001197</v>
       </c>
       <c r="S32" t="n">
         <v>12</v>
@@ -4462,7 +4482,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en upplyft liggande levande sälg.</t>
+          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4477,26 +4497,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127164937</v>
+        <v>127158834</v>
       </c>
       <c r="B35" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4789,39 +4789,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539990</v>
+        <v>540033</v>
       </c>
       <c r="R35" t="n">
-        <v>7001113</v>
+        <v>7001311</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4856,11 +4851,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4877,22 +4867,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4910,10 +4900,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127158834</v>
+        <v>127164937</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4921,34 +4911,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540033</v>
+        <v>539990</v>
       </c>
       <c r="R36" t="n">
-        <v>7001311</v>
+        <v>7001113</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4983,6 +4978,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4999,22 +4999,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127164541</v>
+        <v>127154714</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5150,37 +5150,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540113</v>
+        <v>539872</v>
       </c>
       <c r="R38" t="n">
-        <v>7001087</v>
+        <v>7001243</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5212,6 +5217,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 gamla sälgar.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5228,22 +5238,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5261,7 +5271,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127154714</v>
+        <v>127164835</v>
       </c>
       <c r="B39" t="n">
         <v>80117</v>
@@ -5297,17 +5307,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539872</v>
+        <v>539992</v>
       </c>
       <c r="R39" t="n">
-        <v>7001243</v>
+        <v>7001093</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5341,7 +5351,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Lunglav på 3 gamla sälgar.</t>
+          <t>Växer här på en grov gammal sälg (värdeträd).</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5393,7 +5403,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127164835</v>
+        <v>127153765</v>
       </c>
       <c r="B40" t="n">
         <v>80117</v>
@@ -5424,22 +5434,22 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539992</v>
+        <v>539879</v>
       </c>
       <c r="R40" t="n">
-        <v>7001093</v>
+        <v>7001196</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5473,7 +5483,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+          <t>Fertil lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5525,10 +5535,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153765</v>
+        <v>127164541</v>
       </c>
       <c r="B41" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5536,42 +5546,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539879</v>
+        <v>540113</v>
       </c>
       <c r="R41" t="n">
-        <v>7001196</v>
+        <v>7001087</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5603,11 +5608,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5624,22 +5624,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5906,53 +5906,62 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127163137</v>
+        <v>127158031</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540285</v>
+        <v>540047</v>
       </c>
       <c r="R44" t="n">
-        <v>7001126</v>
+        <v>7001245</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5984,6 +5993,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Vid en bäck på en gammal väg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5992,6 +6006,11 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6008,10 +6027,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127158031</v>
+        <v>127163976</v>
       </c>
       <c r="B45" t="n">
-        <v>98360</v>
+        <v>98466</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6019,33 +6038,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -6053,17 +6063,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540047</v>
+        <v>540285</v>
       </c>
       <c r="R45" t="n">
-        <v>7001245</v>
+        <v>7001072</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6095,11 +6105,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Vid en bäck på en gammal väg.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6108,11 +6113,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6129,38 +6129,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127163976</v>
+        <v>127163137</v>
       </c>
       <c r="B46" t="n">
-        <v>98466</v>
+        <v>98443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6172,7 +6172,7 @@
         <v>540285</v>
       </c>
       <c r="R46" t="n">
-        <v>7001072</v>
+        <v>7001126</v>
       </c>
       <c r="S46" t="n">
         <v>7</v>
@@ -6338,52 +6338,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127153495</v>
+        <v>127153809</v>
       </c>
       <c r="B48" t="n">
-        <v>98443</v>
+        <v>80153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6392,13 +6378,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539858</v>
+        <v>539890</v>
       </c>
       <c r="R48" t="n">
-        <v>7001193</v>
+        <v>7001195</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6430,11 +6416,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6447,6 +6428,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6673,38 +6674,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127152890</v>
+        <v>127153495</v>
       </c>
       <c r="B51" t="n">
-        <v>98464</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6713,10 +6728,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539829</v>
+        <v>539858</v>
       </c>
       <c r="R51" t="n">
-        <v>7001270</v>
+        <v>7001193</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6749,6 +6764,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6780,10 +6800,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127153809</v>
+        <v>127152890</v>
       </c>
       <c r="B52" t="n">
-        <v>80153</v>
+        <v>98464</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6791,27 +6811,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6820,13 +6840,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539890</v>
+        <v>539829</v>
       </c>
       <c r="R52" t="n">
-        <v>7001195</v>
+        <v>7001270</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6870,26 +6890,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7151,62 +7151,58 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127163731</v>
+        <v>127159734</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540303</v>
+        <v>540115</v>
       </c>
       <c r="R55" t="n">
-        <v>7001059</v>
+        <v>7001344</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7249,7 +7245,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7267,10 +7263,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127159734</v>
+        <v>127156042</v>
       </c>
       <c r="B56" t="n">
-        <v>98360</v>
+        <v>98466</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7278,24 +7274,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7308,17 +7313,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540115</v>
+        <v>539924</v>
       </c>
       <c r="R56" t="n">
-        <v>7001344</v>
+        <v>7001238</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7379,7 +7384,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127156042</v>
+        <v>127162577</v>
       </c>
       <c r="B57" t="n">
         <v>98466</v>
@@ -7407,39 +7412,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539924</v>
+        <v>540238</v>
       </c>
       <c r="R57" t="n">
-        <v>7001238</v>
+        <v>7001222</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7479,11 +7470,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7500,7 +7486,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127162577</v>
+        <v>127160489</v>
       </c>
       <c r="B58" t="n">
         <v>98466</v>
@@ -7540,13 +7526,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540238</v>
+        <v>540171</v>
       </c>
       <c r="R58" t="n">
-        <v>7001222</v>
+        <v>7001276</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7586,6 +7572,11 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7602,53 +7593,62 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127160489</v>
+        <v>127163731</v>
       </c>
       <c r="B59" t="n">
-        <v>98466</v>
+        <v>98443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540171</v>
+        <v>540303</v>
       </c>
       <c r="R59" t="n">
-        <v>7001276</v>
+        <v>7001059</v>
       </c>
       <c r="S59" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7816,47 +7816,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127158943</v>
+        <v>127153134</v>
       </c>
       <c r="B61" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -7866,17 +7857,17 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540039</v>
+        <v>539827</v>
       </c>
       <c r="R61" t="n">
-        <v>7001317</v>
+        <v>7001225</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7910,7 +7901,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7925,6 +7916,26 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8196,38 +8207,47 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127153134</v>
+        <v>127158943</v>
       </c>
       <c r="B64" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -8237,17 +8257,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539827</v>
+        <v>540039</v>
       </c>
       <c r="R64" t="n">
-        <v>7001225</v>
+        <v>7001317</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8281,7 +8301,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8296,26 +8316,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8699,48 +8699,67 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127160774</v>
+        <v>127155980</v>
       </c>
       <c r="B68" t="n">
-        <v>80117</v>
+        <v>98466</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540203</v>
+        <v>539933</v>
       </c>
       <c r="R68" t="n">
-        <v>7001394</v>
+        <v>7001238</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8784,26 +8803,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8821,7 +8820,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127155980</v>
+        <v>127162549</v>
       </c>
       <c r="B69" t="n">
         <v>98466</v>
@@ -8849,39 +8848,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539933</v>
+        <v>540212</v>
       </c>
       <c r="R69" t="n">
-        <v>7001238</v>
+        <v>7001230</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8921,11 +8906,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8942,10 +8922,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127162549</v>
+        <v>127164741</v>
       </c>
       <c r="B70" t="n">
-        <v>98466</v>
+        <v>98360</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8953,21 +8933,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8978,17 +8958,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540212</v>
+        <v>540004</v>
       </c>
       <c r="R70" t="n">
-        <v>7001230</v>
+        <v>7001090</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9044,53 +9024,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127164741</v>
+        <v>127160774</v>
       </c>
       <c r="B71" t="n">
-        <v>98360</v>
+        <v>80117</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540004</v>
+        <v>540203</v>
       </c>
       <c r="R71" t="n">
-        <v>7001090</v>
+        <v>7001394</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9130,6 +9105,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Salix caprea</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9253,10 +9253,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127159827</v>
+        <v>127158202</v>
       </c>
       <c r="B73" t="n">
-        <v>80117</v>
+        <v>91344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9264,27 +9264,27 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -9293,13 +9293,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540122</v>
+        <v>540038</v>
       </c>
       <c r="R73" t="n">
-        <v>7001326</v>
+        <v>7001306</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9331,6 +9331,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikliga mängder död ved.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9345,24 +9350,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9380,10 +9375,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127158202</v>
+        <v>127159827</v>
       </c>
       <c r="B74" t="n">
-        <v>91344</v>
+        <v>80117</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9391,27 +9386,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9420,13 +9415,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540038</v>
+        <v>540122</v>
       </c>
       <c r="R74" t="n">
-        <v>7001306</v>
+        <v>7001326</v>
       </c>
       <c r="S74" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9458,11 +9453,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På fyndplatsen finns rikliga mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9477,14 +9467,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9609,62 +9609,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127162730</v>
+        <v>127154622</v>
       </c>
       <c r="B76" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540258</v>
+        <v>539897</v>
       </c>
       <c r="R76" t="n">
-        <v>7001179</v>
+        <v>7001240</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9708,6 +9694,26 @@
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9725,48 +9731,62 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127154622</v>
+        <v>127162730</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>539897</v>
+        <v>540258</v>
       </c>
       <c r="R77" t="n">
-        <v>7001240</v>
+        <v>7001179</v>
       </c>
       <c r="S77" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9810,26 +9830,6 @@
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9949,47 +9949,38 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127155895</v>
+        <v>127157972</v>
       </c>
       <c r="B79" t="n">
-        <v>98360</v>
+        <v>57654</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -9999,17 +9990,17 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539912</v>
+        <v>540038</v>
       </c>
       <c r="R79" t="n">
-        <v>7001269</v>
+        <v>7001245</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10043,7 +10034,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
+          <t>Färska och äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10058,6 +10049,26 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10075,7 +10086,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127156896</v>
+        <v>127161443</v>
       </c>
       <c r="B80" t="n">
         <v>79014</v>
@@ -10104,24 +10115,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>539983</v>
+        <v>540137</v>
       </c>
       <c r="R80" t="n">
-        <v>7001163</v>
+        <v>7001432</v>
       </c>
       <c r="S80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10155,7 +10161,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Långväxta och fertila bålar på flera granar.</t>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10207,7 +10213,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127161443</v>
+        <v>127156896</v>
       </c>
       <c r="B81" t="n">
         <v>79014</v>
@@ -10236,19 +10242,24 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540137</v>
+        <v>539983</v>
       </c>
       <c r="R81" t="n">
-        <v>7001432</v>
+        <v>7001163</v>
       </c>
       <c r="S81" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10282,7 +10293,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
+          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10456,38 +10467,47 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127157972</v>
+        <v>127154216</v>
       </c>
       <c r="B83" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -10497,17 +10517,17 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540038</v>
+        <v>539858</v>
       </c>
       <c r="R83" t="n">
-        <v>7001245</v>
+        <v>7001227</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10541,7 +10561,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
+          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10556,26 +10576,6 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10593,37 +10593,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127154216</v>
+        <v>127155895</v>
       </c>
       <c r="B84" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -10647,10 +10647,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>539858</v>
+        <v>539912</v>
       </c>
       <c r="R84" t="n">
-        <v>7001227</v>
+        <v>7001269</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
+          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10719,10 +10719,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127160670</v>
+        <v>127155804</v>
       </c>
       <c r="B85" t="n">
-        <v>98466</v>
+        <v>98464</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10730,48 +10730,44 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540195</v>
+        <v>539886</v>
       </c>
       <c r="R85" t="n">
-        <v>7001331</v>
+        <v>7001291</v>
       </c>
       <c r="S85" t="n">
         <v>9</v>
@@ -10806,11 +10802,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10819,11 +10810,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10840,7 +10826,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127155804</v>
+        <v>127163738</v>
       </c>
       <c r="B86" t="n">
         <v>98464</v>
@@ -10871,27 +10857,22 @@
       <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>539886</v>
+        <v>540308</v>
       </c>
       <c r="R86" t="n">
-        <v>7001291</v>
+        <v>7001066</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10947,53 +10928,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127163738</v>
+        <v>127164354</v>
       </c>
       <c r="B87" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540308</v>
+        <v>540166</v>
       </c>
       <c r="R87" t="n">
-        <v>7001066</v>
+        <v>7001045</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11033,6 +11009,31 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11049,48 +11050,62 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127164354</v>
+        <v>127160670</v>
       </c>
       <c r="B88" t="n">
-        <v>79014</v>
+        <v>98466</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540166</v>
+        <v>540195</v>
       </c>
       <c r="R88" t="n">
-        <v>7001045</v>
+        <v>7001331</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11122,6 +11137,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -11134,26 +11154,6 @@
       <c r="AH88" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127164710</v>
+        <v>127158784</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,42 +803,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540011</v>
+        <v>540039</v>
       </c>
       <c r="R3" t="n">
-        <v>7001079</v>
+        <v>7001341</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,14 +870,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +906,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,38 +939,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127162096</v>
+        <v>127161646</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +988,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540104</v>
+        <v>540139</v>
       </c>
       <c r="R4" t="n">
-        <v>7001431</v>
+        <v>7001452</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,26 +1043,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,7 +1060,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127160294</v>
+        <v>127164710</v>
       </c>
       <c r="B5" t="n">
         <v>80117</v>
@@ -1092,17 +1096,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540092</v>
+        <v>540011</v>
       </c>
       <c r="R5" t="n">
-        <v>7001341</v>
+        <v>7001079</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,6 +1138,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1160,12 +1169,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1183,38 +1192,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127162017</v>
+        <v>127162096</v>
       </c>
       <c r="B6" t="n">
-        <v>80152</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1223,13 +1232,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540111</v>
+        <v>540104</v>
       </c>
       <c r="R6" t="n">
-        <v>7001420</v>
+        <v>7001431</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,6 +1268,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på två sälgar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,10 +1324,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127158784</v>
+        <v>127160294</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,32 +1335,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1355,13 +1364,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540039</v>
+        <v>540092</v>
       </c>
       <c r="R7" t="n">
         <v>7001341</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,26 +1397,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1424,22 +1418,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1457,10 +1451,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127162604</v>
+        <v>127162017</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>80152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,27 +1462,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1497,13 +1491,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540240</v>
+        <v>540111</v>
       </c>
       <c r="R8" t="n">
-        <v>7001210</v>
+        <v>7001420</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1543,6 +1537,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1559,10 +1578,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127163443</v>
+        <v>127162604</v>
       </c>
       <c r="B9" t="n">
-        <v>98466</v>
+        <v>98360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,21 +1589,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,17 +1614,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540255</v>
+        <v>540240</v>
       </c>
       <c r="R9" t="n">
-        <v>7001070</v>
+        <v>7001210</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1661,10 +1680,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127162418</v>
+        <v>127163443</v>
       </c>
       <c r="B10" t="n">
-        <v>98776</v>
+        <v>98466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,42 +1691,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540127</v>
+        <v>540255</v>
       </c>
       <c r="R10" t="n">
-        <v>7001264</v>
+        <v>7001070</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1747,11 +1766,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1768,47 +1782,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127161646</v>
+        <v>127162418</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1817,13 +1822,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540139</v>
+        <v>540127</v>
       </c>
       <c r="R11" t="n">
-        <v>7001452</v>
+        <v>7001264</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1853,11 +1858,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3166,10 +3166,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127160270</v>
+        <v>127163626</v>
       </c>
       <c r="B22" t="n">
-        <v>98464</v>
+        <v>98466</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,42 +3177,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540095</v>
+        <v>540307</v>
       </c>
       <c r="R22" t="n">
-        <v>7001315</v>
+        <v>7001050</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3242,6 +3251,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3273,10 +3287,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127163626</v>
+        <v>127152848</v>
       </c>
       <c r="B23" t="n">
-        <v>98466</v>
+        <v>98360</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3284,26 +3298,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3318,17 +3332,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540307</v>
+        <v>539832</v>
       </c>
       <c r="R23" t="n">
-        <v>7001050</v>
+        <v>7001265</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3358,11 +3372,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3394,10 +3403,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127152848</v>
+        <v>127160270</v>
       </c>
       <c r="B24" t="n">
-        <v>98360</v>
+        <v>98464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3405,48 +3414,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539832</v>
+        <v>540095</v>
       </c>
       <c r="R24" t="n">
-        <v>7001265</v>
+        <v>7001315</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -5657,48 +5657,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127162532</v>
+        <v>127163137</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540214</v>
+        <v>540285</v>
       </c>
       <c r="R42" t="n">
-        <v>7001228</v>
+        <v>7001126</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5738,31 +5743,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5779,10 +5759,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127164613</v>
+        <v>127162532</v>
       </c>
       <c r="B43" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5790,39 +5770,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540079</v>
+        <v>540214</v>
       </c>
       <c r="R43" t="n">
-        <v>7001087</v>
+        <v>7001228</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5873,22 +5848,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5906,62 +5881,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127158031</v>
+        <v>127164613</v>
       </c>
       <c r="B44" t="n">
-        <v>98360</v>
+        <v>80117</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540047</v>
+        <v>540079</v>
       </c>
       <c r="R44" t="n">
-        <v>7001245</v>
+        <v>7001087</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5993,11 +5959,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Vid en bäck på en gammal väg.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6010,6 +5971,26 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6027,10 +6008,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127163976</v>
+        <v>127158031</v>
       </c>
       <c r="B45" t="n">
-        <v>98466</v>
+        <v>98360</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6038,24 +6019,33 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -6063,17 +6053,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540285</v>
+        <v>540047</v>
       </c>
       <c r="R45" t="n">
-        <v>7001072</v>
+        <v>7001245</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6105,6 +6095,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Vid en bäck på en gammal väg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6113,6 +6108,11 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6129,38 +6129,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127163137</v>
+        <v>127163976</v>
       </c>
       <c r="B46" t="n">
-        <v>98443</v>
+        <v>98466</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6172,7 +6172,7 @@
         <v>540285</v>
       </c>
       <c r="R46" t="n">
-        <v>7001126</v>
+        <v>7001072</v>
       </c>
       <c r="S46" t="n">
         <v>7</v>
@@ -7151,58 +7151,62 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127159734</v>
+        <v>127163731</v>
       </c>
       <c r="B55" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540115</v>
+        <v>540303</v>
       </c>
       <c r="R55" t="n">
-        <v>7001344</v>
+        <v>7001059</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7245,7 +7249,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7263,10 +7267,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127156042</v>
+        <v>127159734</v>
       </c>
       <c r="B56" t="n">
-        <v>98466</v>
+        <v>98360</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7274,33 +7278,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7313,17 +7308,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539924</v>
+        <v>540115</v>
       </c>
       <c r="R56" t="n">
-        <v>7001238</v>
+        <v>7001344</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7384,7 +7379,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127162577</v>
+        <v>127156042</v>
       </c>
       <c r="B57" t="n">
         <v>98466</v>
@@ -7412,25 +7407,39 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540238</v>
+        <v>539924</v>
       </c>
       <c r="R57" t="n">
-        <v>7001222</v>
+        <v>7001238</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7470,6 +7479,11 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7486,7 +7500,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127160489</v>
+        <v>127162577</v>
       </c>
       <c r="B58" t="n">
         <v>98466</v>
@@ -7526,13 +7540,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540171</v>
+        <v>540238</v>
       </c>
       <c r="R58" t="n">
-        <v>7001276</v>
+        <v>7001222</v>
       </c>
       <c r="S58" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7572,11 +7586,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7593,62 +7602,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127163731</v>
+        <v>127160489</v>
       </c>
       <c r="B59" t="n">
-        <v>98443</v>
+        <v>98466</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540303</v>
+        <v>540171</v>
       </c>
       <c r="R59" t="n">
-        <v>7001059</v>
+        <v>7001276</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -10719,58 +10719,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127155804</v>
+        <v>127164354</v>
       </c>
       <c r="B85" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>539886</v>
+        <v>540166</v>
       </c>
       <c r="R85" t="n">
-        <v>7001291</v>
+        <v>7001045</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10810,6 +10800,31 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10826,10 +10841,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127163738</v>
+        <v>127160670</v>
       </c>
       <c r="B86" t="n">
-        <v>98464</v>
+        <v>98466</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10837,24 +10852,33 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -10862,17 +10886,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540308</v>
+        <v>540195</v>
       </c>
       <c r="R86" t="n">
-        <v>7001066</v>
+        <v>7001331</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10904,6 +10928,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10912,6 +10941,11 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10928,48 +10962,58 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127164354</v>
+        <v>127155804</v>
       </c>
       <c r="B87" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540166</v>
+        <v>539886</v>
       </c>
       <c r="R87" t="n">
-        <v>7001045</v>
+        <v>7001291</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11009,31 +11053,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11050,10 +11069,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127160670</v>
+        <v>127163738</v>
       </c>
       <c r="B88" t="n">
-        <v>98466</v>
+        <v>98464</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11061,33 +11080,24 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -11095,17 +11105,17 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540195</v>
+        <v>540308</v>
       </c>
       <c r="R88" t="n">
-        <v>7001331</v>
+        <v>7001066</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11137,11 +11147,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -11150,11 +11155,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127158784</v>
+        <v>127164710</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,47 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540039</v>
+        <v>540011</v>
       </c>
       <c r="R3" t="n">
-        <v>7001341</v>
+        <v>7001079</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,24 +865,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +891,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,47 +924,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127161646</v>
+        <v>127162096</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -988,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540139</v>
+        <v>540104</v>
       </c>
       <c r="R4" t="n">
-        <v>7001452</v>
+        <v>7001431</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1028,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+          <t>Fertil lunglav på två sälgar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,6 +1019,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1060,7 +1056,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127164710</v>
+        <v>127160294</v>
       </c>
       <c r="B5" t="n">
         <v>80117</v>
@@ -1096,17 +1092,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540011</v>
+        <v>540092</v>
       </c>
       <c r="R5" t="n">
-        <v>7001079</v>
+        <v>7001341</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,11 +1134,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1169,12 +1160,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1192,38 +1183,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127162096</v>
+        <v>127162017</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>80152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1232,13 +1223,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540104</v>
+        <v>540111</v>
       </c>
       <c r="R6" t="n">
-        <v>7001431</v>
+        <v>7001420</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,11 +1259,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på två sälgar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1324,10 +1310,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127160294</v>
+        <v>127158784</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,27 +1321,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1364,13 +1355,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540092</v>
+        <v>540039</v>
       </c>
       <c r="R7" t="n">
         <v>7001341</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1397,11 +1388,26 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1418,22 +1424,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1451,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127162017</v>
+        <v>127162604</v>
       </c>
       <c r="B8" t="n">
-        <v>80152</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,27 +1468,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1491,13 +1497,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540111</v>
+        <v>540240</v>
       </c>
       <c r="R8" t="n">
-        <v>7001420</v>
+        <v>7001210</v>
       </c>
       <c r="S8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1537,31 +1543,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1578,10 +1559,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127162604</v>
+        <v>127163443</v>
       </c>
       <c r="B9" t="n">
-        <v>98360</v>
+        <v>98466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,21 +1570,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1614,17 +1595,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540240</v>
+        <v>540255</v>
       </c>
       <c r="R9" t="n">
-        <v>7001210</v>
+        <v>7001070</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1680,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127163443</v>
+        <v>127162418</v>
       </c>
       <c r="B10" t="n">
-        <v>98466</v>
+        <v>98776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,42 +1672,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>219880</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540255</v>
+        <v>540127</v>
       </c>
       <c r="R10" t="n">
-        <v>7001070</v>
+        <v>7001264</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1766,6 +1747,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1782,38 +1768,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127162418</v>
+        <v>127161646</v>
       </c>
       <c r="B11" t="n">
-        <v>98776</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1822,13 +1817,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540127</v>
+        <v>540139</v>
       </c>
       <c r="R11" t="n">
-        <v>7001264</v>
+        <v>7001452</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1858,6 +1853,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3166,10 +3166,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127163626</v>
+        <v>127160270</v>
       </c>
       <c r="B22" t="n">
-        <v>98466</v>
+        <v>98464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,51 +3177,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540307</v>
+        <v>540095</v>
       </c>
       <c r="R22" t="n">
-        <v>7001050</v>
+        <v>7001315</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3251,11 +3242,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3287,10 +3273,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127152848</v>
+        <v>127163626</v>
       </c>
       <c r="B23" t="n">
-        <v>98360</v>
+        <v>98466</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3298,26 +3284,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3332,17 +3318,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539832</v>
+        <v>540307</v>
       </c>
       <c r="R23" t="n">
-        <v>7001265</v>
+        <v>7001050</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3372,6 +3358,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3403,10 +3394,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127160270</v>
+        <v>127152848</v>
       </c>
       <c r="B24" t="n">
-        <v>98464</v>
+        <v>98360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3414,39 +3405,48 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540095</v>
+        <v>539832</v>
       </c>
       <c r="R24" t="n">
-        <v>7001315</v>
+        <v>7001265</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -7151,62 +7151,58 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127163731</v>
+        <v>127159734</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540303</v>
+        <v>540115</v>
       </c>
       <c r="R55" t="n">
-        <v>7001059</v>
+        <v>7001344</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7249,7 +7245,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7267,10 +7263,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127159734</v>
+        <v>127156042</v>
       </c>
       <c r="B56" t="n">
-        <v>98360</v>
+        <v>98466</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7278,24 +7274,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7308,17 +7313,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540115</v>
+        <v>539924</v>
       </c>
       <c r="R56" t="n">
-        <v>7001344</v>
+        <v>7001238</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7379,7 +7384,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127156042</v>
+        <v>127162577</v>
       </c>
       <c r="B57" t="n">
         <v>98466</v>
@@ -7407,39 +7412,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539924</v>
+        <v>540238</v>
       </c>
       <c r="R57" t="n">
-        <v>7001238</v>
+        <v>7001222</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7479,11 +7470,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7500,7 +7486,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127162577</v>
+        <v>127160489</v>
       </c>
       <c r="B58" t="n">
         <v>98466</v>
@@ -7540,13 +7526,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540238</v>
+        <v>540171</v>
       </c>
       <c r="R58" t="n">
-        <v>7001222</v>
+        <v>7001276</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7586,6 +7572,11 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7602,53 +7593,62 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127160489</v>
+        <v>127163731</v>
       </c>
       <c r="B59" t="n">
-        <v>98466</v>
+        <v>98443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540171</v>
+        <v>540303</v>
       </c>
       <c r="R59" t="n">
-        <v>7001276</v>
+        <v>7001059</v>
       </c>
       <c r="S59" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8699,67 +8699,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127155980</v>
+        <v>127160774</v>
       </c>
       <c r="B68" t="n">
-        <v>98466</v>
+        <v>80117</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>539933</v>
+        <v>540203</v>
       </c>
       <c r="R68" t="n">
-        <v>7001238</v>
+        <v>7001394</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8803,6 +8784,26 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8820,10 +8821,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127162549</v>
+        <v>127162146</v>
       </c>
       <c r="B69" t="n">
-        <v>98466</v>
+        <v>98464</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8831,27 +8832,27 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8860,13 +8861,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540212</v>
+        <v>540106</v>
       </c>
       <c r="R69" t="n">
-        <v>7001230</v>
+        <v>7001407</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8906,6 +8907,11 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8922,10 +8928,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127164741</v>
+        <v>127155980</v>
       </c>
       <c r="B70" t="n">
-        <v>98360</v>
+        <v>98466</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8933,42 +8939,56 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540004</v>
+        <v>539933</v>
       </c>
       <c r="R70" t="n">
-        <v>7001090</v>
+        <v>7001238</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9008,6 +9028,11 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9024,48 +9049,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127160774</v>
+        <v>127162549</v>
       </c>
       <c r="B71" t="n">
-        <v>80117</v>
+        <v>98466</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540203</v>
+        <v>540212</v>
       </c>
       <c r="R71" t="n">
-        <v>7001394</v>
+        <v>7001230</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9105,31 +9135,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Salix caprea</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9146,10 +9151,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127162146</v>
+        <v>127164741</v>
       </c>
       <c r="B72" t="n">
-        <v>98464</v>
+        <v>98360</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9157,42 +9162,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540106</v>
+        <v>540004</v>
       </c>
       <c r="R72" t="n">
-        <v>7001407</v>
+        <v>7001090</v>
       </c>
       <c r="S72" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9232,11 +9237,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127153536</v>
+        <v>127164710</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,47 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539859</v>
+        <v>540011</v>
       </c>
       <c r="R2" t="n">
-        <v>7001178</v>
+        <v>7001079</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +770,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127164710</v>
+        <v>127162096</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,22 +838,22 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540011</v>
+        <v>540104</v>
       </c>
       <c r="R3" t="n">
-        <v>7001079</v>
+        <v>7001431</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+          <t>Fertil lunglav på två sälgar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127162096</v>
+        <v>127160294</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,7 +970,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540104</v>
+        <v>540092</v>
       </c>
       <c r="R4" t="n">
-        <v>7001431</v>
+        <v>7001341</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,11 +1017,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på två sälgar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1033,12 +1043,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,32 +1066,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127160294</v>
+        <v>127162017</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1096,13 +1106,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540092</v>
+        <v>540111</v>
       </c>
       <c r="R5" t="n">
-        <v>7001341</v>
+        <v>7001420</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,12 +1170,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1183,10 +1193,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127162017</v>
+        <v>127162604</v>
       </c>
       <c r="B6" t="n">
-        <v>80152</v>
+        <v>98364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,27 +1204,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1223,13 +1233,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540111</v>
+        <v>540240</v>
       </c>
       <c r="R6" t="n">
-        <v>7001420</v>
+        <v>7001210</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1269,31 +1279,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1310,55 +1295,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127158784</v>
+        <v>127163443</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540039</v>
+        <v>540255</v>
       </c>
       <c r="R7" t="n">
-        <v>7001341</v>
+        <v>7001070</v>
       </c>
       <c r="S7" t="n">
         <v>11</v>
@@ -1388,26 +1368,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1416,31 +1381,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1457,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127162604</v>
+        <v>127162418</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,27 +1408,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>219880</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1497,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540240</v>
+        <v>540127</v>
       </c>
       <c r="R8" t="n">
-        <v>7001210</v>
+        <v>7001264</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1543,6 +1483,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1559,53 +1504,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127163443</v>
+        <v>127161646</v>
       </c>
       <c r="B9" t="n">
-        <v>98466</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540255</v>
+        <v>540139</v>
       </c>
       <c r="R9" t="n">
-        <v>7001070</v>
+        <v>7001452</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1637,6 +1591,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1645,6 +1604,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1661,38 +1625,43 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127162418</v>
+        <v>127158784</v>
       </c>
       <c r="B10" t="n">
-        <v>98776</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1701,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540127</v>
+        <v>540039</v>
       </c>
       <c r="R10" t="n">
-        <v>7001264</v>
+        <v>7001341</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1734,11 +1703,26 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1751,6 +1735,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1768,59 +1772,55 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127161646</v>
+        <v>127153536</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>57658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540139</v>
+        <v>539859</v>
       </c>
       <c r="R11" t="n">
-        <v>7001452</v>
+        <v>7001178</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1892,7 +1892,7 @@
         <v>127154593</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2021,47 +2021,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127160359</v>
+        <v>127162375</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540139</v>
+        <v>540115</v>
       </c>
       <c r="R13" t="n">
-        <v>7001298</v>
+        <v>7001309</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2103,24 +2103,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2152,47 +2142,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127155767</v>
+        <v>127160359</v>
       </c>
       <c r="B14" t="n">
-        <v>98360</v>
+        <v>57821</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2202,17 +2187,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539895</v>
+        <v>540139</v>
       </c>
       <c r="R14" t="n">
-        <v>7001284</v>
+        <v>7001298</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2239,14 +2224,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2278,37 +2273,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127162375</v>
+        <v>127155767</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2318,22 +2313,27 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540115</v>
+        <v>539895</v>
       </c>
       <c r="R15" t="n">
-        <v>7001309</v>
+        <v>7001284</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2402,7 +2402,7 @@
         <v>127161347</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127160480</v>
+        <v>127159187</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,37 +2542,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540188</v>
+        <v>540057</v>
       </c>
       <c r="R17" t="n">
-        <v>7001269</v>
+        <v>7001353</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2599,11 +2609,26 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2630,12 +2655,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2653,10 +2678,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127159187</v>
+        <v>127160480</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2664,47 +2689,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540057</v>
+        <v>540188</v>
       </c>
       <c r="R18" t="n">
-        <v>7001353</v>
+        <v>7001269</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2731,26 +2746,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2800,48 +2800,62 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127164774</v>
+        <v>127163626</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540022</v>
+        <v>540307</v>
       </c>
       <c r="R19" t="n">
-        <v>7001093</v>
+        <v>7001050</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2873,6 +2887,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2885,26 +2904,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2922,48 +2921,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127153666</v>
+        <v>127152848</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>98364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539888</v>
+        <v>539832</v>
       </c>
       <c r="R20" t="n">
-        <v>7001166</v>
+        <v>7001265</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3007,26 +3020,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3044,48 +3037,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127163769</v>
+        <v>127160270</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540285</v>
+        <v>540095</v>
       </c>
       <c r="R21" t="n">
-        <v>7001071</v>
+        <v>7001315</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3129,26 +3127,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3166,50 +3144,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127160270</v>
+        <v>127164774</v>
       </c>
       <c r="B22" t="n">
-        <v>98464</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540095</v>
+        <v>540022</v>
       </c>
       <c r="R22" t="n">
-        <v>7001315</v>
+        <v>7001093</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3256,6 +3229,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3273,62 +3266,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127163626</v>
+        <v>127153666</v>
       </c>
       <c r="B23" t="n">
-        <v>98466</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540307</v>
+        <v>539888</v>
       </c>
       <c r="R23" t="n">
-        <v>7001050</v>
+        <v>7001166</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3360,11 +3339,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3377,6 +3351,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3394,62 +3388,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127152848</v>
+        <v>127163769</v>
       </c>
       <c r="B24" t="n">
-        <v>98360</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539832</v>
+        <v>540285</v>
       </c>
       <c r="R24" t="n">
-        <v>7001265</v>
+        <v>7001071</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3493,6 +3473,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3513,7 +3513,7 @@
         <v>127158356</v>
       </c>
       <c r="B25" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>127163495</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>127155997</v>
       </c>
       <c r="B27" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>127153018</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4002,38 +4002,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153641</v>
+        <v>127153897</v>
       </c>
       <c r="B29" t="n">
-        <v>80146</v>
+        <v>98447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4042,13 +4056,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539864</v>
+        <v>539873</v>
       </c>
       <c r="R29" t="n">
-        <v>7001177</v>
+        <v>7001197</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4080,6 +4094,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4092,26 +4111,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4129,38 +4128,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127153581</v>
+        <v>127153641</v>
       </c>
       <c r="B30" t="n">
-        <v>80117</v>
+        <v>80150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4169,13 +4168,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539872</v>
+        <v>539864</v>
       </c>
       <c r="R30" t="n">
-        <v>7001176</v>
+        <v>7001177</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4256,10 +4255,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127160821</v>
+        <v>127153581</v>
       </c>
       <c r="B31" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4292,14 +4291,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540188</v>
+        <v>539872</v>
       </c>
       <c r="R31" t="n">
-        <v>7001373</v>
+        <v>7001176</v>
       </c>
       <c r="S31" t="n">
         <v>12</v>
@@ -4332,11 +4331,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en upplyft liggande levande sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4388,64 +4382,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127153897</v>
+        <v>127160821</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>80121</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539873</v>
+        <v>540188</v>
       </c>
       <c r="R32" t="n">
-        <v>7001197</v>
+        <v>7001373</v>
       </c>
       <c r="S32" t="n">
         <v>12</v>
@@ -4482,7 +4462,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
+          <t>På en upplyft liggande levande sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4497,6 +4477,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127161738</v>
+        <v>127158834</v>
       </c>
       <c r="B33" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4525,42 +4525,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540129</v>
+        <v>540033</v>
       </c>
       <c r="R33" t="n">
-        <v>7001452</v>
+        <v>7001311</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4592,11 +4587,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4613,22 +4603,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4646,10 +4636,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127161580</v>
+        <v>127161738</v>
       </c>
       <c r="B34" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4677,7 +4667,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4686,13 +4676,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540152</v>
+        <v>540129</v>
       </c>
       <c r="R34" t="n">
-        <v>7001464</v>
+        <v>7001452</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4726,7 +4716,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4778,10 +4768,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127158834</v>
+        <v>127161580</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4789,34 +4779,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540033</v>
+        <v>540152</v>
       </c>
       <c r="R35" t="n">
-        <v>7001311</v>
+        <v>7001464</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4851,6 +4846,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4867,22 +4867,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4903,7 +4903,7 @@
         <v>127164937</v>
       </c>
       <c r="B36" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>127163212</v>
       </c>
       <c r="B37" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>127154714</v>
       </c>
       <c r="B38" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>127164835</v>
       </c>
       <c r="B39" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>127153765</v>
       </c>
       <c r="B40" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>127164541</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5657,53 +5657,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127163137</v>
+        <v>127162532</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540285</v>
+        <v>540214</v>
       </c>
       <c r="R42" t="n">
-        <v>7001126</v>
+        <v>7001228</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5743,6 +5738,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5759,48 +5779,62 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127162532</v>
+        <v>127158031</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>98364</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540214</v>
+        <v>540047</v>
       </c>
       <c r="R43" t="n">
-        <v>7001228</v>
+        <v>7001245</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5832,6 +5866,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Vid en bäck på en gammal väg.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5844,26 +5883,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5881,38 +5900,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127164613</v>
+        <v>127163976</v>
       </c>
       <c r="B44" t="n">
-        <v>80117</v>
+        <v>98470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5921,13 +5940,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540079</v>
+        <v>540285</v>
       </c>
       <c r="R44" t="n">
-        <v>7001087</v>
+        <v>7001072</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5967,31 +5986,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6008,10 +6002,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127158031</v>
+        <v>127162701</v>
       </c>
       <c r="B45" t="n">
-        <v>98360</v>
+        <v>98468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6019,33 +6013,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -6053,17 +6038,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540047</v>
+        <v>540246</v>
       </c>
       <c r="R45" t="n">
-        <v>7001245</v>
+        <v>7001169</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6093,11 +6078,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Vid en bäck på en gammal väg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6129,38 +6109,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127163976</v>
+        <v>127163137</v>
       </c>
       <c r="B46" t="n">
-        <v>98466</v>
+        <v>98447</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6172,7 +6152,7 @@
         <v>540285</v>
       </c>
       <c r="R46" t="n">
-        <v>7001072</v>
+        <v>7001126</v>
       </c>
       <c r="S46" t="n">
         <v>7</v>
@@ -6231,38 +6211,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127162701</v>
+        <v>127164613</v>
       </c>
       <c r="B47" t="n">
-        <v>98464</v>
+        <v>80121</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6271,13 +6251,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540246</v>
+        <v>540079</v>
       </c>
       <c r="R47" t="n">
-        <v>7001169</v>
+        <v>7001087</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6321,6 +6301,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6341,7 +6341,7 @@
         <v>127153809</v>
       </c>
       <c r="B48" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>127160120</v>
       </c>
       <c r="B49" t="n">
-        <v>98776</v>
+        <v>98780</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>127164902</v>
       </c>
       <c r="B50" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>127153495</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>127152890</v>
       </c>
       <c r="B52" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>127162675</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>127161775</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>127159734</v>
       </c>
       <c r="B55" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>127156042</v>
       </c>
       <c r="B56" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>127162577</v>
       </c>
       <c r="B57" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>127160489</v>
       </c>
       <c r="B58" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,47 +7593,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127163731</v>
+        <v>127164425</v>
       </c>
       <c r="B59" t="n">
-        <v>98443</v>
+        <v>98468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7642,13 +7633,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540303</v>
+        <v>540128</v>
       </c>
       <c r="R59" t="n">
-        <v>7001059</v>
+        <v>7001058</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7709,38 +7700,47 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127164425</v>
+        <v>127163731</v>
       </c>
       <c r="B60" t="n">
-        <v>98464</v>
+        <v>98447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7749,13 +7749,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540128</v>
+        <v>540303</v>
       </c>
       <c r="R60" t="n">
-        <v>7001058</v>
+        <v>7001059</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>127153134</v>
       </c>
       <c r="B61" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>127156085</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>127155182</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>127158943</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>127163069</v>
       </c>
       <c r="B65" t="n">
-        <v>91322</v>
+        <v>91326</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>127160440</v>
       </c>
       <c r="B66" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>127160736</v>
       </c>
       <c r="B67" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>127160774</v>
       </c>
       <c r="B68" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8821,10 +8821,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127162146</v>
+        <v>127155980</v>
       </c>
       <c r="B69" t="n">
-        <v>98464</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8832,42 +8832,56 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540106</v>
+        <v>539933</v>
       </c>
       <c r="R69" t="n">
-        <v>7001407</v>
+        <v>7001238</v>
       </c>
       <c r="S69" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8928,10 +8942,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127155980</v>
+        <v>127162549</v>
       </c>
       <c r="B70" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8956,39 +8970,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539933</v>
+        <v>540212</v>
       </c>
       <c r="R70" t="n">
-        <v>7001238</v>
+        <v>7001230</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9028,11 +9028,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9049,10 +9044,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127162549</v>
+        <v>127164741</v>
       </c>
       <c r="B71" t="n">
-        <v>98466</v>
+        <v>98364</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9060,21 +9055,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9085,17 +9080,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540212</v>
+        <v>540004</v>
       </c>
       <c r="R71" t="n">
-        <v>7001230</v>
+        <v>7001090</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9151,10 +9146,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127164741</v>
+        <v>127162146</v>
       </c>
       <c r="B72" t="n">
-        <v>98360</v>
+        <v>98468</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9162,42 +9157,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540004</v>
+        <v>540106</v>
       </c>
       <c r="R72" t="n">
-        <v>7001090</v>
+        <v>7001407</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9237,6 +9232,11 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9256,7 +9256,7 @@
         <v>127158202</v>
       </c>
       <c r="B73" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>127159827</v>
       </c>
       <c r="B74" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>127153185</v>
       </c>
       <c r="B75" t="n">
-        <v>98776</v>
+        <v>98780</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>127154622</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>127162730</v>
       </c>
       <c r="B77" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>127163162</v>
       </c>
       <c r="B78" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127157972</v>
+        <v>127161443</v>
       </c>
       <c r="B79" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9960,47 +9960,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540038</v>
+        <v>540137</v>
       </c>
       <c r="R79" t="n">
-        <v>7001245</v>
+        <v>7001432</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10034,7 +10024,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10063,12 +10053,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10086,10 +10076,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127161443</v>
+        <v>127156896</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10115,19 +10105,24 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540137</v>
+        <v>539983</v>
       </c>
       <c r="R80" t="n">
-        <v>7001432</v>
+        <v>7001163</v>
       </c>
       <c r="S80" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10161,7 +10156,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
+          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10213,10 +10208,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127156896</v>
+        <v>127157972</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10224,42 +10219,47 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>539983</v>
+        <v>540038</v>
       </c>
       <c r="R81" t="n">
-        <v>7001163</v>
+        <v>7001245</v>
       </c>
       <c r="S81" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Långväxta och fertila bålar på flera granar.</t>
+          <t>Färska och äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10322,12 +10322,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10345,45 +10345,64 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127160558</v>
+        <v>127154216</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540205</v>
+        <v>539858</v>
       </c>
       <c r="R82" t="n">
-        <v>7001321</v>
+        <v>7001227</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10418,6 +10437,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10430,26 +10454,6 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10467,64 +10471,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127154216</v>
+        <v>127160558</v>
       </c>
       <c r="B83" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>539858</v>
+        <v>540205</v>
       </c>
       <c r="R83" t="n">
-        <v>7001227</v>
+        <v>7001321</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10559,11 +10544,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10576,6 +10556,26 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10596,7 +10596,7 @@
         <v>127155895</v>
       </c>
       <c r="B84" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>127164354</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10841,10 +10841,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127160670</v>
+        <v>127155804</v>
       </c>
       <c r="B86" t="n">
-        <v>98466</v>
+        <v>98468</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10852,48 +10852,44 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540195</v>
+        <v>539886</v>
       </c>
       <c r="R86" t="n">
-        <v>7001331</v>
+        <v>7001291</v>
       </c>
       <c r="S86" t="n">
         <v>9</v>
@@ -10928,11 +10924,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10941,11 +10932,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10962,10 +10948,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127155804</v>
+        <v>127163738</v>
       </c>
       <c r="B87" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10993,27 +10979,22 @@
       <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>539886</v>
+        <v>540308</v>
       </c>
       <c r="R87" t="n">
-        <v>7001291</v>
+        <v>7001066</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11069,10 +11050,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127163738</v>
+        <v>127160670</v>
       </c>
       <c r="B88" t="n">
-        <v>98464</v>
+        <v>98470</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11080,24 +11061,33 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -11105,17 +11095,17 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540308</v>
+        <v>540195</v>
       </c>
       <c r="R88" t="n">
-        <v>7001066</v>
+        <v>7001331</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11147,6 +11137,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -11155,6 +11150,11 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11174,7 +11174,7 @@
         <v>127159714</v>
       </c>
       <c r="B89" t="n">
-        <v>98441</v>
+        <v>98445</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>127157856</v>
       </c>
       <c r="B90" t="n">
-        <v>98349</v>
+        <v>98353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>127157226</v>
       </c>
       <c r="B91" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>127159972</v>
       </c>
       <c r="B92" t="n">
-        <v>98441</v>
+        <v>98445</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>127155729</v>
       </c>
       <c r="B93" t="n">
-        <v>98349</v>
+        <v>98353</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>127174668</v>
       </c>
       <c r="B94" t="n">
-        <v>90871</v>
+        <v>90875</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>127157050</v>
       </c>
       <c r="B95" t="n">
-        <v>98349</v>
+        <v>98353</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>127160214</v>
       </c>
       <c r="B96" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>127160071</v>
       </c>
       <c r="B97" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>127155870</v>
       </c>
       <c r="B98" t="n">
-        <v>98349</v>
+        <v>98353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>127164256</v>
       </c>
       <c r="B99" t="n">
-        <v>98349</v>
+        <v>98353</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>127157299</v>
       </c>
       <c r="B100" t="n">
-        <v>98349</v>
+        <v>98353</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>127162786</v>
       </c>
       <c r="B101" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127164710</v>
+        <v>127158784</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540011</v>
+        <v>540039</v>
       </c>
       <c r="R2" t="n">
-        <v>7001079</v>
+        <v>7001341</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,14 +753,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +789,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127162096</v>
+        <v>127153536</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,42 +833,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540104</v>
+        <v>539859</v>
       </c>
       <c r="R3" t="n">
-        <v>7001431</v>
+        <v>7001178</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +907,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,26 +922,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127160294</v>
+        <v>127164710</v>
       </c>
       <c r="B4" t="n">
         <v>80121</v>
@@ -975,17 +975,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540092</v>
+        <v>540011</v>
       </c>
       <c r="R4" t="n">
-        <v>7001341</v>
+        <v>7001079</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,6 +1017,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1043,12 +1048,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,38 +1071,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127162017</v>
+        <v>127162096</v>
       </c>
       <c r="B5" t="n">
-        <v>80156</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1106,13 +1111,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540111</v>
+        <v>540104</v>
       </c>
       <c r="R5" t="n">
-        <v>7001420</v>
+        <v>7001431</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,6 +1147,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på två sälgar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1193,38 +1203,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127162604</v>
+        <v>127160294</v>
       </c>
       <c r="B6" t="n">
-        <v>98364</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1233,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540240</v>
+        <v>540092</v>
       </c>
       <c r="R6" t="n">
-        <v>7001210</v>
+        <v>7001341</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1279,6 +1289,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1295,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127163443</v>
+        <v>127162017</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>80156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,42 +1341,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540255</v>
+        <v>540111</v>
       </c>
       <c r="R7" t="n">
-        <v>7001070</v>
+        <v>7001420</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1381,6 +1416,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1397,38 +1457,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127162418</v>
+        <v>127161646</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1437,13 +1506,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540127</v>
+        <v>540139</v>
       </c>
       <c r="R8" t="n">
-        <v>7001264</v>
+        <v>7001452</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,6 +1542,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,62 +1578,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127161646</v>
+        <v>127163443</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540139</v>
+        <v>540255</v>
       </c>
       <c r="R9" t="n">
-        <v>7001452</v>
+        <v>7001070</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1591,11 +1656,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1604,11 +1664,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1625,43 +1680,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127158784</v>
+        <v>127162604</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>98364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1670,13 +1720,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540039</v>
+        <v>540240</v>
       </c>
       <c r="R10" t="n">
-        <v>7001341</v>
+        <v>7001210</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,26 +1753,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1731,31 +1766,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1772,58 +1782,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127153536</v>
+        <v>127162418</v>
       </c>
       <c r="B11" t="n">
-        <v>57658</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>219880</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539859</v>
+        <v>540127</v>
       </c>
       <c r="R11" t="n">
-        <v>7001178</v>
+        <v>7001264</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1853,11 +1858,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2021,37 +2021,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127162375</v>
+        <v>127155767</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2061,22 +2061,27 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540115</v>
+        <v>539895</v>
       </c>
       <c r="R13" t="n">
-        <v>7001309</v>
+        <v>7001284</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2110,7 +2115,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2273,37 +2278,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155767</v>
+        <v>127162375</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2313,27 +2318,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539895</v>
+        <v>540115</v>
       </c>
       <c r="R15" t="n">
-        <v>7001284</v>
+        <v>7001309</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2531,10 +2531,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127159187</v>
+        <v>127160480</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,47 +2542,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540057</v>
+        <v>540188</v>
       </c>
       <c r="R17" t="n">
-        <v>7001353</v>
+        <v>7001269</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2609,26 +2599,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2655,12 +2630,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2678,10 +2653,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127160480</v>
+        <v>127159187</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,37 +2664,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540188</v>
+        <v>540057</v>
       </c>
       <c r="R18" t="n">
-        <v>7001269</v>
+        <v>7001353</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2746,11 +2731,26 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2800,62 +2800,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127163626</v>
+        <v>127164774</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540307</v>
+        <v>540022</v>
       </c>
       <c r="R19" t="n">
-        <v>7001050</v>
+        <v>7001093</v>
       </c>
       <c r="S19" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2887,11 +2873,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2904,6 +2885,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2921,62 +2922,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127152848</v>
+        <v>127153666</v>
       </c>
       <c r="B20" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539832</v>
+        <v>539888</v>
       </c>
       <c r="R20" t="n">
-        <v>7001265</v>
+        <v>7001166</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3020,6 +3007,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3037,10 +3044,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127160270</v>
+        <v>127163626</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3048,42 +3055,51 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540095</v>
+        <v>540307</v>
       </c>
       <c r="R21" t="n">
-        <v>7001315</v>
+        <v>7001050</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3113,6 +3129,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3144,45 +3165,59 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127164774</v>
+        <v>127152848</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>98364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540022</v>
+        <v>539832</v>
       </c>
       <c r="R22" t="n">
-        <v>7001093</v>
+        <v>7001265</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3229,26 +3264,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3266,48 +3281,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127153666</v>
+        <v>127160270</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539888</v>
+        <v>540095</v>
       </c>
       <c r="R23" t="n">
-        <v>7001166</v>
+        <v>7001315</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3351,26 +3371,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -4002,52 +4002,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153897</v>
+        <v>127153641</v>
       </c>
       <c r="B29" t="n">
-        <v>98447</v>
+        <v>80150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4056,13 +4042,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539873</v>
+        <v>539864</v>
       </c>
       <c r="R29" t="n">
-        <v>7001197</v>
+        <v>7001177</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4094,11 +4080,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4111,6 +4092,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4128,38 +4129,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127153641</v>
+        <v>127153581</v>
       </c>
       <c r="B30" t="n">
-        <v>80150</v>
+        <v>80121</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4168,13 +4169,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539864</v>
+        <v>539872</v>
       </c>
       <c r="R30" t="n">
-        <v>7001177</v>
+        <v>7001176</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4255,7 +4256,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127153581</v>
+        <v>127160821</v>
       </c>
       <c r="B31" t="n">
         <v>80121</v>
@@ -4291,14 +4292,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539872</v>
+        <v>540188</v>
       </c>
       <c r="R31" t="n">
-        <v>7001176</v>
+        <v>7001373</v>
       </c>
       <c r="S31" t="n">
         <v>12</v>
@@ -4331,6 +4332,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en upplyft liggande levande sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4382,50 +4388,64 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127160821</v>
+        <v>127153897</v>
       </c>
       <c r="B32" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540188</v>
+        <v>539873</v>
       </c>
       <c r="R32" t="n">
-        <v>7001373</v>
+        <v>7001197</v>
       </c>
       <c r="S32" t="n">
         <v>12</v>
@@ -4462,7 +4482,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en upplyft liggande levande sälg.</t>
+          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4477,26 +4497,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127158834</v>
+        <v>127161738</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4525,37 +4525,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540033</v>
+        <v>540129</v>
       </c>
       <c r="R33" t="n">
-        <v>7001311</v>
+        <v>7001452</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4587,6 +4592,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4603,22 +4613,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4636,7 +4646,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127161738</v>
+        <v>127161580</v>
       </c>
       <c r="B34" t="n">
         <v>80121</v>
@@ -4667,7 +4677,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4676,13 +4686,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540129</v>
+        <v>540152</v>
       </c>
       <c r="R34" t="n">
-        <v>7001452</v>
+        <v>7001464</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4716,7 +4726,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4768,10 +4778,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127161580</v>
+        <v>127158834</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4779,39 +4789,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540152</v>
+        <v>540033</v>
       </c>
       <c r="R35" t="n">
-        <v>7001464</v>
+        <v>7001311</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4846,11 +4851,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4867,22 +4867,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5139,7 +5139,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127154714</v>
+        <v>127164835</v>
       </c>
       <c r="B38" t="n">
         <v>80121</v>
@@ -5175,17 +5175,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539872</v>
+        <v>539992</v>
       </c>
       <c r="R38" t="n">
-        <v>7001243</v>
+        <v>7001093</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Lunglav på 3 gamla sälgar.</t>
+          <t>Växer här på en grov gammal sälg (värdeträd).</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5271,10 +5271,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127164835</v>
+        <v>127164541</v>
       </c>
       <c r="B39" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5282,39 +5282,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539992</v>
+        <v>540113</v>
       </c>
       <c r="R39" t="n">
-        <v>7001093</v>
+        <v>7001087</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5349,11 +5344,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Växer här på en grov gammal sälg (värdeträd).</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5370,22 +5360,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5403,7 +5393,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153765</v>
+        <v>127154714</v>
       </c>
       <c r="B40" t="n">
         <v>80121</v>
@@ -5434,7 +5424,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5443,13 +5433,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539879</v>
+        <v>539872</v>
       </c>
       <c r="R40" t="n">
-        <v>7001196</v>
+        <v>7001243</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5483,7 +5473,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg.</t>
+          <t>Lunglav på 3 gamla sälgar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5535,10 +5525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127164541</v>
+        <v>127153765</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5546,37 +5536,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540113</v>
+        <v>539879</v>
       </c>
       <c r="R41" t="n">
-        <v>7001087</v>
+        <v>7001196</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5608,6 +5603,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5624,22 +5624,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5779,62 +5779,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127158031</v>
+        <v>127164613</v>
       </c>
       <c r="B43" t="n">
-        <v>98364</v>
+        <v>80121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540047</v>
+        <v>540079</v>
       </c>
       <c r="R43" t="n">
-        <v>7001245</v>
+        <v>7001087</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5866,11 +5857,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Vid en bäck på en gammal väg.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5883,6 +5869,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5900,38 +5906,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127163976</v>
+        <v>127163137</v>
       </c>
       <c r="B44" t="n">
-        <v>98470</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5943,7 +5949,7 @@
         <v>540285</v>
       </c>
       <c r="R44" t="n">
-        <v>7001072</v>
+        <v>7001126</v>
       </c>
       <c r="S44" t="n">
         <v>7</v>
@@ -6002,10 +6008,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127162701</v>
+        <v>127163976</v>
       </c>
       <c r="B45" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6013,21 +6019,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6042,13 +6048,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540246</v>
+        <v>540285</v>
       </c>
       <c r="R45" t="n">
-        <v>7001169</v>
+        <v>7001072</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6088,11 +6094,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6109,53 +6110,62 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127163137</v>
+        <v>127158031</v>
       </c>
       <c r="B46" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540285</v>
+        <v>540047</v>
       </c>
       <c r="R46" t="n">
-        <v>7001126</v>
+        <v>7001245</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6187,6 +6197,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Vid en bäck på en gammal väg.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6195,6 +6210,11 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6211,38 +6231,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127164613</v>
+        <v>127162701</v>
       </c>
       <c r="B47" t="n">
-        <v>80121</v>
+        <v>98468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6251,13 +6271,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540079</v>
+        <v>540246</v>
       </c>
       <c r="R47" t="n">
-        <v>7001087</v>
+        <v>7001169</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6301,26 +6321,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6338,38 +6338,52 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127153809</v>
+        <v>127153495</v>
       </c>
       <c r="B48" t="n">
-        <v>80157</v>
+        <v>98447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6378,13 +6392,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539890</v>
+        <v>539858</v>
       </c>
       <c r="R48" t="n">
-        <v>7001195</v>
+        <v>7001193</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6416,6 +6430,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6428,26 +6447,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6674,52 +6673,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127153495</v>
+        <v>127153809</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>80157</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6728,13 +6713,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539858</v>
+        <v>539890</v>
       </c>
       <c r="R51" t="n">
-        <v>7001193</v>
+        <v>7001195</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6766,11 +6751,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6783,6 +6763,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6907,48 +6907,62 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127162675</v>
+        <v>127163731</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540237</v>
+        <v>540303</v>
       </c>
       <c r="R53" t="n">
-        <v>7001188</v>
+        <v>7001059</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6992,26 +7006,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7029,7 +7023,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127161775</v>
+        <v>127162675</v>
       </c>
       <c r="B54" t="n">
         <v>79018</v>
@@ -7064,13 +7058,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540092</v>
+        <v>540237</v>
       </c>
       <c r="R54" t="n">
-        <v>7001443</v>
+        <v>7001188</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7151,58 +7145,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127159734</v>
+        <v>127161775</v>
       </c>
       <c r="B55" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540115</v>
+        <v>540092</v>
       </c>
       <c r="R55" t="n">
-        <v>7001344</v>
+        <v>7001443</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7245,7 +7229,27 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7263,10 +7267,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127156042</v>
+        <v>127164425</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>98468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7274,56 +7278,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539924</v>
+        <v>540128</v>
       </c>
       <c r="R56" t="n">
-        <v>7001238</v>
+        <v>7001058</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7366,7 +7356,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7384,10 +7374,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127162577</v>
+        <v>127159734</v>
       </c>
       <c r="B57" t="n">
-        <v>98470</v>
+        <v>98364</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7395,21 +7385,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7418,19 +7408,24 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540238</v>
+        <v>540115</v>
       </c>
       <c r="R57" t="n">
-        <v>7001222</v>
+        <v>7001344</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7470,6 +7465,11 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7486,7 +7486,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127160489</v>
+        <v>127156042</v>
       </c>
       <c r="B58" t="n">
         <v>98470</v>
@@ -7514,25 +7514,39 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540171</v>
+        <v>539924</v>
       </c>
       <c r="R58" t="n">
-        <v>7001276</v>
+        <v>7001238</v>
       </c>
       <c r="S58" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7575,7 +7589,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7593,10 +7607,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127164425</v>
+        <v>127162577</v>
       </c>
       <c r="B59" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7604,42 +7618,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540128</v>
+        <v>540238</v>
       </c>
       <c r="R59" t="n">
-        <v>7001058</v>
+        <v>7001222</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7679,11 +7693,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7700,62 +7709,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127163731</v>
+        <v>127160489</v>
       </c>
       <c r="B60" t="n">
-        <v>98447</v>
+        <v>98470</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540303</v>
+        <v>540171</v>
       </c>
       <c r="R60" t="n">
-        <v>7001059</v>
+        <v>7001276</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7816,10 +7816,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127153134</v>
+        <v>127156085</v>
       </c>
       <c r="B61" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7827,44 +7827,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>539827</v>
+        <v>539948</v>
       </c>
       <c r="R61" t="n">
-        <v>7001225</v>
+        <v>7001204</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7899,11 +7889,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7930,12 +7915,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7953,7 +7938,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127156085</v>
+        <v>127155182</v>
       </c>
       <c r="B62" t="n">
         <v>79018</v>
@@ -7982,16 +7967,21 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>539948</v>
+        <v>539891</v>
       </c>
       <c r="R62" t="n">
-        <v>7001204</v>
+        <v>7001292</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8024,6 +8014,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8075,53 +8070,67 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127155182</v>
+        <v>127158943</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>539891</v>
+        <v>540039</v>
       </c>
       <c r="R63" t="n">
-        <v>7001292</v>
+        <v>7001317</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8155,7 +8164,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med apothecier.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8170,26 +8179,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8207,47 +8196,38 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127158943</v>
+        <v>127153134</v>
       </c>
       <c r="B64" t="n">
-        <v>98447</v>
+        <v>57658</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -8257,17 +8237,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540039</v>
+        <v>539827</v>
       </c>
       <c r="R64" t="n">
-        <v>7001317</v>
+        <v>7001225</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8301,7 +8281,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8316,6 +8296,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127155980</v>
+        <v>127164741</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>98364</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8832,56 +8832,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539933</v>
+        <v>540004</v>
       </c>
       <c r="R69" t="n">
-        <v>7001238</v>
+        <v>7001090</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8921,11 +8907,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8942,7 +8923,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127162549</v>
+        <v>127155980</v>
       </c>
       <c r="B70" t="n">
         <v>98470</v>
@@ -8970,25 +8951,39 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540212</v>
+        <v>539933</v>
       </c>
       <c r="R70" t="n">
-        <v>7001230</v>
+        <v>7001238</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9028,6 +9023,11 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9044,10 +9044,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127164741</v>
+        <v>127162146</v>
       </c>
       <c r="B71" t="n">
-        <v>98364</v>
+        <v>98468</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9055,42 +9055,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540004</v>
+        <v>540106</v>
       </c>
       <c r="R71" t="n">
-        <v>7001090</v>
+        <v>7001407</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9130,6 +9130,11 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9146,10 +9151,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127162146</v>
+        <v>127162549</v>
       </c>
       <c r="B72" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9157,27 +9162,27 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9186,13 +9191,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540106</v>
+        <v>540212</v>
       </c>
       <c r="R72" t="n">
-        <v>7001407</v>
+        <v>7001230</v>
       </c>
       <c r="S72" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9232,11 +9237,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9731,7 +9731,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127162730</v>
+        <v>127163162</v>
       </c>
       <c r="B77" t="n">
         <v>98364</v>
@@ -9759,16 +9759,7 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9776,17 +9767,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540258</v>
+        <v>540247</v>
       </c>
       <c r="R77" t="n">
-        <v>7001179</v>
+        <v>7001094</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9826,11 +9817,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9847,7 +9833,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127163162</v>
+        <v>127162730</v>
       </c>
       <c r="B78" t="n">
         <v>98364</v>
@@ -9875,7 +9861,16 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9883,17 +9878,17 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540247</v>
+        <v>540258</v>
       </c>
       <c r="R78" t="n">
-        <v>7001094</v>
+        <v>7001179</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9933,6 +9928,11 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9949,7 +9949,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127161443</v>
+        <v>127156896</v>
       </c>
       <c r="B79" t="n">
         <v>79018</v>
@@ -9978,19 +9978,24 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540137</v>
+        <v>539983</v>
       </c>
       <c r="R79" t="n">
-        <v>7001432</v>
+        <v>7001163</v>
       </c>
       <c r="S79" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10024,7 +10029,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
+          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10076,7 +10081,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127156896</v>
+        <v>127160558</v>
       </c>
       <c r="B80" t="n">
         <v>79018</v>
@@ -10105,24 +10110,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>539983</v>
+        <v>540205</v>
       </c>
       <c r="R80" t="n">
-        <v>7001163</v>
+        <v>7001321</v>
       </c>
       <c r="S80" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10152,11 +10152,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10208,38 +10203,47 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127157972</v>
+        <v>127155895</v>
       </c>
       <c r="B81" t="n">
-        <v>57658</v>
+        <v>98364</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -10249,17 +10253,17 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540038</v>
+        <v>539912</v>
       </c>
       <c r="R81" t="n">
-        <v>7001245</v>
+        <v>7001269</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10293,7 +10297,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
+          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10308,26 +10312,6 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10345,67 +10329,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127154216</v>
+        <v>127161443</v>
       </c>
       <c r="B82" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>539858</v>
+        <v>540137</v>
       </c>
       <c r="R82" t="n">
-        <v>7001227</v>
+        <v>7001432</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10439,7 +10404,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10454,6 +10419,26 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10471,10 +10456,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127160558</v>
+        <v>127157972</v>
       </c>
       <c r="B83" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10482,37 +10467,47 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540205</v>
+        <v>540038</v>
       </c>
       <c r="R83" t="n">
-        <v>7001321</v>
+        <v>7001245</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10544,6 +10539,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10570,12 +10570,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10593,37 +10593,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127155895</v>
+        <v>127154216</v>
       </c>
       <c r="B84" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -10647,10 +10647,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>539912</v>
+        <v>539858</v>
       </c>
       <c r="R84" t="n">
-        <v>7001269</v>
+        <v>7001227</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
+          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10841,10 +10841,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127155804</v>
+        <v>127160670</v>
       </c>
       <c r="B86" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10852,44 +10852,48 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>539886</v>
+        <v>540195</v>
       </c>
       <c r="R86" t="n">
-        <v>7001291</v>
+        <v>7001331</v>
       </c>
       <c r="S86" t="n">
         <v>9</v>
@@ -10924,6 +10928,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10932,6 +10941,11 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10948,7 +10962,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127163738</v>
+        <v>127155804</v>
       </c>
       <c r="B87" t="n">
         <v>98468</v>
@@ -10979,22 +10993,27 @@
       <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540308</v>
+        <v>539886</v>
       </c>
       <c r="R87" t="n">
-        <v>7001066</v>
+        <v>7001291</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11050,10 +11069,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127160670</v>
+        <v>127163738</v>
       </c>
       <c r="B88" t="n">
-        <v>98470</v>
+        <v>98468</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11061,33 +11080,24 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -11095,17 +11105,17 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540195</v>
+        <v>540308</v>
       </c>
       <c r="R88" t="n">
-        <v>7001331</v>
+        <v>7001066</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11137,11 +11147,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -11150,11 +11155,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -12069,48 +12069,67 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127160214</v>
+        <v>127160071</v>
       </c>
       <c r="B96" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540081</v>
+        <v>540115</v>
       </c>
       <c r="R96" t="n">
-        <v>7001299</v>
+        <v>7001289</v>
       </c>
       <c r="S96" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12142,6 +12161,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12154,26 +12178,6 @@
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12191,67 +12195,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127160071</v>
+        <v>127160214</v>
       </c>
       <c r="B97" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540115</v>
+        <v>540081</v>
       </c>
       <c r="R97" t="n">
-        <v>7001289</v>
+        <v>7001299</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12283,11 +12268,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12300,6 +12280,26 @@
       <c r="AH97" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127158784</v>
+        <v>127162096</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,32 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540039</v>
+        <v>540104</v>
       </c>
       <c r="R2" t="n">
-        <v>7001341</v>
+        <v>7001431</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,24 +748,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+          <t>Fertil lunglav på två sälgar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +774,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -822,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127153536</v>
+        <v>127160294</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,47 +818,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539859</v>
+        <v>540092</v>
       </c>
       <c r="R3" t="n">
-        <v>7001178</v>
+        <v>7001341</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,11 +885,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -922,6 +897,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,32 +934,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127164710</v>
+        <v>127162017</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>80156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -975,14 +970,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540011</v>
+        <v>540111</v>
       </c>
       <c r="R4" t="n">
-        <v>7001079</v>
+        <v>7001420</v>
       </c>
       <c r="S4" t="n">
         <v>16</v>
@@ -1015,11 +1010,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127162096</v>
+        <v>127158784</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,27 +1072,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1111,13 +1106,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540104</v>
+        <v>540039</v>
       </c>
       <c r="R5" t="n">
-        <v>7001431</v>
+        <v>7001341</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,14 +1139,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,22 +1175,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,38 +1208,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127160294</v>
+        <v>127161646</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1243,13 +1257,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540092</v>
+        <v>540139</v>
       </c>
       <c r="R6" t="n">
-        <v>7001341</v>
+        <v>7001452</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,6 +1295,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1293,26 +1312,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1330,10 +1329,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127162017</v>
+        <v>127163443</v>
       </c>
       <c r="B7" t="n">
-        <v>80156</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,42 +1340,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540111</v>
+        <v>540255</v>
       </c>
       <c r="R7" t="n">
-        <v>7001420</v>
+        <v>7001070</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1416,31 +1415,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1457,47 +1431,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127161646</v>
+        <v>127162604</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1506,13 +1471,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540139</v>
+        <v>540240</v>
       </c>
       <c r="R8" t="n">
-        <v>7001452</v>
+        <v>7001210</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1544,11 +1509,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1557,11 +1517,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1578,10 +1533,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127163443</v>
+        <v>127162418</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>98780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,42 +1544,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219880</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540255</v>
+        <v>540127</v>
       </c>
       <c r="R9" t="n">
-        <v>7001070</v>
+        <v>7001264</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1664,6 +1619,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1680,53 +1640,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127162604</v>
+        <v>127153536</v>
       </c>
       <c r="B10" t="n">
-        <v>98364</v>
+        <v>57658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540240</v>
+        <v>539859</v>
       </c>
       <c r="R10" t="n">
-        <v>7001210</v>
+        <v>7001178</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1758,6 +1723,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1766,6 +1736,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1782,53 +1757,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127162418</v>
+        <v>127164710</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>80121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540127</v>
+        <v>540011</v>
       </c>
       <c r="R11" t="n">
-        <v>7001264</v>
+        <v>7001079</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1860,6 +1835,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1872,6 +1852,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2021,47 +2021,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127155767</v>
+        <v>127160359</v>
       </c>
       <c r="B13" t="n">
-        <v>98364</v>
+        <v>57821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2071,17 +2066,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539895</v>
+        <v>540139</v>
       </c>
       <c r="R13" t="n">
-        <v>7001284</v>
+        <v>7001298</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2108,14 +2103,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2147,47 +2152,47 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127160359</v>
+        <v>127162375</v>
       </c>
       <c r="B14" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2196,13 +2201,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540139</v>
+        <v>540115</v>
       </c>
       <c r="R14" t="n">
-        <v>7001298</v>
+        <v>7001309</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2229,24 +2234,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2278,37 +2273,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127162375</v>
+        <v>127155767</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2318,22 +2313,27 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540115</v>
+        <v>539895</v>
       </c>
       <c r="R15" t="n">
-        <v>7001309</v>
+        <v>7001284</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3510,10 +3510,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127158356</v>
+        <v>127163495</v>
       </c>
       <c r="B25" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3521,42 +3521,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540032</v>
+        <v>540258</v>
       </c>
       <c r="R25" t="n">
-        <v>7001287</v>
+        <v>7001065</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3614,12 +3609,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3637,48 +3632,67 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127163495</v>
+        <v>127155997</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>98364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540258</v>
+        <v>539924</v>
       </c>
       <c r="R26" t="n">
-        <v>7001065</v>
+        <v>7001238</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3721,27 +3735,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3759,64 +3753,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127155997</v>
+        <v>127158356</v>
       </c>
       <c r="B27" t="n">
-        <v>98364</v>
+        <v>91330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539924</v>
+        <v>540032</v>
       </c>
       <c r="R27" t="n">
-        <v>7001238</v>
+        <v>7001287</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3862,7 +3842,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127161738</v>
+        <v>127161580</v>
       </c>
       <c r="B33" t="n">
         <v>80121</v>
@@ -4545,7 +4545,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4554,13 +4554,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540129</v>
+        <v>540152</v>
       </c>
       <c r="R33" t="n">
-        <v>7001452</v>
+        <v>7001464</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4646,10 +4646,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127161580</v>
+        <v>127158834</v>
       </c>
       <c r="B34" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4657,39 +4657,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540152</v>
+        <v>540033</v>
       </c>
       <c r="R34" t="n">
-        <v>7001464</v>
+        <v>7001311</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4724,11 +4719,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4745,22 +4735,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4778,10 +4768,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127158834</v>
+        <v>127164937</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4789,34 +4779,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540033</v>
+        <v>539990</v>
       </c>
       <c r="R35" t="n">
-        <v>7001311</v>
+        <v>7001113</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4851,6 +4846,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4867,22 +4867,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4900,38 +4900,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127164937</v>
+        <v>127163212</v>
       </c>
       <c r="B36" t="n">
-        <v>80121</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4940,13 +4940,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539990</v>
+        <v>540253</v>
       </c>
       <c r="R36" t="n">
-        <v>7001113</v>
+        <v>7001109</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4978,11 +4978,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4995,26 +4990,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5032,53 +5007,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127163212</v>
+        <v>127161738</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>80121</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540253</v>
+        <v>540129</v>
       </c>
       <c r="R37" t="n">
-        <v>7001109</v>
+        <v>7001452</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5110,6 +5085,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5122,6 +5102,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6907,47 +6907,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127163731</v>
+        <v>127164425</v>
       </c>
       <c r="B53" t="n">
-        <v>98447</v>
+        <v>98468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6956,13 +6947,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540303</v>
+        <v>540128</v>
       </c>
       <c r="R53" t="n">
-        <v>7001059</v>
+        <v>7001058</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7267,38 +7258,47 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127164425</v>
+        <v>127163731</v>
       </c>
       <c r="B56" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7307,13 +7307,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540128</v>
+        <v>540303</v>
       </c>
       <c r="R56" t="n">
-        <v>7001058</v>
+        <v>7001059</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127156896</v>
+        <v>127161443</v>
       </c>
       <c r="B79" t="n">
         <v>79018</v>
@@ -9978,24 +9978,19 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539983</v>
+        <v>540137</v>
       </c>
       <c r="R79" t="n">
-        <v>7001163</v>
+        <v>7001432</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10029,7 +10024,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Långväxta och fertila bålar på flera granar.</t>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10081,7 +10076,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127160558</v>
+        <v>127156896</v>
       </c>
       <c r="B80" t="n">
         <v>79018</v>
@@ -10110,19 +10105,24 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540205</v>
+        <v>539983</v>
       </c>
       <c r="R80" t="n">
-        <v>7001321</v>
+        <v>7001163</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10152,6 +10152,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10203,64 +10208,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127155895</v>
+        <v>127160558</v>
       </c>
       <c r="B81" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>539912</v>
+        <v>540205</v>
       </c>
       <c r="R81" t="n">
-        <v>7001269</v>
+        <v>7001321</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10295,11 +10281,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10312,6 +10293,26 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10329,10 +10330,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127161443</v>
+        <v>127157972</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10340,37 +10341,47 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540137</v>
+        <v>540038</v>
       </c>
       <c r="R82" t="n">
-        <v>7001432</v>
+        <v>7001245</v>
       </c>
       <c r="S82" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10404,7 +10415,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
+          <t>Färska och äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10433,12 +10444,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10456,38 +10467,47 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127157972</v>
+        <v>127154216</v>
       </c>
       <c r="B83" t="n">
-        <v>57658</v>
+        <v>98447</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -10497,17 +10517,17 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540038</v>
+        <v>539858</v>
       </c>
       <c r="R83" t="n">
-        <v>7001245</v>
+        <v>7001227</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10541,7 +10561,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
+          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10556,26 +10576,6 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10593,37 +10593,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127154216</v>
+        <v>127155895</v>
       </c>
       <c r="B84" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -10647,10 +10647,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>539858</v>
+        <v>539912</v>
       </c>
       <c r="R84" t="n">
-        <v>7001227</v>
+        <v>7001269</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
+          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12069,67 +12069,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127160071</v>
+        <v>127160214</v>
       </c>
       <c r="B96" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540115</v>
+        <v>540081</v>
       </c>
       <c r="R96" t="n">
-        <v>7001289</v>
+        <v>7001299</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12161,11 +12142,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12178,6 +12154,26 @@
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12195,48 +12191,67 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127160214</v>
+        <v>127160071</v>
       </c>
       <c r="B97" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540081</v>
+        <v>540115</v>
       </c>
       <c r="R97" t="n">
-        <v>7001299</v>
+        <v>7001289</v>
       </c>
       <c r="S97" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12268,6 +12283,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12280,26 +12300,6 @@
       <c r="AH97" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -2800,45 +2800,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127164774</v>
+        <v>127160270</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540022</v>
+        <v>540095</v>
       </c>
       <c r="R19" t="n">
-        <v>7001093</v>
+        <v>7001315</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2885,26 +2890,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3044,62 +3029,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127163626</v>
+        <v>127163769</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540307</v>
+        <v>540285</v>
       </c>
       <c r="R21" t="n">
-        <v>7001050</v>
+        <v>7001071</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3131,11 +3102,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3148,6 +3114,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3165,59 +3151,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127152848</v>
+        <v>127164774</v>
       </c>
       <c r="B22" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>539832</v>
+        <v>540022</v>
       </c>
       <c r="R22" t="n">
-        <v>7001265</v>
+        <v>7001093</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3264,6 +3236,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3281,10 +3273,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127160270</v>
+        <v>127163626</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3292,42 +3284,51 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540095</v>
+        <v>540307</v>
       </c>
       <c r="R23" t="n">
-        <v>7001315</v>
+        <v>7001050</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3357,6 +3358,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3388,48 +3394,62 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127163769</v>
+        <v>127152848</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>98364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540285</v>
+        <v>539832</v>
       </c>
       <c r="R24" t="n">
-        <v>7001071</v>
+        <v>7001265</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3473,26 +3493,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127163495</v>
+        <v>127158356</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3521,37 +3521,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540258</v>
+        <v>540032</v>
       </c>
       <c r="R25" t="n">
-        <v>7001065</v>
+        <v>7001287</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3609,12 +3614,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3632,67 +3637,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127155997</v>
+        <v>127163495</v>
       </c>
       <c r="B26" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539924</v>
+        <v>540258</v>
       </c>
       <c r="R26" t="n">
-        <v>7001238</v>
+        <v>7001065</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3735,7 +3721,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3753,50 +3759,64 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127158356</v>
+        <v>127155997</v>
       </c>
       <c r="B27" t="n">
-        <v>91330</v>
+        <v>98364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540032</v>
+        <v>539924</v>
       </c>
       <c r="R27" t="n">
-        <v>7001287</v>
+        <v>7001238</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3842,27 +3862,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127161580</v>
+        <v>127161738</v>
       </c>
       <c r="B33" t="n">
         <v>80121</v>
@@ -4545,7 +4545,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4554,13 +4554,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540152</v>
+        <v>540129</v>
       </c>
       <c r="R33" t="n">
-        <v>7001464</v>
+        <v>7001452</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4646,10 +4646,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127158834</v>
+        <v>127161580</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4657,34 +4657,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540033</v>
+        <v>540152</v>
       </c>
       <c r="R34" t="n">
-        <v>7001311</v>
+        <v>7001464</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4719,6 +4724,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4735,22 +4745,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4768,10 +4778,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127164937</v>
+        <v>127158834</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4779,39 +4789,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539990</v>
+        <v>540033</v>
       </c>
       <c r="R35" t="n">
-        <v>7001113</v>
+        <v>7001311</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4846,11 +4851,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4867,22 +4867,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4900,38 +4900,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127163212</v>
+        <v>127164937</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>80121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4940,13 +4940,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540253</v>
+        <v>539990</v>
       </c>
       <c r="R36" t="n">
-        <v>7001109</v>
+        <v>7001113</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4978,6 +4978,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4990,6 +4995,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5007,53 +5032,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127161738</v>
+        <v>127163212</v>
       </c>
       <c r="B37" t="n">
-        <v>80121</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540129</v>
+        <v>540253</v>
       </c>
       <c r="R37" t="n">
-        <v>7001452</v>
+        <v>7001109</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5085,11 +5110,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5102,26 +5122,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127160120</v>
+        <v>127152890</v>
       </c>
       <c r="B49" t="n">
-        <v>98780</v>
+        <v>98468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6475,42 +6475,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219880</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540106</v>
+        <v>539829</v>
       </c>
       <c r="R49" t="n">
-        <v>7001289</v>
+        <v>7001270</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6571,10 +6571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127164902</v>
+        <v>127153809</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>80157</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6582,42 +6582,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539989</v>
+        <v>539890</v>
       </c>
       <c r="R50" t="n">
-        <v>7001089</v>
+        <v>7001195</v>
       </c>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6657,6 +6657,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6673,10 +6698,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127153809</v>
+        <v>127160120</v>
       </c>
       <c r="B51" t="n">
-        <v>80157</v>
+        <v>98780</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6684,42 +6709,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>219880</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539890</v>
+        <v>540106</v>
       </c>
       <c r="R51" t="n">
-        <v>7001195</v>
+        <v>7001289</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6763,26 +6788,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6800,10 +6805,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127152890</v>
+        <v>127164902</v>
       </c>
       <c r="B52" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6811,42 +6816,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539829</v>
+        <v>539989</v>
       </c>
       <c r="R52" t="n">
-        <v>7001270</v>
+        <v>7001089</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6886,11 +6891,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6907,50 +6907,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127164425</v>
+        <v>127162675</v>
       </c>
       <c r="B53" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540128</v>
+        <v>540237</v>
       </c>
       <c r="R53" t="n">
-        <v>7001058</v>
+        <v>7001188</v>
       </c>
       <c r="S53" t="n">
         <v>11</v>
@@ -6997,6 +6992,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7014,7 +7029,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127162675</v>
+        <v>127161775</v>
       </c>
       <c r="B54" t="n">
         <v>79018</v>
@@ -7049,13 +7064,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540237</v>
+        <v>540092</v>
       </c>
       <c r="R54" t="n">
-        <v>7001188</v>
+        <v>7001443</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7136,48 +7151,62 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127161775</v>
+        <v>127163731</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540092</v>
+        <v>540303</v>
       </c>
       <c r="R55" t="n">
-        <v>7001443</v>
+        <v>7001059</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7221,26 +7250,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7258,62 +7267,58 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127163731</v>
+        <v>127159734</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540303</v>
+        <v>540115</v>
       </c>
       <c r="R56" t="n">
-        <v>7001059</v>
+        <v>7001344</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7356,7 +7361,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7374,10 +7379,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127159734</v>
+        <v>127156042</v>
       </c>
       <c r="B57" t="n">
-        <v>98364</v>
+        <v>98470</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7385,24 +7390,33 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7415,17 +7429,17 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540115</v>
+        <v>539924</v>
       </c>
       <c r="R57" t="n">
-        <v>7001344</v>
+        <v>7001238</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7486,7 +7500,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127156042</v>
+        <v>127162577</v>
       </c>
       <c r="B58" t="n">
         <v>98470</v>
@@ -7514,39 +7528,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>539924</v>
+        <v>540238</v>
       </c>
       <c r="R58" t="n">
-        <v>7001238</v>
+        <v>7001222</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7586,11 +7586,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7607,7 +7602,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127162577</v>
+        <v>127160489</v>
       </c>
       <c r="B59" t="n">
         <v>98470</v>
@@ -7647,13 +7642,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540238</v>
+        <v>540171</v>
       </c>
       <c r="R59" t="n">
-        <v>7001222</v>
+        <v>7001276</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7693,6 +7688,11 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7709,10 +7709,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127160489</v>
+        <v>127164425</v>
       </c>
       <c r="B60" t="n">
-        <v>98470</v>
+        <v>98468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7720,42 +7720,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540171</v>
+        <v>540128</v>
       </c>
       <c r="R60" t="n">
-        <v>7001276</v>
+        <v>7001058</v>
       </c>
       <c r="S60" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -9044,10 +9044,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127162146</v>
+        <v>127162549</v>
       </c>
       <c r="B71" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9055,27 +9055,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9084,13 +9084,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540106</v>
+        <v>540212</v>
       </c>
       <c r="R71" t="n">
-        <v>7001407</v>
+        <v>7001230</v>
       </c>
       <c r="S71" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9130,11 +9130,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9151,10 +9146,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127162549</v>
+        <v>127162146</v>
       </c>
       <c r="B72" t="n">
-        <v>98470</v>
+        <v>98468</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9162,27 +9157,27 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9191,13 +9186,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540212</v>
+        <v>540106</v>
       </c>
       <c r="R72" t="n">
-        <v>7001230</v>
+        <v>7001407</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9237,6 +9232,11 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9253,53 +9253,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127158202</v>
+        <v>127153185</v>
       </c>
       <c r="B73" t="n">
-        <v>91348</v>
+        <v>98780</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540038</v>
+        <v>539835</v>
       </c>
       <c r="R73" t="n">
-        <v>7001306</v>
+        <v>7001233</v>
       </c>
       <c r="S73" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9331,11 +9331,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På fyndplatsen finns rikliga mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9348,16 +9343,6 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9375,10 +9360,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127159827</v>
+        <v>127158202</v>
       </c>
       <c r="B74" t="n">
-        <v>80121</v>
+        <v>91348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9386,27 +9371,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9415,13 +9400,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540122</v>
+        <v>540038</v>
       </c>
       <c r="R74" t="n">
-        <v>7001326</v>
+        <v>7001306</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9453,6 +9438,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikliga mängder död ved.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9467,24 +9457,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9502,53 +9482,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127153185</v>
+        <v>127159827</v>
       </c>
       <c r="B75" t="n">
-        <v>98780</v>
+        <v>80121</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>539835</v>
+        <v>540122</v>
       </c>
       <c r="R75" t="n">
-        <v>7001233</v>
+        <v>7001326</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9592,6 +9572,26 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127162096</v>
+        <v>127164710</v>
       </c>
       <c r="B2" t="n">
         <v>80121</v>
@@ -706,22 +706,22 @@
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540104</v>
+        <v>540011</v>
       </c>
       <c r="R2" t="n">
-        <v>7001431</v>
+        <v>7001079</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,7 +807,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127160294</v>
+        <v>127162096</v>
       </c>
       <c r="B3" t="n">
         <v>80121</v>
@@ -838,7 +838,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540092</v>
+        <v>540104</v>
       </c>
       <c r="R3" t="n">
-        <v>7001341</v>
+        <v>7001431</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +885,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på två sälgar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -911,12 +916,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,32 +939,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127162017</v>
+        <v>127160294</v>
       </c>
       <c r="B4" t="n">
-        <v>80156</v>
+        <v>80121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540111</v>
+        <v>540092</v>
       </c>
       <c r="R4" t="n">
-        <v>7001420</v>
+        <v>7001341</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1038,12 +1043,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,43 +1066,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127158784</v>
+        <v>127162017</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>80156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540039</v>
+        <v>540111</v>
       </c>
       <c r="R5" t="n">
-        <v>7001341</v>
+        <v>7001420</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,26 +1139,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1175,22 +1160,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1208,47 +1193,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127161646</v>
+        <v>127158784</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1257,13 +1238,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540139</v>
+        <v>540039</v>
       </c>
       <c r="R6" t="n">
-        <v>7001452</v>
+        <v>7001341</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1290,14 +1271,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1312,6 +1303,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1329,53 +1340,58 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127163443</v>
+        <v>127153536</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540255</v>
+        <v>539859</v>
       </c>
       <c r="R7" t="n">
-        <v>7001070</v>
+        <v>7001178</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1407,6 +1423,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1415,6 +1436,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1431,38 +1457,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127162604</v>
+        <v>127161646</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1471,13 +1506,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540240</v>
+        <v>540139</v>
       </c>
       <c r="R8" t="n">
-        <v>7001210</v>
+        <v>7001452</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,6 +1544,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1517,6 +1557,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1533,10 +1578,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127162418</v>
+        <v>127162604</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>98365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,27 +1589,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219880</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1573,10 +1618,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540127</v>
+        <v>540240</v>
       </c>
       <c r="R9" t="n">
-        <v>7001264</v>
+        <v>7001210</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1619,11 +1664,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1640,58 +1680,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127153536</v>
+        <v>127163443</v>
       </c>
       <c r="B10" t="n">
-        <v>57658</v>
+        <v>98471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539859</v>
+        <v>540255</v>
       </c>
       <c r="R10" t="n">
-        <v>7001178</v>
+        <v>7001070</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,11 +1758,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1736,11 +1766,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1757,53 +1782,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127164710</v>
+        <v>127162418</v>
       </c>
       <c r="B11" t="n">
-        <v>80121</v>
+        <v>98781</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540011</v>
+        <v>540127</v>
       </c>
       <c r="R11" t="n">
-        <v>7001079</v>
+        <v>7001264</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1835,11 +1860,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1852,26 +1872,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2152,37 +2152,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127162375</v>
+        <v>127155767</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2192,22 +2192,27 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540115</v>
+        <v>539895</v>
       </c>
       <c r="R14" t="n">
-        <v>7001309</v>
+        <v>7001284</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2241,7 +2246,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2273,37 +2278,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155767</v>
+        <v>127162375</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2313,27 +2318,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539895</v>
+        <v>540115</v>
       </c>
       <c r="R15" t="n">
-        <v>7001284</v>
+        <v>7001309</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2803,7 +2803,7 @@
         <v>127160270</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127153666</v>
+        <v>127164774</v>
       </c>
       <c r="B20" t="n">
         <v>79018</v>
@@ -2938,17 +2938,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539888</v>
+        <v>540022</v>
       </c>
       <c r="R20" t="n">
-        <v>7001166</v>
+        <v>7001093</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127163769</v>
+        <v>127153666</v>
       </c>
       <c r="B21" t="n">
         <v>79018</v>
@@ -3060,17 +3060,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540285</v>
+        <v>539888</v>
       </c>
       <c r="R21" t="n">
-        <v>7001071</v>
+        <v>7001166</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3128,12 +3128,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127164774</v>
+        <v>127163769</v>
       </c>
       <c r="B22" t="n">
         <v>79018</v>
@@ -3186,13 +3186,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540022</v>
+        <v>540285</v>
       </c>
       <c r="R22" t="n">
-        <v>7001093</v>
+        <v>7001071</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>127163626</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>127152848</v>
       </c>
       <c r="B24" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3510,50 +3510,64 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127158356</v>
+        <v>127155997</v>
       </c>
       <c r="B25" t="n">
-        <v>91330</v>
+        <v>98365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540032</v>
+        <v>539924</v>
       </c>
       <c r="R25" t="n">
-        <v>7001287</v>
+        <v>7001238</v>
       </c>
       <c r="S25" t="n">
         <v>9</v>
@@ -3599,27 +3613,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3637,10 +3631,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127163495</v>
+        <v>127158356</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3648,37 +3642,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540258</v>
+        <v>540032</v>
       </c>
       <c r="R26" t="n">
-        <v>7001065</v>
+        <v>7001287</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3736,12 +3735,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3759,67 +3758,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127155997</v>
+        <v>127163495</v>
       </c>
       <c r="B27" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539924</v>
+        <v>540258</v>
       </c>
       <c r="R27" t="n">
-        <v>7001238</v>
+        <v>7001065</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3862,7 +3842,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3880,48 +3880,67 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153018</v>
+        <v>127153897</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539829</v>
+        <v>539873</v>
       </c>
       <c r="R28" t="n">
-        <v>7001270</v>
+        <v>7001197</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3953,6 +3972,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3965,26 +3989,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4388,67 +4392,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127153897</v>
+        <v>127153018</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539873</v>
+        <v>539829</v>
       </c>
       <c r="R32" t="n">
-        <v>7001197</v>
+        <v>7001270</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4480,11 +4465,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4497,6 +4477,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127158834</v>
+        <v>127164937</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4789,34 +4789,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540033</v>
+        <v>539990</v>
       </c>
       <c r="R35" t="n">
-        <v>7001311</v>
+        <v>7001113</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4851,6 +4856,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4867,22 +4877,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4900,10 +4910,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127164937</v>
+        <v>127158834</v>
       </c>
       <c r="B36" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4911,39 +4921,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539990</v>
+        <v>540033</v>
       </c>
       <c r="R36" t="n">
-        <v>7001113</v>
+        <v>7001311</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4978,11 +4983,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4999,22 +4999,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5035,7 +5035,7 @@
         <v>127163212</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127164835</v>
+        <v>127154714</v>
       </c>
       <c r="B38" t="n">
         <v>80121</v>
@@ -5175,17 +5175,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539992</v>
+        <v>539872</v>
       </c>
       <c r="R38" t="n">
-        <v>7001093</v>
+        <v>7001243</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+          <t>Lunglav på 3 gamla sälgar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5271,10 +5271,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127164541</v>
+        <v>127164835</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5282,34 +5282,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540113</v>
+        <v>539992</v>
       </c>
       <c r="R39" t="n">
-        <v>7001087</v>
+        <v>7001093</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5344,6 +5349,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5360,22 +5370,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5393,7 +5403,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127154714</v>
+        <v>127153765</v>
       </c>
       <c r="B40" t="n">
         <v>80121</v>
@@ -5424,7 +5434,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5433,13 +5443,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539872</v>
+        <v>539879</v>
       </c>
       <c r="R40" t="n">
-        <v>7001243</v>
+        <v>7001196</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5473,7 +5483,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Lunglav på 3 gamla sälgar.</t>
+          <t>Fertil lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5525,10 +5535,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153765</v>
+        <v>127164541</v>
       </c>
       <c r="B41" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5536,42 +5546,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539879</v>
+        <v>540113</v>
       </c>
       <c r="R41" t="n">
-        <v>7001196</v>
+        <v>7001087</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5603,11 +5608,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5624,22 +5624,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127162532</v>
+        <v>127164613</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5668,34 +5668,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540214</v>
+        <v>540079</v>
       </c>
       <c r="R42" t="n">
-        <v>7001228</v>
+        <v>7001087</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5746,22 +5751,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5779,10 +5784,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127164613</v>
+        <v>127162532</v>
       </c>
       <c r="B43" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5790,39 +5795,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540079</v>
+        <v>540214</v>
       </c>
       <c r="R43" t="n">
-        <v>7001087</v>
+        <v>7001228</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5873,22 +5873,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5906,53 +5906,62 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127163137</v>
+        <v>127158031</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>98365</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540285</v>
+        <v>540047</v>
       </c>
       <c r="R44" t="n">
-        <v>7001126</v>
+        <v>7001245</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5984,6 +5993,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Vid en bäck på en gammal väg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5992,6 +6006,11 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6011,7 +6030,7 @@
         <v>127163976</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6110,62 +6129,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127158031</v>
+        <v>127163137</v>
       </c>
       <c r="B46" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540047</v>
+        <v>540285</v>
       </c>
       <c r="R46" t="n">
-        <v>7001245</v>
+        <v>7001126</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6197,11 +6207,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Vid en bäck på en gammal väg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6210,11 +6215,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6234,7 +6234,7 @@
         <v>127162701</v>
       </c>
       <c r="B47" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6338,52 +6338,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127153495</v>
+        <v>127153809</v>
       </c>
       <c r="B48" t="n">
-        <v>98447</v>
+        <v>80157</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6392,13 +6378,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539858</v>
+        <v>539890</v>
       </c>
       <c r="R48" t="n">
-        <v>7001193</v>
+        <v>7001195</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6430,11 +6416,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6447,6 +6428,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6464,10 +6465,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127152890</v>
+        <v>127160120</v>
       </c>
       <c r="B49" t="n">
-        <v>98468</v>
+        <v>98781</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6475,42 +6476,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>219880</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539829</v>
+        <v>540106</v>
       </c>
       <c r="R49" t="n">
-        <v>7001270</v>
+        <v>7001289</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6571,10 +6572,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127153809</v>
+        <v>127164902</v>
       </c>
       <c r="B50" t="n">
-        <v>80157</v>
+        <v>98471</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6582,42 +6583,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539890</v>
+        <v>539989</v>
       </c>
       <c r="R50" t="n">
-        <v>7001195</v>
+        <v>7001089</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6657,31 +6658,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6698,53 +6674,67 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127160120</v>
+        <v>127153495</v>
       </c>
       <c r="B51" t="n">
-        <v>98780</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540106</v>
+        <v>539858</v>
       </c>
       <c r="R51" t="n">
-        <v>7001289</v>
+        <v>7001193</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6774,6 +6764,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6805,10 +6800,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127164902</v>
+        <v>127152890</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>98469</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6816,42 +6811,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539989</v>
+        <v>539829</v>
       </c>
       <c r="R52" t="n">
-        <v>7001089</v>
+        <v>7001270</v>
       </c>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6891,6 +6886,11 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7151,62 +7151,58 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127163731</v>
+        <v>127159734</v>
       </c>
       <c r="B55" t="n">
-        <v>98447</v>
+        <v>98365</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540303</v>
+        <v>540115</v>
       </c>
       <c r="R55" t="n">
-        <v>7001059</v>
+        <v>7001344</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7249,7 +7245,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7267,10 +7263,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127159734</v>
+        <v>127156042</v>
       </c>
       <c r="B56" t="n">
-        <v>98364</v>
+        <v>98471</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7278,24 +7274,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7308,17 +7313,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540115</v>
+        <v>539924</v>
       </c>
       <c r="R56" t="n">
-        <v>7001344</v>
+        <v>7001238</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7379,10 +7384,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127156042</v>
+        <v>127162577</v>
       </c>
       <c r="B57" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7407,39 +7412,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539924</v>
+        <v>540238</v>
       </c>
       <c r="R57" t="n">
-        <v>7001238</v>
+        <v>7001222</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7479,11 +7470,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7500,10 +7486,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127162577</v>
+        <v>127160489</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7540,13 +7526,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540238</v>
+        <v>540171</v>
       </c>
       <c r="R58" t="n">
-        <v>7001222</v>
+        <v>7001276</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7586,6 +7572,11 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7602,10 +7593,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127160489</v>
+        <v>127164425</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>98469</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7613,42 +7604,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540171</v>
+        <v>540128</v>
       </c>
       <c r="R59" t="n">
-        <v>7001276</v>
+        <v>7001058</v>
       </c>
       <c r="S59" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7709,38 +7700,47 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127164425</v>
+        <v>127163731</v>
       </c>
       <c r="B60" t="n">
-        <v>98468</v>
+        <v>98448</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7749,13 +7749,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540128</v>
+        <v>540303</v>
       </c>
       <c r="R60" t="n">
-        <v>7001058</v>
+        <v>7001059</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>127158943</v>
       </c>
       <c r="B63" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>127160736</v>
       </c>
       <c r="B67" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8821,10 +8821,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127164741</v>
+        <v>127155980</v>
       </c>
       <c r="B69" t="n">
-        <v>98364</v>
+        <v>98471</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8832,42 +8832,56 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540004</v>
+        <v>539933</v>
       </c>
       <c r="R69" t="n">
-        <v>7001090</v>
+        <v>7001238</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8907,6 +8921,11 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8923,10 +8942,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127155980</v>
+        <v>127162549</v>
       </c>
       <c r="B70" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8951,39 +8970,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539933</v>
+        <v>540212</v>
       </c>
       <c r="R70" t="n">
-        <v>7001238</v>
+        <v>7001230</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9023,11 +9028,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9044,10 +9044,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127162549</v>
+        <v>127164741</v>
       </c>
       <c r="B71" t="n">
-        <v>98470</v>
+        <v>98365</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9055,21 +9055,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9080,17 +9080,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540212</v>
+        <v>540004</v>
       </c>
       <c r="R71" t="n">
-        <v>7001230</v>
+        <v>7001090</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>127162146</v>
       </c>
       <c r="B72" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>127153185</v>
       </c>
       <c r="B73" t="n">
-        <v>98780</v>
+        <v>98781</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127158202</v>
+        <v>127159827</v>
       </c>
       <c r="B74" t="n">
-        <v>91348</v>
+        <v>80121</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9371,27 +9371,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9400,13 +9400,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540038</v>
+        <v>540122</v>
       </c>
       <c r="R74" t="n">
-        <v>7001306</v>
+        <v>7001326</v>
       </c>
       <c r="S74" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9438,11 +9438,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På fyndplatsen finns rikliga mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9457,14 +9452,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9482,10 +9487,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127159827</v>
+        <v>127158202</v>
       </c>
       <c r="B75" t="n">
-        <v>80121</v>
+        <v>91348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9493,27 +9498,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9522,13 +9527,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540122</v>
+        <v>540038</v>
       </c>
       <c r="R75" t="n">
-        <v>7001326</v>
+        <v>7001306</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9560,6 +9565,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikliga mängder död ved.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9574,24 +9584,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9731,10 +9731,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127163162</v>
+        <v>127162730</v>
       </c>
       <c r="B77" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9759,7 +9759,16 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9767,17 +9776,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540247</v>
+        <v>540258</v>
       </c>
       <c r="R77" t="n">
-        <v>7001094</v>
+        <v>7001179</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9817,6 +9826,11 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9833,10 +9847,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127162730</v>
+        <v>127163162</v>
       </c>
       <c r="B78" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9861,16 +9875,7 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9878,17 +9883,17 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540258</v>
+        <v>540247</v>
       </c>
       <c r="R78" t="n">
-        <v>7001179</v>
+        <v>7001094</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9928,11 +9933,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9949,10 +9949,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127161443</v>
+        <v>127157972</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9960,37 +9960,47 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540137</v>
+        <v>540038</v>
       </c>
       <c r="R79" t="n">
-        <v>7001432</v>
+        <v>7001245</v>
       </c>
       <c r="S79" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10024,7 +10034,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
+          <t>Färska och äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10053,12 +10063,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10076,7 +10086,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127156896</v>
+        <v>127161443</v>
       </c>
       <c r="B80" t="n">
         <v>79018</v>
@@ -10105,24 +10115,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>539983</v>
+        <v>540137</v>
       </c>
       <c r="R80" t="n">
-        <v>7001163</v>
+        <v>7001432</v>
       </c>
       <c r="S80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10156,7 +10161,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Långväxta och fertila bålar på flera granar.</t>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10208,7 +10213,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127160558</v>
+        <v>127156896</v>
       </c>
       <c r="B81" t="n">
         <v>79018</v>
@@ -10237,19 +10242,24 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540205</v>
+        <v>539983</v>
       </c>
       <c r="R81" t="n">
-        <v>7001321</v>
+        <v>7001163</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10279,6 +10289,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10330,10 +10345,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127157972</v>
+        <v>127160558</v>
       </c>
       <c r="B82" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10341,47 +10356,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540038</v>
+        <v>540205</v>
       </c>
       <c r="R82" t="n">
-        <v>7001245</v>
+        <v>7001321</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10413,11 +10418,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10444,12 +10444,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10467,37 +10467,37 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127154216</v>
+        <v>127155895</v>
       </c>
       <c r="B83" t="n">
-        <v>98447</v>
+        <v>98365</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -10521,10 +10521,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>539858</v>
+        <v>539912</v>
       </c>
       <c r="R83" t="n">
-        <v>7001227</v>
+        <v>7001269</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
+          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10593,37 +10593,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127155895</v>
+        <v>127154216</v>
       </c>
       <c r="B84" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -10647,10 +10647,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>539912</v>
+        <v>539858</v>
       </c>
       <c r="R84" t="n">
-        <v>7001269</v>
+        <v>7001227</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
+          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10719,48 +10719,62 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127164354</v>
+        <v>127160670</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>98471</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540166</v>
+        <v>540195</v>
       </c>
       <c r="R85" t="n">
-        <v>7001045</v>
+        <v>7001331</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10792,6 +10806,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10804,26 +10823,6 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10841,62 +10840,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127160670</v>
+        <v>127164354</v>
       </c>
       <c r="B86" t="n">
-        <v>98470</v>
+        <v>79018</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540195</v>
+        <v>540166</v>
       </c>
       <c r="R86" t="n">
-        <v>7001331</v>
+        <v>7001045</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10928,11 +10913,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10945,6 +10925,26 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10965,7 +10965,7 @@
         <v>127155804</v>
       </c>
       <c r="B87" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>127163738</v>
       </c>
       <c r="B88" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>127159714</v>
       </c>
       <c r="B89" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11307,10 +11307,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127157856</v>
+        <v>127157226</v>
       </c>
       <c r="B90" t="n">
-        <v>98353</v>
+        <v>98471</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11318,26 +11318,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11350,7 +11350,6 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11362,13 +11361,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539984</v>
+        <v>539976</v>
       </c>
       <c r="R90" t="n">
-        <v>7001243</v>
+        <v>7001240</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11395,33 +11394,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11445,10 +11428,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127157226</v>
+        <v>127157856</v>
       </c>
       <c r="B91" t="n">
-        <v>98470</v>
+        <v>98354</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11456,26 +11439,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11488,6 +11471,7 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11499,13 +11483,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>539976</v>
+        <v>539984</v>
       </c>
       <c r="R91" t="n">
-        <v>7001240</v>
+        <v>7001243</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11532,17 +11516,33 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>127159972</v>
       </c>
       <c r="B92" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>127155729</v>
       </c>
       <c r="B93" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>127157050</v>
       </c>
       <c r="B95" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>127160071</v>
       </c>
       <c r="B97" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>127155870</v>
       </c>
       <c r="B98" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>127164256</v>
       </c>
       <c r="B99" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>127157299</v>
       </c>
       <c r="B100" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>127162786</v>
       </c>
       <c r="B101" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -2399,10 +2399,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127161347</v>
+        <v>127159187</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2410,27 +2410,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2439,13 +2444,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540157</v>
+        <v>540057</v>
       </c>
       <c r="R16" t="n">
-        <v>7001411</v>
+        <v>7001353</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2472,14 +2477,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Fertil garnlav å gran.</t>
+          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,12 +2523,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2531,7 +2546,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127160480</v>
+        <v>127161347</v>
       </c>
       <c r="B17" t="n">
         <v>79018</v>
@@ -2560,19 +2575,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540188</v>
+        <v>540157</v>
       </c>
       <c r="R17" t="n">
-        <v>7001269</v>
+        <v>7001411</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2602,6 +2622,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2653,10 +2678,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127159187</v>
+        <v>127160480</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2664,47 +2689,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540057</v>
+        <v>540188</v>
       </c>
       <c r="R18" t="n">
-        <v>7001353</v>
+        <v>7001269</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2731,26 +2746,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127158031</v>
+        <v>127162701</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5917,33 +5917,24 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -5951,17 +5942,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540047</v>
+        <v>540246</v>
       </c>
       <c r="R44" t="n">
-        <v>7001245</v>
+        <v>7001169</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5991,11 +5982,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Vid en bäck på en gammal väg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6027,10 +6013,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127163976</v>
+        <v>127158031</v>
       </c>
       <c r="B45" t="n">
-        <v>98471</v>
+        <v>98365</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6038,24 +6024,33 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -6063,17 +6058,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540285</v>
+        <v>540047</v>
       </c>
       <c r="R45" t="n">
-        <v>7001072</v>
+        <v>7001245</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6105,6 +6100,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Vid en bäck på en gammal väg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6113,6 +6113,11 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6129,38 +6134,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127163137</v>
+        <v>127163976</v>
       </c>
       <c r="B46" t="n">
-        <v>98448</v>
+        <v>98471</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6172,7 +6177,7 @@
         <v>540285</v>
       </c>
       <c r="R46" t="n">
-        <v>7001126</v>
+        <v>7001072</v>
       </c>
       <c r="S46" t="n">
         <v>7</v>
@@ -6231,38 +6236,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127162701</v>
+        <v>127163137</v>
       </c>
       <c r="B47" t="n">
-        <v>98469</v>
+        <v>98448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6271,13 +6276,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540246</v>
+        <v>540285</v>
       </c>
       <c r="R47" t="n">
-        <v>7001169</v>
+        <v>7001126</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6317,11 +6322,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -8460,38 +8460,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127160440</v>
+        <v>127160736</v>
       </c>
       <c r="B66" t="n">
-        <v>91784</v>
+        <v>98469</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540128</v>
+        <v>540193</v>
       </c>
       <c r="R66" t="n">
-        <v>7001287</v>
+        <v>7001357</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8538,11 +8538,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8555,26 +8550,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8592,38 +8567,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127160736</v>
+        <v>127160440</v>
       </c>
       <c r="B67" t="n">
-        <v>98469</v>
+        <v>91784</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8632,13 +8607,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540193</v>
+        <v>540128</v>
       </c>
       <c r="R67" t="n">
-        <v>7001357</v>
+        <v>7001287</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8670,6 +8645,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8682,6 +8662,26 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127155980</v>
+        <v>127162146</v>
       </c>
       <c r="B69" t="n">
-        <v>98471</v>
+        <v>98469</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8832,56 +8832,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539933</v>
+        <v>540106</v>
       </c>
       <c r="R69" t="n">
-        <v>7001238</v>
+        <v>7001407</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8942,7 +8928,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127162549</v>
+        <v>127155980</v>
       </c>
       <c r="B70" t="n">
         <v>98471</v>
@@ -8970,25 +8956,39 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540212</v>
+        <v>539933</v>
       </c>
       <c r="R70" t="n">
-        <v>7001230</v>
+        <v>7001238</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9028,6 +9028,11 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9044,10 +9049,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127164741</v>
+        <v>127162549</v>
       </c>
       <c r="B71" t="n">
-        <v>98365</v>
+        <v>98471</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9055,21 +9060,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9080,17 +9085,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540004</v>
+        <v>540212</v>
       </c>
       <c r="R71" t="n">
-        <v>7001090</v>
+        <v>7001230</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9146,10 +9151,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127162146</v>
+        <v>127164741</v>
       </c>
       <c r="B72" t="n">
-        <v>98469</v>
+        <v>98365</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9157,42 +9162,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540106</v>
+        <v>540004</v>
       </c>
       <c r="R72" t="n">
-        <v>7001407</v>
+        <v>7001090</v>
       </c>
       <c r="S72" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9232,11 +9237,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9609,48 +9609,62 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127154622</v>
+        <v>127162730</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>98365</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>539897</v>
+        <v>540258</v>
       </c>
       <c r="R76" t="n">
-        <v>7001240</v>
+        <v>7001179</v>
       </c>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9694,26 +9708,6 @@
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9731,7 +9725,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127162730</v>
+        <v>127163162</v>
       </c>
       <c r="B77" t="n">
         <v>98365</v>
@@ -9759,16 +9753,7 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9776,17 +9761,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540258</v>
+        <v>540247</v>
       </c>
       <c r="R77" t="n">
-        <v>7001179</v>
+        <v>7001094</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9826,11 +9811,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9847,53 +9827,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127163162</v>
+        <v>127154622</v>
       </c>
       <c r="B78" t="n">
-        <v>98365</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540247</v>
+        <v>539897</v>
       </c>
       <c r="R78" t="n">
-        <v>7001094</v>
+        <v>7001240</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9933,6 +9908,31 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9949,10 +9949,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127157972</v>
+        <v>127161443</v>
       </c>
       <c r="B79" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9960,47 +9960,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540038</v>
+        <v>540137</v>
       </c>
       <c r="R79" t="n">
-        <v>7001245</v>
+        <v>7001432</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10034,7 +10024,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10063,12 +10053,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10086,7 +10076,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127161443</v>
+        <v>127156896</v>
       </c>
       <c r="B80" t="n">
         <v>79018</v>
@@ -10115,19 +10105,24 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540137</v>
+        <v>539983</v>
       </c>
       <c r="R80" t="n">
-        <v>7001432</v>
+        <v>7001163</v>
       </c>
       <c r="S80" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10161,7 +10156,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
+          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10213,7 +10208,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127156896</v>
+        <v>127160558</v>
       </c>
       <c r="B81" t="n">
         <v>79018</v>
@@ -10242,24 +10237,19 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>539983</v>
+        <v>540205</v>
       </c>
       <c r="R81" t="n">
-        <v>7001163</v>
+        <v>7001321</v>
       </c>
       <c r="S81" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10289,11 +10279,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10345,45 +10330,64 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127160558</v>
+        <v>127155895</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>98365</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540205</v>
+        <v>539912</v>
       </c>
       <c r="R82" t="n">
-        <v>7001321</v>
+        <v>7001269</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10418,6 +10422,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10430,26 +10439,6 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10467,37 +10456,37 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127155895</v>
+        <v>127154216</v>
       </c>
       <c r="B83" t="n">
-        <v>98365</v>
+        <v>98448</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10507,7 +10496,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -10521,10 +10510,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>539912</v>
+        <v>539858</v>
       </c>
       <c r="R83" t="n">
-        <v>7001269</v>
+        <v>7001227</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10561,7 +10550,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
+          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10593,47 +10582,38 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127154216</v>
+        <v>127157972</v>
       </c>
       <c r="B84" t="n">
-        <v>98448</v>
+        <v>57658</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -10643,17 +10623,17 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>539858</v>
+        <v>540038</v>
       </c>
       <c r="R84" t="n">
-        <v>7001227</v>
+        <v>7001245</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10687,7 +10667,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
+          <t>Färska och äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10702,6 +10682,26 @@
       <c r="AH84" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10719,62 +10719,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127160670</v>
+        <v>127164354</v>
       </c>
       <c r="B85" t="n">
-        <v>98471</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540195</v>
+        <v>540166</v>
       </c>
       <c r="R85" t="n">
-        <v>7001331</v>
+        <v>7001045</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10806,11 +10792,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10823,6 +10804,26 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10840,48 +10841,62 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127164354</v>
+        <v>127160670</v>
       </c>
       <c r="B86" t="n">
-        <v>79018</v>
+        <v>98471</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540166</v>
+        <v>540195</v>
       </c>
       <c r="R86" t="n">
-        <v>7001045</v>
+        <v>7001331</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10913,6 +10928,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10925,26 +10945,6 @@
       <c r="AH86" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127164710</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>127162096</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>127160294</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>127162017</v>
       </c>
       <c r="B5" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>127158784</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127153536</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>127161646</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127162604</v>
+        <v>127163443</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540240</v>
+        <v>540255</v>
       </c>
       <c r="R9" t="n">
-        <v>7001210</v>
+        <v>7001070</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127163443</v>
+        <v>127162604</v>
       </c>
       <c r="B10" t="n">
-        <v>98471</v>
+        <v>98367</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,21 +1691,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1716,17 +1716,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540255</v>
+        <v>540240</v>
       </c>
       <c r="R10" t="n">
-        <v>7001070</v>
+        <v>7001210</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>127162418</v>
       </c>
       <c r="B11" t="n">
-        <v>98781</v>
+        <v>98783</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127154593</v>
       </c>
       <c r="B12" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2021,47 +2021,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127160359</v>
+        <v>127162375</v>
       </c>
       <c r="B13" t="n">
-        <v>57821</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540139</v>
+        <v>540115</v>
       </c>
       <c r="R13" t="n">
-        <v>7001298</v>
+        <v>7001309</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2103,24 +2103,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2152,47 +2142,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127155767</v>
+        <v>127160359</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2202,17 +2187,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539895</v>
+        <v>540139</v>
       </c>
       <c r="R14" t="n">
-        <v>7001284</v>
+        <v>7001298</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2239,14 +2224,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2278,37 +2273,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127162375</v>
+        <v>127155767</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>98367</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2318,22 +2313,27 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540115</v>
+        <v>539895</v>
       </c>
       <c r="R15" t="n">
-        <v>7001309</v>
+        <v>7001284</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2399,10 +2399,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127159187</v>
+        <v>127161347</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2410,32 +2410,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2444,13 +2439,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540057</v>
+        <v>540157</v>
       </c>
       <c r="R16" t="n">
-        <v>7001353</v>
+        <v>7001411</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2477,24 +2472,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
+          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,12 +2508,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2546,10 +2531,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127161347</v>
+        <v>127159187</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,27 +2542,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2586,13 +2576,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540157</v>
+        <v>540057</v>
       </c>
       <c r="R17" t="n">
-        <v>7001411</v>
+        <v>7001353</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2619,14 +2609,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Fertil garnlav å gran.</t>
+          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2681,7 +2681,7 @@
         <v>127160480</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127160270</v>
+        <v>127163626</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2811,42 +2811,51 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540095</v>
+        <v>540307</v>
       </c>
       <c r="R19" t="n">
-        <v>7001315</v>
+        <v>7001050</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2876,6 +2885,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2907,45 +2921,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127164774</v>
+        <v>127152848</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>98367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540022</v>
+        <v>539832</v>
       </c>
       <c r="R20" t="n">
-        <v>7001093</v>
+        <v>7001265</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -2992,26 +3020,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3029,48 +3037,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127153666</v>
+        <v>127160270</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>98471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539888</v>
+        <v>540095</v>
       </c>
       <c r="R21" t="n">
-        <v>7001166</v>
+        <v>7001315</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3114,26 +3127,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3151,10 +3144,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127163769</v>
+        <v>127164774</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3186,13 +3179,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540285</v>
+        <v>540022</v>
       </c>
       <c r="R22" t="n">
-        <v>7001071</v>
+        <v>7001093</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3273,62 +3266,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127163626</v>
+        <v>127153666</v>
       </c>
       <c r="B23" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540307</v>
+        <v>539888</v>
       </c>
       <c r="R23" t="n">
-        <v>7001050</v>
+        <v>7001166</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3360,11 +3339,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3377,6 +3351,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3394,62 +3388,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127152848</v>
+        <v>127163769</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539832</v>
+        <v>540285</v>
       </c>
       <c r="R24" t="n">
-        <v>7001265</v>
+        <v>7001071</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3493,6 +3473,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3510,67 +3510,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127155997</v>
+        <v>127163495</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>539924</v>
+        <v>540258</v>
       </c>
       <c r="R25" t="n">
-        <v>7001238</v>
+        <v>7001065</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3613,7 +3594,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3634,7 +3635,7 @@
         <v>127158356</v>
       </c>
       <c r="B26" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3758,48 +3759,67 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127163495</v>
+        <v>127155997</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>98367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540258</v>
+        <v>539924</v>
       </c>
       <c r="R27" t="n">
-        <v>7001065</v>
+        <v>7001238</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3842,27 +3862,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3883,7 +3883,7 @@
         <v>127153897</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4006,53 +4006,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153641</v>
+        <v>127153018</v>
       </c>
       <c r="B29" t="n">
-        <v>80150</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539864</v>
+        <v>539829</v>
       </c>
       <c r="R29" t="n">
-        <v>7001177</v>
+        <v>7001270</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4100,22 +4095,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4133,38 +4128,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127153581</v>
+        <v>127153641</v>
       </c>
       <c r="B30" t="n">
-        <v>80121</v>
+        <v>80152</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4173,13 +4168,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539872</v>
+        <v>539864</v>
       </c>
       <c r="R30" t="n">
-        <v>7001176</v>
+        <v>7001177</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4260,10 +4255,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127160821</v>
+        <v>127153581</v>
       </c>
       <c r="B31" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4296,14 +4291,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540188</v>
+        <v>539872</v>
       </c>
       <c r="R31" t="n">
-        <v>7001373</v>
+        <v>7001176</v>
       </c>
       <c r="S31" t="n">
         <v>12</v>
@@ -4336,11 +4331,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en upplyft liggande levande sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4392,10 +4382,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127153018</v>
+        <v>127160821</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4403,37 +4393,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>539829</v>
+        <v>540188</v>
       </c>
       <c r="R32" t="n">
-        <v>7001270</v>
+        <v>7001373</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4465,6 +4460,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På en upplyft liggande levande sälg.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4481,22 +4481,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4514,53 +4514,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127161738</v>
+        <v>127163212</v>
       </c>
       <c r="B33" t="n">
-        <v>80121</v>
+        <v>98473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540129</v>
+        <v>540253</v>
       </c>
       <c r="R33" t="n">
-        <v>7001452</v>
+        <v>7001109</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4592,11 +4592,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4609,26 +4604,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4646,10 +4621,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127161580</v>
+        <v>127161738</v>
       </c>
       <c r="B34" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4677,7 +4652,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4686,13 +4661,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540152</v>
+        <v>540129</v>
       </c>
       <c r="R34" t="n">
-        <v>7001464</v>
+        <v>7001452</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4726,7 +4701,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4778,10 +4753,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127164937</v>
+        <v>127161580</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4809,19 +4784,19 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539990</v>
+        <v>540152</v>
       </c>
       <c r="R35" t="n">
-        <v>7001113</v>
+        <v>7001464</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4858,7 +4833,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
+          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4913,7 +4888,7 @@
         <v>127158834</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5032,38 +5007,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127163212</v>
+        <v>127164937</v>
       </c>
       <c r="B37" t="n">
-        <v>98471</v>
+        <v>80123</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5072,13 +5047,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540253</v>
+        <v>539990</v>
       </c>
       <c r="R37" t="n">
-        <v>7001109</v>
+        <v>7001113</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5110,6 +5085,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5122,6 +5102,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5142,7 +5142,7 @@
         <v>127154714</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5271,10 +5271,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127164835</v>
+        <v>127153765</v>
       </c>
       <c r="B39" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5302,22 +5302,22 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539992</v>
+        <v>539879</v>
       </c>
       <c r="R39" t="n">
-        <v>7001093</v>
+        <v>7001196</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+          <t>Fertil lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5403,10 +5403,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153765</v>
+        <v>127164541</v>
       </c>
       <c r="B40" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5414,42 +5414,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539879</v>
+        <v>540113</v>
       </c>
       <c r="R40" t="n">
-        <v>7001196</v>
+        <v>7001087</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5481,11 +5476,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5502,22 +5492,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5535,10 +5525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127164541</v>
+        <v>127164835</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5546,34 +5536,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540113</v>
+        <v>539992</v>
       </c>
       <c r="R41" t="n">
-        <v>7001087</v>
+        <v>7001093</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5608,6 +5603,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5624,22 +5624,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127164613</v>
+        <v>127162532</v>
       </c>
       <c r="B42" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5668,39 +5668,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540079</v>
+        <v>540214</v>
       </c>
       <c r="R42" t="n">
-        <v>7001087</v>
+        <v>7001228</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5751,22 +5746,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5784,10 +5779,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127162532</v>
+        <v>127164613</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5795,34 +5790,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540214</v>
+        <v>540079</v>
       </c>
       <c r="R43" t="n">
-        <v>7001228</v>
+        <v>7001087</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5873,22 +5873,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127162701</v>
+        <v>127163976</v>
       </c>
       <c r="B44" t="n">
-        <v>98469</v>
+        <v>98473</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5946,13 +5946,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540246</v>
+        <v>540285</v>
       </c>
       <c r="R44" t="n">
-        <v>7001169</v>
+        <v>7001072</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5992,11 +5992,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6016,7 +6011,7 @@
         <v>127158031</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6134,7 +6129,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127163976</v>
+        <v>127162701</v>
       </c>
       <c r="B46" t="n">
         <v>98471</v>
@@ -6145,21 +6140,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6174,13 +6169,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540285</v>
+        <v>540246</v>
       </c>
       <c r="R46" t="n">
-        <v>7001072</v>
+        <v>7001169</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6220,6 +6215,11 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6239,7 +6239,7 @@
         <v>127163137</v>
       </c>
       <c r="B47" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6338,10 +6338,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127153809</v>
+        <v>127160120</v>
       </c>
       <c r="B48" t="n">
-        <v>80157</v>
+        <v>98783</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6349,42 +6349,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>219880</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>539890</v>
+        <v>540106</v>
       </c>
       <c r="R48" t="n">
-        <v>7001195</v>
+        <v>7001289</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6428,26 +6428,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6465,10 +6445,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127160120</v>
+        <v>127164902</v>
       </c>
       <c r="B49" t="n">
-        <v>98781</v>
+        <v>98473</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6476,42 +6456,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540106</v>
+        <v>539989</v>
       </c>
       <c r="R49" t="n">
-        <v>7001289</v>
+        <v>7001089</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6551,11 +6531,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6572,53 +6547,67 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127164902</v>
+        <v>127153495</v>
       </c>
       <c r="B50" t="n">
-        <v>98471</v>
+        <v>98450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539989</v>
+        <v>539858</v>
       </c>
       <c r="R50" t="n">
-        <v>7001089</v>
+        <v>7001193</v>
       </c>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6650,6 +6639,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6658,6 +6652,11 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6674,52 +6673,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127153495</v>
+        <v>127152890</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>98471</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6728,10 +6713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539858</v>
+        <v>539829</v>
       </c>
       <c r="R51" t="n">
-        <v>7001193</v>
+        <v>7001270</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6764,11 +6749,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6800,10 +6780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127152890</v>
+        <v>127153809</v>
       </c>
       <c r="B52" t="n">
-        <v>98469</v>
+        <v>80159</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6811,27 +6791,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6840,13 +6820,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539829</v>
+        <v>539890</v>
       </c>
       <c r="R52" t="n">
-        <v>7001270</v>
+        <v>7001195</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6890,6 +6870,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6910,7 +6910,7 @@
         <v>127162675</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>127161775</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>127159734</v>
       </c>
       <c r="B55" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>127156042</v>
       </c>
       <c r="B56" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>127162577</v>
       </c>
       <c r="B57" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>127160489</v>
       </c>
       <c r="B58" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>127164425</v>
       </c>
       <c r="B59" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>127163731</v>
       </c>
       <c r="B60" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>127156085</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>127155182</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8070,47 +8070,38 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127158943</v>
+        <v>127153134</v>
       </c>
       <c r="B63" t="n">
-        <v>98448</v>
+        <v>57660</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8120,17 +8111,17 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540039</v>
+        <v>539827</v>
       </c>
       <c r="R63" t="n">
-        <v>7001317</v>
+        <v>7001225</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8164,7 +8155,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
+          <t>Rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8179,6 +8170,26 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8196,38 +8207,47 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127153134</v>
+        <v>127158943</v>
       </c>
       <c r="B64" t="n">
-        <v>57658</v>
+        <v>98450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -8237,17 +8257,17 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>539827</v>
+        <v>540039</v>
       </c>
       <c r="R64" t="n">
-        <v>7001225</v>
+        <v>7001317</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8281,7 +8301,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en gran.</t>
+          <t>Minst 10 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8296,26 +8316,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8336,7 +8336,7 @@
         <v>127163069</v>
       </c>
       <c r="B65" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8460,38 +8460,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127160736</v>
+        <v>127160440</v>
       </c>
       <c r="B66" t="n">
-        <v>98469</v>
+        <v>91786</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>gulnande löv/blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540193</v>
+        <v>540128</v>
       </c>
       <c r="R66" t="n">
-        <v>7001357</v>
+        <v>7001287</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8538,6 +8538,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8550,6 +8555,26 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8567,38 +8592,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127160440</v>
+        <v>127160736</v>
       </c>
       <c r="B67" t="n">
-        <v>91784</v>
+        <v>98471</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8607,13 +8632,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540128</v>
+        <v>540193</v>
       </c>
       <c r="R67" t="n">
-        <v>7001287</v>
+        <v>7001357</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8645,11 +8670,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Fruktkroppar längs minst 5 meter i en lutande död gran.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8662,26 +8682,6 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -8699,48 +8699,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127160774</v>
+        <v>127162146</v>
       </c>
       <c r="B68" t="n">
-        <v>80121</v>
+        <v>98471</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540203</v>
+        <v>540106</v>
       </c>
       <c r="R68" t="n">
-        <v>7001394</v>
+        <v>7001407</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8784,26 +8789,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8821,53 +8806,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127162146</v>
+        <v>127160774</v>
       </c>
       <c r="B69" t="n">
-        <v>98469</v>
+        <v>80123</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540106</v>
+        <v>540203</v>
       </c>
       <c r="R69" t="n">
-        <v>7001407</v>
+        <v>7001394</v>
       </c>
       <c r="S69" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8911,6 +8891,26 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127155980</v>
+        <v>127164741</v>
       </c>
       <c r="B70" t="n">
-        <v>98471</v>
+        <v>98367</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8939,56 +8939,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539933</v>
+        <v>540004</v>
       </c>
       <c r="R70" t="n">
-        <v>7001238</v>
+        <v>7001090</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9028,11 +9014,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9049,10 +9030,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127162549</v>
+        <v>127155980</v>
       </c>
       <c r="B71" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9077,25 +9058,39 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540212</v>
+        <v>539933</v>
       </c>
       <c r="R71" t="n">
-        <v>7001230</v>
+        <v>7001238</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9135,6 +9130,11 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9151,10 +9151,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127164741</v>
+        <v>127162549</v>
       </c>
       <c r="B72" t="n">
-        <v>98365</v>
+        <v>98473</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9162,21 +9162,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9187,17 +9187,17 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540004</v>
+        <v>540212</v>
       </c>
       <c r="R72" t="n">
-        <v>7001090</v>
+        <v>7001230</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>127153185</v>
       </c>
       <c r="B73" t="n">
-        <v>98781</v>
+        <v>98783</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127159827</v>
+        <v>127158202</v>
       </c>
       <c r="B74" t="n">
-        <v>80121</v>
+        <v>91350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9371,27 +9371,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9400,13 +9400,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540122</v>
+        <v>540038</v>
       </c>
       <c r="R74" t="n">
-        <v>7001326</v>
+        <v>7001306</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9438,6 +9438,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikliga mängder död ved.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9452,24 +9457,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9487,10 +9482,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127158202</v>
+        <v>127159827</v>
       </c>
       <c r="B75" t="n">
-        <v>91348</v>
+        <v>80123</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9498,27 +9493,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9527,13 +9522,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540038</v>
+        <v>540122</v>
       </c>
       <c r="R75" t="n">
-        <v>7001306</v>
+        <v>7001326</v>
       </c>
       <c r="S75" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9565,11 +9560,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På fyndplatsen finns rikliga mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9584,14 +9574,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9609,10 +9609,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127162730</v>
+        <v>127163162</v>
       </c>
       <c r="B76" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9637,16 +9637,7 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9654,17 +9645,17 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540258</v>
+        <v>540247</v>
       </c>
       <c r="R76" t="n">
-        <v>7001179</v>
+        <v>7001094</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9704,11 +9695,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9725,10 +9711,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127163162</v>
+        <v>127162730</v>
       </c>
       <c r="B77" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9753,7 +9739,16 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9761,17 +9756,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540247</v>
+        <v>540258</v>
       </c>
       <c r="R77" t="n">
-        <v>7001094</v>
+        <v>7001179</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9811,6 +9806,11 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9830,7 +9830,7 @@
         <v>127154622</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127161443</v>
+        <v>127156896</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9978,19 +9978,24 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540137</v>
+        <v>539983</v>
       </c>
       <c r="R79" t="n">
-        <v>7001432</v>
+        <v>7001163</v>
       </c>
       <c r="S79" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10024,7 +10029,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
+          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10076,10 +10081,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127156896</v>
+        <v>127160558</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10105,24 +10110,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>539983</v>
+        <v>540205</v>
       </c>
       <c r="R80" t="n">
-        <v>7001163</v>
+        <v>7001321</v>
       </c>
       <c r="S80" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10152,11 +10152,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10208,10 +10203,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127160558</v>
+        <v>127157972</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10219,37 +10214,47 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540205</v>
+        <v>540038</v>
       </c>
       <c r="R81" t="n">
-        <v>7001321</v>
+        <v>7001245</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10281,6 +10286,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10307,12 +10317,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10333,7 +10343,7 @@
         <v>127155895</v>
       </c>
       <c r="B82" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10459,7 +10469,7 @@
         <v>127154216</v>
       </c>
       <c r="B83" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10582,10 +10592,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127157972</v>
+        <v>127161443</v>
       </c>
       <c r="B84" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10593,47 +10603,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540038</v>
+        <v>540137</v>
       </c>
       <c r="R84" t="n">
-        <v>7001245</v>
+        <v>7001432</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10722,7 +10722,7 @@
         <v>127164354</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127160670</v>
+        <v>127163738</v>
       </c>
       <c r="B86" t="n">
         <v>98471</v>
@@ -10852,33 +10852,24 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -10886,17 +10877,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540195</v>
+        <v>540308</v>
       </c>
       <c r="R86" t="n">
-        <v>7001331</v>
+        <v>7001066</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10928,11 +10919,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10941,11 +10927,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10965,7 +10946,7 @@
         <v>127155804</v>
       </c>
       <c r="B87" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11069,10 +11050,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127163738</v>
+        <v>127160670</v>
       </c>
       <c r="B88" t="n">
-        <v>98469</v>
+        <v>98473</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11080,24 +11061,33 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -11105,17 +11095,17 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540308</v>
+        <v>540195</v>
       </c>
       <c r="R88" t="n">
-        <v>7001066</v>
+        <v>7001331</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11147,6 +11137,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -11155,6 +11150,11 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11174,7 +11174,7 @@
         <v>127159714</v>
       </c>
       <c r="B89" t="n">
-        <v>98446</v>
+        <v>98448</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11307,10 +11307,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127157226</v>
+        <v>127157856</v>
       </c>
       <c r="B90" t="n">
-        <v>98471</v>
+        <v>98356</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11318,26 +11318,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11350,6 +11350,7 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11361,13 +11362,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539976</v>
+        <v>539984</v>
       </c>
       <c r="R90" t="n">
-        <v>7001240</v>
+        <v>7001243</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11394,17 +11395,33 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11428,10 +11445,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127157856</v>
+        <v>127157226</v>
       </c>
       <c r="B91" t="n">
-        <v>98354</v>
+        <v>98473</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11439,26 +11456,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11471,7 +11488,6 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11483,13 +11499,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>539984</v>
+        <v>539976</v>
       </c>
       <c r="R91" t="n">
-        <v>7001243</v>
+        <v>7001240</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11516,33 +11532,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>127159972</v>
       </c>
       <c r="B92" t="n">
-        <v>98446</v>
+        <v>98448</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>127155729</v>
       </c>
       <c r="B93" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>127174668</v>
       </c>
       <c r="B94" t="n">
-        <v>90875</v>
+        <v>90877</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>127157050</v>
       </c>
       <c r="B95" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>127160214</v>
       </c>
       <c r="B96" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>127160071</v>
       </c>
       <c r="B97" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>127155870</v>
       </c>
       <c r="B98" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>127164256</v>
       </c>
       <c r="B99" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>127157299</v>
       </c>
       <c r="B100" t="n">
-        <v>98354</v>
+        <v>98356</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>127162786</v>
       </c>
       <c r="B101" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127164710</v>
+        <v>127153536</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540011</v>
+        <v>539859</v>
       </c>
       <c r="R2" t="n">
-        <v>7001079</v>
+        <v>7001178</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,26 +775,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127162096</v>
+        <v>127164710</v>
       </c>
       <c r="B3" t="n">
         <v>80123</v>
@@ -838,22 +823,22 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540104</v>
+        <v>540011</v>
       </c>
       <c r="R3" t="n">
-        <v>7001431</v>
+        <v>7001079</v>
       </c>
       <c r="S3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,7 +924,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127160294</v>
+        <v>127162096</v>
       </c>
       <c r="B4" t="n">
         <v>80123</v>
@@ -970,7 +955,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -979,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540092</v>
+        <v>540104</v>
       </c>
       <c r="R4" t="n">
-        <v>7001341</v>
+        <v>7001431</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,6 +1002,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på två sälgar.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1043,12 +1033,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,32 +1056,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127162017</v>
+        <v>127160294</v>
       </c>
       <c r="B5" t="n">
-        <v>80158</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1106,13 +1096,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540111</v>
+        <v>540092</v>
       </c>
       <c r="R5" t="n">
-        <v>7001420</v>
+        <v>7001341</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1170,12 +1160,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1193,43 +1183,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127158784</v>
+        <v>127162017</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>80158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1238,13 +1223,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540039</v>
+        <v>540111</v>
       </c>
       <c r="R6" t="n">
-        <v>7001341</v>
+        <v>7001420</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1271,26 +1256,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1307,22 +1277,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,10 +1310,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127153536</v>
+        <v>127158784</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,16 +1321,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1371,7 +1341,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1381,17 +1351,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539859</v>
+        <v>540039</v>
       </c>
       <c r="R7" t="n">
-        <v>7001178</v>
+        <v>7001341</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1418,14 +1388,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1440,6 +1420,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127163443</v>
+        <v>127162604</v>
       </c>
       <c r="B9" t="n">
-        <v>98473</v>
+        <v>98367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540255</v>
+        <v>540240</v>
       </c>
       <c r="R9" t="n">
-        <v>7001070</v>
+        <v>7001210</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127162604</v>
+        <v>127163443</v>
       </c>
       <c r="B10" t="n">
-        <v>98367</v>
+        <v>98473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,21 +1691,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1716,17 +1716,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540240</v>
+        <v>540255</v>
       </c>
       <c r="R10" t="n">
-        <v>7001210</v>
+        <v>7001070</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2021,47 +2021,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127162375</v>
+        <v>127160359</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540115</v>
+        <v>540139</v>
       </c>
       <c r="R13" t="n">
-        <v>7001309</v>
+        <v>7001298</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2103,14 +2103,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2142,47 +2152,47 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127160359</v>
+        <v>127162375</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2191,13 +2201,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540139</v>
+        <v>540115</v>
       </c>
       <c r="R14" t="n">
-        <v>7001298</v>
+        <v>7001309</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2224,24 +2234,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2399,10 +2399,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127161347</v>
+        <v>127159187</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2410,27 +2410,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2439,13 +2444,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540157</v>
+        <v>540057</v>
       </c>
       <c r="R16" t="n">
-        <v>7001411</v>
+        <v>7001353</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2472,14 +2477,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Fertil garnlav å gran.</t>
+          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,12 +2523,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2531,10 +2546,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127159187</v>
+        <v>127161347</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,32 +2557,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2576,13 +2586,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540057</v>
+        <v>540157</v>
       </c>
       <c r="R17" t="n">
-        <v>7001353</v>
+        <v>7001411</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2609,24 +2619,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
+          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2800,62 +2800,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127163626</v>
+        <v>127164774</v>
       </c>
       <c r="B19" t="n">
-        <v>98473</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540307</v>
+        <v>540022</v>
       </c>
       <c r="R19" t="n">
-        <v>7001050</v>
+        <v>7001093</v>
       </c>
       <c r="S19" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2887,11 +2873,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2904,6 +2885,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2921,62 +2922,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127152848</v>
+        <v>127153666</v>
       </c>
       <c r="B20" t="n">
-        <v>98367</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539832</v>
+        <v>539888</v>
       </c>
       <c r="R20" t="n">
-        <v>7001265</v>
+        <v>7001166</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3020,6 +3007,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3037,53 +3044,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127160270</v>
+        <v>127163769</v>
       </c>
       <c r="B21" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540095</v>
+        <v>540285</v>
       </c>
       <c r="R21" t="n">
-        <v>7001315</v>
+        <v>7001071</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3127,6 +3129,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3144,45 +3166,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127164774</v>
+        <v>127160270</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>98471</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540022</v>
+        <v>540095</v>
       </c>
       <c r="R22" t="n">
-        <v>7001093</v>
+        <v>7001315</v>
       </c>
       <c r="S22" t="n">
         <v>8</v>
@@ -3229,26 +3256,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3266,48 +3273,62 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127153666</v>
+        <v>127163626</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>98473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539888</v>
+        <v>540307</v>
       </c>
       <c r="R23" t="n">
-        <v>7001166</v>
+        <v>7001050</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3339,6 +3360,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3351,26 +3377,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3388,48 +3394,62 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127163769</v>
+        <v>127152848</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>98367</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540285</v>
+        <v>539832</v>
       </c>
       <c r="R24" t="n">
-        <v>7001071</v>
+        <v>7001265</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3473,26 +3493,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3632,50 +3632,64 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127158356</v>
+        <v>127155997</v>
       </c>
       <c r="B26" t="n">
-        <v>91332</v>
+        <v>98367</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540032</v>
+        <v>539924</v>
       </c>
       <c r="R26" t="n">
-        <v>7001287</v>
+        <v>7001238</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3721,27 +3735,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3759,64 +3753,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127155997</v>
+        <v>127158356</v>
       </c>
       <c r="B27" t="n">
-        <v>98367</v>
+        <v>91332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539924</v>
+        <v>540032</v>
       </c>
       <c r="R27" t="n">
-        <v>7001238</v>
+        <v>7001287</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3862,7 +3842,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3880,67 +3880,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153897</v>
+        <v>127153018</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539873</v>
+        <v>539829</v>
       </c>
       <c r="R28" t="n">
-        <v>7001197</v>
+        <v>7001270</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3972,11 +3953,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3989,6 +3965,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4006,48 +4002,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153018</v>
+        <v>127153641</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>80152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539829</v>
+        <v>539864</v>
       </c>
       <c r="R29" t="n">
-        <v>7001270</v>
+        <v>7001177</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4095,22 +4096,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4128,38 +4129,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127153641</v>
+        <v>127153581</v>
       </c>
       <c r="B30" t="n">
-        <v>80152</v>
+        <v>80123</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4168,13 +4169,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>539864</v>
+        <v>539872</v>
       </c>
       <c r="R30" t="n">
-        <v>7001177</v>
+        <v>7001176</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4255,7 +4256,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127153581</v>
+        <v>127160821</v>
       </c>
       <c r="B31" t="n">
         <v>80123</v>
@@ -4291,14 +4292,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>539872</v>
+        <v>540188</v>
       </c>
       <c r="R31" t="n">
-        <v>7001176</v>
+        <v>7001373</v>
       </c>
       <c r="S31" t="n">
         <v>12</v>
@@ -4331,6 +4332,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en upplyft liggande levande sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4382,50 +4388,64 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127160821</v>
+        <v>127153897</v>
       </c>
       <c r="B32" t="n">
-        <v>80123</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540188</v>
+        <v>539873</v>
       </c>
       <c r="R32" t="n">
-        <v>7001373</v>
+        <v>7001197</v>
       </c>
       <c r="S32" t="n">
         <v>12</v>
@@ -4462,7 +4482,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en upplyft liggande levande sälg.</t>
+          <t>Minst 70 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4477,26 +4497,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4514,53 +4514,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127163212</v>
+        <v>127161738</v>
       </c>
       <c r="B33" t="n">
-        <v>98473</v>
+        <v>80123</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540253</v>
+        <v>540129</v>
       </c>
       <c r="R33" t="n">
-        <v>7001109</v>
+        <v>7001452</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4592,6 +4592,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4604,6 +4609,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4621,7 +4646,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127161738</v>
+        <v>127161580</v>
       </c>
       <c r="B34" t="n">
         <v>80123</v>
@@ -4652,7 +4677,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4661,13 +4686,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540129</v>
+        <v>540152</v>
       </c>
       <c r="R34" t="n">
-        <v>7001452</v>
+        <v>7001464</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4701,7 +4726,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4753,10 +4778,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127161580</v>
+        <v>127158834</v>
       </c>
       <c r="B35" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4764,39 +4789,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540152</v>
+        <v>540033</v>
       </c>
       <c r="R35" t="n">
-        <v>7001464</v>
+        <v>7001311</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4831,11 +4851,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4852,22 +4867,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4885,10 +4900,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127158834</v>
+        <v>127164937</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4896,34 +4911,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540033</v>
+        <v>539990</v>
       </c>
       <c r="R36" t="n">
-        <v>7001311</v>
+        <v>7001113</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4958,6 +4978,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4974,22 +4999,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5007,38 +5032,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127164937</v>
+        <v>127163212</v>
       </c>
       <c r="B37" t="n">
-        <v>80123</v>
+        <v>98473</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5047,13 +5072,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539990</v>
+        <v>540253</v>
       </c>
       <c r="R37" t="n">
-        <v>7001113</v>
+        <v>7001109</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5085,11 +5110,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5102,26 +5122,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127153765</v>
+        <v>127164835</v>
       </c>
       <c r="B39" t="n">
         <v>80123</v>
@@ -5302,22 +5302,22 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539879</v>
+        <v>539992</v>
       </c>
       <c r="R39" t="n">
-        <v>7001196</v>
+        <v>7001093</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg.</t>
+          <t>Växer här på en grov gammal sälg (värdeträd).</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5403,10 +5403,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127164541</v>
+        <v>127153765</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5414,37 +5414,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540113</v>
+        <v>539879</v>
       </c>
       <c r="R40" t="n">
-        <v>7001087</v>
+        <v>7001196</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5476,6 +5481,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5492,22 +5502,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5525,10 +5535,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127164835</v>
+        <v>127164541</v>
       </c>
       <c r="B41" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5536,39 +5546,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539992</v>
+        <v>540113</v>
       </c>
       <c r="R41" t="n">
-        <v>7001093</v>
+        <v>7001087</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5603,11 +5608,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Växer här på en grov gammal sälg (värdeträd).</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5624,22 +5624,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5906,38 +5906,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127163976</v>
+        <v>127163137</v>
       </c>
       <c r="B44" t="n">
-        <v>98473</v>
+        <v>98450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5949,7 +5949,7 @@
         <v>540285</v>
       </c>
       <c r="R44" t="n">
-        <v>7001072</v>
+        <v>7001126</v>
       </c>
       <c r="S44" t="n">
         <v>7</v>
@@ -6129,10 +6129,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127162701</v>
+        <v>127163976</v>
       </c>
       <c r="B46" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6140,21 +6140,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6169,13 +6169,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540246</v>
+        <v>540285</v>
       </c>
       <c r="R46" t="n">
-        <v>7001169</v>
+        <v>7001072</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6215,11 +6215,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6236,38 +6231,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127163137</v>
+        <v>127162701</v>
       </c>
       <c r="B47" t="n">
-        <v>98450</v>
+        <v>98471</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6276,13 +6271,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540285</v>
+        <v>540246</v>
       </c>
       <c r="R47" t="n">
-        <v>7001126</v>
+        <v>7001169</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6322,6 +6317,11 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6338,10 +6338,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127160120</v>
+        <v>127153809</v>
       </c>
       <c r="B48" t="n">
-        <v>98783</v>
+        <v>80159</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6349,42 +6349,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219880</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540106</v>
+        <v>539890</v>
       </c>
       <c r="R48" t="n">
-        <v>7001289</v>
+        <v>7001195</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6428,6 +6428,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6445,53 +6465,67 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127164902</v>
+        <v>127153495</v>
       </c>
       <c r="B49" t="n">
-        <v>98473</v>
+        <v>98450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>539989</v>
+        <v>539858</v>
       </c>
       <c r="R49" t="n">
-        <v>7001089</v>
+        <v>7001193</v>
       </c>
       <c r="S49" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6523,6 +6557,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6531,6 +6570,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6547,67 +6591,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127153495</v>
+        <v>127160120</v>
       </c>
       <c r="B50" t="n">
-        <v>98450</v>
+        <v>98783</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>539858</v>
+        <v>540106</v>
       </c>
       <c r="R50" t="n">
-        <v>7001193</v>
+        <v>7001289</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6637,11 +6667,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor, 2 blomställningar och 2 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6673,10 +6698,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127152890</v>
+        <v>127164902</v>
       </c>
       <c r="B51" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6684,42 +6709,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539829</v>
+        <v>539989</v>
       </c>
       <c r="R51" t="n">
-        <v>7001270</v>
+        <v>7001089</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6759,11 +6784,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6780,10 +6800,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127153809</v>
+        <v>127152890</v>
       </c>
       <c r="B52" t="n">
-        <v>80159</v>
+        <v>98471</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6791,27 +6811,27 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6820,13 +6840,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539890</v>
+        <v>539829</v>
       </c>
       <c r="R52" t="n">
-        <v>7001195</v>
+        <v>7001270</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6870,26 +6890,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7151,58 +7151,62 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127159734</v>
+        <v>127163731</v>
       </c>
       <c r="B55" t="n">
-        <v>98367</v>
+        <v>98450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540115</v>
+        <v>540303</v>
       </c>
       <c r="R55" t="n">
-        <v>7001344</v>
+        <v>7001059</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7245,7 +7249,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7263,10 +7267,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127156042</v>
+        <v>127159734</v>
       </c>
       <c r="B56" t="n">
-        <v>98473</v>
+        <v>98367</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7274,33 +7278,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -7313,17 +7308,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539924</v>
+        <v>540115</v>
       </c>
       <c r="R56" t="n">
-        <v>7001238</v>
+        <v>7001344</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7384,7 +7379,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127162577</v>
+        <v>127156042</v>
       </c>
       <c r="B57" t="n">
         <v>98473</v>
@@ -7412,25 +7407,39 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540238</v>
+        <v>539924</v>
       </c>
       <c r="R57" t="n">
-        <v>7001222</v>
+        <v>7001238</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7470,6 +7479,11 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7486,7 +7500,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127160489</v>
+        <v>127162577</v>
       </c>
       <c r="B58" t="n">
         <v>98473</v>
@@ -7526,13 +7540,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540171</v>
+        <v>540238</v>
       </c>
       <c r="R58" t="n">
-        <v>7001276</v>
+        <v>7001222</v>
       </c>
       <c r="S58" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7572,11 +7586,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7593,10 +7602,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127164425</v>
+        <v>127160489</v>
       </c>
       <c r="B59" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7604,42 +7613,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540128</v>
+        <v>540171</v>
       </c>
       <c r="R59" t="n">
-        <v>7001058</v>
+        <v>7001276</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7700,47 +7709,38 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127163731</v>
+        <v>127164425</v>
       </c>
       <c r="B60" t="n">
-        <v>98450</v>
+        <v>98471</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7749,13 +7749,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540303</v>
+        <v>540128</v>
       </c>
       <c r="R60" t="n">
-        <v>7001059</v>
+        <v>7001058</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8699,53 +8699,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127162146</v>
+        <v>127160774</v>
       </c>
       <c r="B68" t="n">
-        <v>98471</v>
+        <v>80123</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540106</v>
+        <v>540203</v>
       </c>
       <c r="R68" t="n">
-        <v>7001407</v>
+        <v>7001394</v>
       </c>
       <c r="S68" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8789,6 +8784,26 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8806,48 +8821,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127160774</v>
+        <v>127162146</v>
       </c>
       <c r="B69" t="n">
-        <v>80123</v>
+        <v>98471</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540203</v>
+        <v>540106</v>
       </c>
       <c r="R69" t="n">
-        <v>7001394</v>
+        <v>7001407</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8891,26 +8911,6 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8928,10 +8928,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127164741</v>
+        <v>127155980</v>
       </c>
       <c r="B70" t="n">
-        <v>98367</v>
+        <v>98473</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8939,42 +8939,56 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540004</v>
+        <v>539933</v>
       </c>
       <c r="R70" t="n">
-        <v>7001090</v>
+        <v>7001238</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9014,6 +9028,11 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9030,7 +9049,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127155980</v>
+        <v>127162549</v>
       </c>
       <c r="B71" t="n">
         <v>98473</v>
@@ -9058,39 +9077,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>539933</v>
+        <v>540212</v>
       </c>
       <c r="R71" t="n">
-        <v>7001238</v>
+        <v>7001230</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9130,11 +9135,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9151,10 +9151,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127162549</v>
+        <v>127164741</v>
       </c>
       <c r="B72" t="n">
-        <v>98473</v>
+        <v>98367</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9162,21 +9162,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9187,17 +9187,17 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540212</v>
+        <v>540004</v>
       </c>
       <c r="R72" t="n">
-        <v>7001230</v>
+        <v>7001090</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127158202</v>
+        <v>127159827</v>
       </c>
       <c r="B74" t="n">
-        <v>91350</v>
+        <v>80123</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9371,27 +9371,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9400,13 +9400,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540038</v>
+        <v>540122</v>
       </c>
       <c r="R74" t="n">
-        <v>7001306</v>
+        <v>7001326</v>
       </c>
       <c r="S74" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9438,11 +9438,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På fyndplatsen finns rikliga mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9457,14 +9452,24 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9482,10 +9487,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127159827</v>
+        <v>127158202</v>
       </c>
       <c r="B75" t="n">
-        <v>80123</v>
+        <v>91350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9493,27 +9498,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9522,13 +9527,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540122</v>
+        <v>540038</v>
       </c>
       <c r="R75" t="n">
-        <v>7001326</v>
+        <v>7001306</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9560,6 +9565,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikliga mängder död ved.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9574,24 +9584,14 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9609,53 +9609,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127163162</v>
+        <v>127154622</v>
       </c>
       <c r="B76" t="n">
-        <v>98367</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540247</v>
+        <v>539897</v>
       </c>
       <c r="R76" t="n">
-        <v>7001094</v>
+        <v>7001240</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9695,6 +9690,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9827,48 +9847,53 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127154622</v>
+        <v>127163162</v>
       </c>
       <c r="B78" t="n">
-        <v>79020</v>
+        <v>98367</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>539897</v>
+        <v>540247</v>
       </c>
       <c r="R78" t="n">
-        <v>7001240</v>
+        <v>7001094</v>
       </c>
       <c r="S78" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9908,31 +9933,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9949,7 +9949,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127156896</v>
+        <v>127161443</v>
       </c>
       <c r="B79" t="n">
         <v>79020</v>
@@ -9978,24 +9978,19 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539983</v>
+        <v>540137</v>
       </c>
       <c r="R79" t="n">
-        <v>7001163</v>
+        <v>7001432</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10029,7 +10024,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Långväxta och fertila bålar på flera granar.</t>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10081,7 +10076,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127160558</v>
+        <v>127156896</v>
       </c>
       <c r="B80" t="n">
         <v>79020</v>
@@ -10110,19 +10105,24 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540205</v>
+        <v>539983</v>
       </c>
       <c r="R80" t="n">
-        <v>7001321</v>
+        <v>7001163</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10152,6 +10152,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10203,10 +10208,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127157972</v>
+        <v>127160558</v>
       </c>
       <c r="B81" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10214,47 +10219,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540038</v>
+        <v>540205</v>
       </c>
       <c r="R81" t="n">
-        <v>7001245</v>
+        <v>7001321</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10286,11 +10281,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10317,12 +10307,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10340,47 +10330,38 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127155895</v>
+        <v>127157972</v>
       </c>
       <c r="B82" t="n">
-        <v>98367</v>
+        <v>57660</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -10390,17 +10371,17 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>539912</v>
+        <v>540038</v>
       </c>
       <c r="R82" t="n">
-        <v>7001269</v>
+        <v>7001245</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10434,7 +10415,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
+          <t>Färska och äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10449,6 +10430,26 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10592,48 +10593,67 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127161443</v>
+        <v>127155895</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>98367</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540137</v>
+        <v>539912</v>
       </c>
       <c r="R84" t="n">
-        <v>7001432</v>
+        <v>7001269</v>
       </c>
       <c r="S84" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10667,7 +10687,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
+          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10682,26 +10702,6 @@
       <c r="AH84" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10719,48 +10719,62 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127164354</v>
+        <v>127160670</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>98473</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540166</v>
+        <v>540195</v>
       </c>
       <c r="R85" t="n">
-        <v>7001045</v>
+        <v>7001331</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10792,6 +10806,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10804,26 +10823,6 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10841,7 +10840,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127163738</v>
+        <v>127155804</v>
       </c>
       <c r="B86" t="n">
         <v>98471</v>
@@ -10872,22 +10871,27 @@
       <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540308</v>
+        <v>539886</v>
       </c>
       <c r="R86" t="n">
-        <v>7001066</v>
+        <v>7001291</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10943,7 +10947,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127155804</v>
+        <v>127163738</v>
       </c>
       <c r="B87" t="n">
         <v>98471</v>
@@ -10974,27 +10978,22 @@
       <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>539886</v>
+        <v>540308</v>
       </c>
       <c r="R87" t="n">
-        <v>7001291</v>
+        <v>7001066</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11050,62 +11049,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127160670</v>
+        <v>127164354</v>
       </c>
       <c r="B88" t="n">
-        <v>98473</v>
+        <v>79020</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540195</v>
+        <v>540166</v>
       </c>
       <c r="R88" t="n">
-        <v>7001331</v>
+        <v>7001045</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11137,11 +11122,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -11154,6 +11134,26 @@
       <c r="AH88" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11307,10 +11307,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127157856</v>
+        <v>127157226</v>
       </c>
       <c r="B90" t="n">
-        <v>98356</v>
+        <v>98473</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11318,26 +11318,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11350,7 +11350,6 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11362,13 +11361,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539984</v>
+        <v>539976</v>
       </c>
       <c r="R90" t="n">
-        <v>7001243</v>
+        <v>7001240</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11395,33 +11394,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11445,10 +11428,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127157226</v>
+        <v>127157856</v>
       </c>
       <c r="B91" t="n">
-        <v>98473</v>
+        <v>98356</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11456,26 +11439,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11488,6 +11471,7 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11499,13 +11483,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>539976</v>
+        <v>539984</v>
       </c>
       <c r="R91" t="n">
-        <v>7001240</v>
+        <v>7001243</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11532,17 +11516,33 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -2399,10 +2399,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127159187</v>
+        <v>127161347</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2410,32 +2410,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2444,13 +2439,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540057</v>
+        <v>540157</v>
       </c>
       <c r="R16" t="n">
-        <v>7001353</v>
+        <v>7001411</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2477,24 +2472,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>18:42</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
+          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2523,12 +2508,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2546,7 +2531,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127161347</v>
+        <v>127160480</v>
       </c>
       <c r="B17" t="n">
         <v>79020</v>
@@ -2575,24 +2560,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540157</v>
+        <v>540188</v>
       </c>
       <c r="R17" t="n">
-        <v>7001411</v>
+        <v>7001269</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2622,11 +2602,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2678,10 +2653,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127160480</v>
+        <v>127159187</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,37 +2664,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540188</v>
+        <v>540057</v>
       </c>
       <c r="R18" t="n">
-        <v>7001269</v>
+        <v>7001353</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2746,11 +2731,26 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, högt upp på stammen av en lutande gran i kanten mot yngre skog i ljusöppet läge.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127160270</v>
+        <v>127163626</v>
       </c>
       <c r="B22" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,42 +3177,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540095</v>
+        <v>540307</v>
       </c>
       <c r="R22" t="n">
-        <v>7001315</v>
+        <v>7001050</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3242,6 +3251,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3273,10 +3287,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127163626</v>
+        <v>127152848</v>
       </c>
       <c r="B23" t="n">
-        <v>98473</v>
+        <v>98367</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3284,26 +3298,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3318,17 +3332,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540307</v>
+        <v>539832</v>
       </c>
       <c r="R23" t="n">
-        <v>7001050</v>
+        <v>7001265</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3358,11 +3372,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3394,10 +3403,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127152848</v>
+        <v>127160270</v>
       </c>
       <c r="B24" t="n">
-        <v>98367</v>
+        <v>98471</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3405,48 +3414,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>539832</v>
+        <v>540095</v>
       </c>
       <c r="R24" t="n">
-        <v>7001265</v>
+        <v>7001315</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -4514,53 +4514,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127161738</v>
+        <v>127163212</v>
       </c>
       <c r="B33" t="n">
-        <v>80123</v>
+        <v>98473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540129</v>
+        <v>540253</v>
       </c>
       <c r="R33" t="n">
-        <v>7001452</v>
+        <v>7001109</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4592,11 +4592,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4609,26 +4604,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4646,7 +4621,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127161580</v>
+        <v>127161738</v>
       </c>
       <c r="B34" t="n">
         <v>80123</v>
@@ -4677,7 +4652,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4686,13 +4661,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540152</v>
+        <v>540129</v>
       </c>
       <c r="R34" t="n">
-        <v>7001464</v>
+        <v>7001452</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4726,7 +4701,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4778,10 +4753,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127158834</v>
+        <v>127161580</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4789,34 +4764,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540033</v>
+        <v>540152</v>
       </c>
       <c r="R35" t="n">
-        <v>7001311</v>
+        <v>7001464</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4851,6 +4831,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4867,22 +4852,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4900,10 +4885,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127164937</v>
+        <v>127158834</v>
       </c>
       <c r="B36" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4911,39 +4896,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>539990</v>
+        <v>540033</v>
       </c>
       <c r="R36" t="n">
-        <v>7001113</v>
+        <v>7001311</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4978,11 +4958,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4999,22 +4974,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5032,38 +5007,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127163212</v>
+        <v>127164937</v>
       </c>
       <c r="B37" t="n">
-        <v>98473</v>
+        <v>80123</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5072,13 +5047,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540253</v>
+        <v>539990</v>
       </c>
       <c r="R37" t="n">
-        <v>7001109</v>
+        <v>7001113</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5110,6 +5085,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5122,6 +5102,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6907,45 +6907,55 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127162675</v>
+        <v>127159734</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>98367</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540237</v>
+        <v>540115</v>
       </c>
       <c r="R53" t="n">
-        <v>7001188</v>
+        <v>7001344</v>
       </c>
       <c r="S53" t="n">
         <v>11</v>
@@ -6991,27 +7001,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7029,48 +7019,67 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127161775</v>
+        <v>127156042</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>98473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540092</v>
+        <v>539924</v>
       </c>
       <c r="R54" t="n">
-        <v>7001443</v>
+        <v>7001238</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7113,27 +7122,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7267,55 +7256,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127159734</v>
+        <v>127162675</v>
       </c>
       <c r="B56" t="n">
-        <v>98367</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540115</v>
+        <v>540237</v>
       </c>
       <c r="R56" t="n">
-        <v>7001344</v>
+        <v>7001188</v>
       </c>
       <c r="S56" t="n">
         <v>11</v>
@@ -7361,7 +7340,27 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7379,67 +7378,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127156042</v>
+        <v>127161775</v>
       </c>
       <c r="B57" t="n">
-        <v>98473</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>539924</v>
+        <v>540092</v>
       </c>
       <c r="R57" t="n">
-        <v>7001238</v>
+        <v>7001443</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7482,7 +7462,27 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127162146</v>
+        <v>127155980</v>
       </c>
       <c r="B69" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8832,42 +8832,56 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540106</v>
+        <v>539933</v>
       </c>
       <c r="R69" t="n">
-        <v>7001407</v>
+        <v>7001238</v>
       </c>
       <c r="S69" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8928,7 +8942,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127155980</v>
+        <v>127162549</v>
       </c>
       <c r="B70" t="n">
         <v>98473</v>
@@ -8956,39 +8970,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539933</v>
+        <v>540212</v>
       </c>
       <c r="R70" t="n">
-        <v>7001238</v>
+        <v>7001230</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9028,11 +9028,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9049,10 +9044,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127162549</v>
+        <v>127164741</v>
       </c>
       <c r="B71" t="n">
-        <v>98473</v>
+        <v>98367</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9060,21 +9055,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9085,17 +9080,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540212</v>
+        <v>540004</v>
       </c>
       <c r="R71" t="n">
-        <v>7001230</v>
+        <v>7001090</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9151,10 +9146,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127164741</v>
+        <v>127162146</v>
       </c>
       <c r="B72" t="n">
-        <v>98367</v>
+        <v>98471</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9162,42 +9157,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540004</v>
+        <v>540106</v>
       </c>
       <c r="R72" t="n">
-        <v>7001090</v>
+        <v>7001407</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9237,6 +9232,11 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -10719,62 +10719,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127160670</v>
+        <v>127164354</v>
       </c>
       <c r="B85" t="n">
-        <v>98473</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540195</v>
+        <v>540166</v>
       </c>
       <c r="R85" t="n">
-        <v>7001331</v>
+        <v>7001045</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10806,11 +10792,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10823,6 +10804,26 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10840,10 +10841,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127155804</v>
+        <v>127160670</v>
       </c>
       <c r="B86" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10851,44 +10852,48 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>539886</v>
+        <v>540195</v>
       </c>
       <c r="R86" t="n">
-        <v>7001291</v>
+        <v>7001331</v>
       </c>
       <c r="S86" t="n">
         <v>9</v>
@@ -10923,6 +10928,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10931,6 +10941,11 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10947,7 +10962,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127163738</v>
+        <v>127155804</v>
       </c>
       <c r="B87" t="n">
         <v>98471</v>
@@ -10978,22 +10993,27 @@
       <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540308</v>
+        <v>539886</v>
       </c>
       <c r="R87" t="n">
-        <v>7001066</v>
+        <v>7001291</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11049,48 +11069,53 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127164354</v>
+        <v>127163738</v>
       </c>
       <c r="B88" t="n">
-        <v>79020</v>
+        <v>98471</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540166</v>
+        <v>540308</v>
       </c>
       <c r="R88" t="n">
-        <v>7001045</v>
+        <v>7001066</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11130,31 +11155,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11307,10 +11307,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127157226</v>
+        <v>127157856</v>
       </c>
       <c r="B90" t="n">
-        <v>98473</v>
+        <v>98356</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11318,26 +11318,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11350,6 +11350,7 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11361,13 +11362,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>539976</v>
+        <v>539984</v>
       </c>
       <c r="R90" t="n">
-        <v>7001240</v>
+        <v>7001243</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11394,17 +11395,33 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -11428,10 +11445,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127157856</v>
+        <v>127157226</v>
       </c>
       <c r="B91" t="n">
-        <v>98356</v>
+        <v>98473</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11439,26 +11456,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11471,7 +11488,6 @@
           <t>överblommad</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -11483,13 +11499,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>539984</v>
+        <v>539976</v>
       </c>
       <c r="R91" t="n">
-        <v>7001243</v>
+        <v>7001240</v>
       </c>
       <c r="S91" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11516,33 +11532,17 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Minst 214 plantor av guckusko i grupper och glest spridda inom ca 80 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -12069,48 +12069,67 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127160214</v>
+        <v>127160071</v>
       </c>
       <c r="B96" t="n">
-        <v>80123</v>
+        <v>98450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540081</v>
+        <v>540115</v>
       </c>
       <c r="R96" t="n">
-        <v>7001299</v>
+        <v>7001289</v>
       </c>
       <c r="S96" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12142,6 +12161,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12154,26 +12178,6 @@
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12191,67 +12195,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127160071</v>
+        <v>127160214</v>
       </c>
       <c r="B97" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540115</v>
+        <v>540081</v>
       </c>
       <c r="R97" t="n">
-        <v>7001289</v>
+        <v>7001299</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12283,11 +12268,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12300,6 +12280,26 @@
       <c r="AH97" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127164710</v>
+        <v>127158784</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,42 +803,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540011</v>
+        <v>540039</v>
       </c>
       <c r="R3" t="n">
-        <v>7001079</v>
+        <v>7001341</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,14 +870,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +906,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,38 +939,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127162096</v>
+        <v>127162604</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>98367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540104</v>
+        <v>540240</v>
       </c>
       <c r="R4" t="n">
-        <v>7001431</v>
+        <v>7001210</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,11 +1017,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på två sälgar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1015,31 +1025,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,53 +1041,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127160294</v>
+        <v>127163443</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>98473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540092</v>
+        <v>540255</v>
       </c>
       <c r="R5" t="n">
-        <v>7001341</v>
+        <v>7001070</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,31 +1127,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127162017</v>
+        <v>127162418</v>
       </c>
       <c r="B6" t="n">
-        <v>80158</v>
+        <v>98783</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,27 +1154,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>219880</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1223,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540111</v>
+        <v>540127</v>
       </c>
       <c r="R6" t="n">
-        <v>7001420</v>
+        <v>7001264</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,26 +1233,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1310,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127158784</v>
+        <v>127164710</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,47 +1261,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540039</v>
+        <v>540011</v>
       </c>
       <c r="R7" t="n">
-        <v>7001341</v>
+        <v>7001079</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,24 +1323,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,22 +1349,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1457,47 +1382,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127161646</v>
+        <v>127162096</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1506,13 +1422,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540139</v>
+        <v>540104</v>
       </c>
       <c r="R8" t="n">
-        <v>7001452</v>
+        <v>7001431</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1546,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+          <t>Fertil lunglav på två sälgar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1561,6 +1477,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1578,38 +1514,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127162604</v>
+        <v>127160294</v>
       </c>
       <c r="B9" t="n">
-        <v>98367</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1618,10 +1554,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540240</v>
+        <v>540092</v>
       </c>
       <c r="R9" t="n">
-        <v>7001210</v>
+        <v>7001341</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1664,6 +1600,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1680,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127163443</v>
+        <v>127162017</v>
       </c>
       <c r="B10" t="n">
-        <v>98473</v>
+        <v>80158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,42 +1652,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540255</v>
+        <v>540111</v>
       </c>
       <c r="R10" t="n">
-        <v>7001070</v>
+        <v>7001420</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1766,6 +1727,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1782,38 +1768,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127162418</v>
+        <v>127161646</v>
       </c>
       <c r="B11" t="n">
-        <v>98783</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1822,13 +1817,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540127</v>
+        <v>540139</v>
       </c>
       <c r="R11" t="n">
-        <v>7001264</v>
+        <v>7001452</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1858,6 +1853,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,10 +1889,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127154593</v>
+        <v>127160359</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,42 +1900,51 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539874</v>
+        <v>540139</v>
       </c>
       <c r="R12" t="n">
-        <v>7001234</v>
+        <v>7001298</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1962,14 +1971,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
+          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,26 +2003,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2021,42 +2020,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127160359</v>
+        <v>127155767</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>98367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2066,17 +2070,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540139</v>
+        <v>539895</v>
       </c>
       <c r="R13" t="n">
-        <v>7001298</v>
+        <v>7001284</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2103,24 +2107,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2152,62 +2146,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127162375</v>
+        <v>127154593</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540115</v>
+        <v>539874</v>
       </c>
       <c r="R14" t="n">
-        <v>7001309</v>
+        <v>7001234</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2241,7 +2226,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,6 +2241,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2273,37 +2278,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127155767</v>
+        <v>127162375</v>
       </c>
       <c r="B15" t="n">
-        <v>98367</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2313,27 +2318,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539895</v>
+        <v>540115</v>
       </c>
       <c r="R15" t="n">
-        <v>7001284</v>
+        <v>7001309</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127153666</v>
+        <v>127163769</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2953,17 +2953,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>539888</v>
+        <v>540285</v>
       </c>
       <c r="R20" t="n">
-        <v>7001166</v>
+        <v>7001071</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127163769</v>
+        <v>127153666</v>
       </c>
       <c r="B21" t="n">
         <v>79020</v>
@@ -3075,17 +3075,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540285</v>
+        <v>539888</v>
       </c>
       <c r="R21" t="n">
-        <v>7001071</v>
+        <v>7001166</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3166,10 +3166,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127163626</v>
+        <v>127160270</v>
       </c>
       <c r="B22" t="n">
-        <v>98473</v>
+        <v>98471</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,51 +3177,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540307</v>
+        <v>540095</v>
       </c>
       <c r="R22" t="n">
-        <v>7001050</v>
+        <v>7001315</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3251,11 +3242,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3287,10 +3273,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127152848</v>
+        <v>127163626</v>
       </c>
       <c r="B23" t="n">
-        <v>98367</v>
+        <v>98473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3298,26 +3284,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3332,17 +3318,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>539832</v>
+        <v>540307</v>
       </c>
       <c r="R23" t="n">
-        <v>7001265</v>
+        <v>7001050</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3372,6 +3358,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>I ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3403,10 +3394,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127160270</v>
+        <v>127152848</v>
       </c>
       <c r="B24" t="n">
-        <v>98471</v>
+        <v>98367</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3414,39 +3405,48 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540095</v>
+        <v>539832</v>
       </c>
       <c r="R24" t="n">
-        <v>7001315</v>
+        <v>7001265</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3632,64 +3632,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127155997</v>
+        <v>127158356</v>
       </c>
       <c r="B26" t="n">
-        <v>98367</v>
+        <v>91332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>539924</v>
+        <v>540032</v>
       </c>
       <c r="R26" t="n">
-        <v>7001238</v>
+        <v>7001287</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3735,7 +3721,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3753,50 +3759,64 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127158356</v>
+        <v>127155997</v>
       </c>
       <c r="B27" t="n">
-        <v>91332</v>
+        <v>98367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540032</v>
+        <v>539924</v>
       </c>
       <c r="R27" t="n">
-        <v>7001287</v>
+        <v>7001238</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3842,27 +3862,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4621,10 +4621,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127161738</v>
+        <v>127158834</v>
       </c>
       <c r="B34" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4632,42 +4632,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540129</v>
+        <v>540033</v>
       </c>
       <c r="R34" t="n">
-        <v>7001452</v>
+        <v>7001311</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4699,11 +4694,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4720,22 +4710,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4753,7 +4743,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127161580</v>
+        <v>127161738</v>
       </c>
       <c r="B35" t="n">
         <v>80123</v>
@@ -4784,7 +4774,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4793,13 +4783,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540152</v>
+        <v>540129</v>
       </c>
       <c r="R35" t="n">
-        <v>7001464</v>
+        <v>7001452</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4833,7 +4823,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4885,10 +4875,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127158834</v>
+        <v>127161580</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4896,34 +4886,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540033</v>
+        <v>540152</v>
       </c>
       <c r="R36" t="n">
-        <v>7001311</v>
+        <v>7001464</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4958,6 +4953,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4974,22 +4974,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127154714</v>
+        <v>127164541</v>
       </c>
       <c r="B38" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5150,42 +5150,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>539872</v>
+        <v>540113</v>
       </c>
       <c r="R38" t="n">
-        <v>7001243</v>
+        <v>7001087</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5217,11 +5212,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 gamla sälgar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5238,22 +5228,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5271,7 +5261,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127164835</v>
+        <v>127154714</v>
       </c>
       <c r="B39" t="n">
         <v>80123</v>
@@ -5307,17 +5297,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539992</v>
+        <v>539872</v>
       </c>
       <c r="R39" t="n">
-        <v>7001093</v>
+        <v>7001243</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5351,7 +5341,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+          <t>Lunglav på 3 gamla sälgar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5403,7 +5393,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127153765</v>
+        <v>127164835</v>
       </c>
       <c r="B40" t="n">
         <v>80123</v>
@@ -5434,22 +5424,22 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539879</v>
+        <v>539992</v>
       </c>
       <c r="R40" t="n">
-        <v>7001196</v>
+        <v>7001093</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5483,7 +5473,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en gammal sälg.</t>
+          <t>Växer här på en grov gammal sälg (värdeträd).</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5535,10 +5525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127164541</v>
+        <v>127153765</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5546,37 +5536,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540113</v>
+        <v>539879</v>
       </c>
       <c r="R41" t="n">
-        <v>7001087</v>
+        <v>7001196</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5608,6 +5603,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5624,22 +5624,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127162532</v>
+        <v>127164613</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5668,34 +5668,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540214</v>
+        <v>540079</v>
       </c>
       <c r="R42" t="n">
-        <v>7001228</v>
+        <v>7001087</v>
       </c>
       <c r="S42" t="n">
         <v>9</v>
@@ -5746,22 +5751,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5779,53 +5784,62 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127164613</v>
+        <v>127158031</v>
       </c>
       <c r="B43" t="n">
-        <v>80123</v>
+        <v>98367</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540079</v>
+        <v>540047</v>
       </c>
       <c r="R43" t="n">
-        <v>7001087</v>
+        <v>7001245</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5857,6 +5871,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Vid en bäck på en gammal väg.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5869,26 +5888,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5906,38 +5905,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127163137</v>
+        <v>127163976</v>
       </c>
       <c r="B44" t="n">
-        <v>98450</v>
+        <v>98473</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5949,7 +5948,7 @@
         <v>540285</v>
       </c>
       <c r="R44" t="n">
-        <v>7001126</v>
+        <v>7001072</v>
       </c>
       <c r="S44" t="n">
         <v>7</v>
@@ -6008,62 +6007,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127158031</v>
+        <v>127162532</v>
       </c>
       <c r="B45" t="n">
-        <v>98367</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540047</v>
+        <v>540214</v>
       </c>
       <c r="R45" t="n">
-        <v>7001245</v>
+        <v>7001228</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6095,11 +6080,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Vid en bäck på en gammal väg.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6112,6 +6092,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6129,38 +6129,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127163976</v>
+        <v>127163137</v>
       </c>
       <c r="B46" t="n">
-        <v>98473</v>
+        <v>98450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6172,7 +6172,7 @@
         <v>540285</v>
       </c>
       <c r="R46" t="n">
-        <v>7001072</v>
+        <v>7001126</v>
       </c>
       <c r="S46" t="n">
         <v>7</v>
@@ -6591,10 +6591,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127160120</v>
+        <v>127152890</v>
       </c>
       <c r="B50" t="n">
-        <v>98783</v>
+        <v>98471</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6602,42 +6602,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219880</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540106</v>
+        <v>539829</v>
       </c>
       <c r="R50" t="n">
-        <v>7001289</v>
+        <v>7001270</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6698,10 +6698,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127164902</v>
+        <v>127160120</v>
       </c>
       <c r="B51" t="n">
-        <v>98473</v>
+        <v>98783</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6709,42 +6709,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>219880</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>539989</v>
+        <v>540106</v>
       </c>
       <c r="R51" t="n">
-        <v>7001089</v>
+        <v>7001289</v>
       </c>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6784,6 +6784,11 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6800,10 +6805,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127152890</v>
+        <v>127164902</v>
       </c>
       <c r="B52" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6811,42 +6816,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>539829</v>
+        <v>539989</v>
       </c>
       <c r="R52" t="n">
-        <v>7001270</v>
+        <v>7001089</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6886,11 +6891,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6907,58 +6907,62 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127159734</v>
+        <v>127163731</v>
       </c>
       <c r="B53" t="n">
-        <v>98367</v>
+        <v>98450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540115</v>
+        <v>540303</v>
       </c>
       <c r="R53" t="n">
-        <v>7001344</v>
+        <v>7001059</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7001,7 +7005,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7019,10 +7023,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127156042</v>
+        <v>127164425</v>
       </c>
       <c r="B54" t="n">
-        <v>98473</v>
+        <v>98471</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7030,56 +7034,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>539924</v>
+        <v>540128</v>
       </c>
       <c r="R54" t="n">
-        <v>7001238</v>
+        <v>7001058</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7122,7 +7112,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7140,62 +7130,58 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127163731</v>
+        <v>127159734</v>
       </c>
       <c r="B55" t="n">
-        <v>98450</v>
+        <v>98367</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540303</v>
+        <v>540115</v>
       </c>
       <c r="R55" t="n">
-        <v>7001059</v>
+        <v>7001344</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7238,7 +7224,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7256,48 +7242,67 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127162675</v>
+        <v>127156042</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>98473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540237</v>
+        <v>539924</v>
       </c>
       <c r="R56" t="n">
-        <v>7001188</v>
+        <v>7001238</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7340,27 +7345,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7378,45 +7363,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127161775</v>
+        <v>127162577</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>98473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540092</v>
+        <v>540238</v>
       </c>
       <c r="R57" t="n">
-        <v>7001443</v>
+        <v>7001222</v>
       </c>
       <c r="S57" t="n">
         <v>8</v>
@@ -7459,31 +7449,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7500,7 +7465,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127162577</v>
+        <v>127160489</v>
       </c>
       <c r="B58" t="n">
         <v>98473</v>
@@ -7540,13 +7505,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540238</v>
+        <v>540171</v>
       </c>
       <c r="R58" t="n">
-        <v>7001222</v>
+        <v>7001276</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7586,6 +7551,11 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7602,53 +7572,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127160489</v>
+        <v>127162675</v>
       </c>
       <c r="B59" t="n">
-        <v>98473</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540171</v>
+        <v>540237</v>
       </c>
       <c r="R59" t="n">
-        <v>7001276</v>
+        <v>7001188</v>
       </c>
       <c r="S59" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7692,6 +7657,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7709,53 +7694,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127164425</v>
+        <v>127161775</v>
       </c>
       <c r="B60" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540128</v>
+        <v>540092</v>
       </c>
       <c r="R60" t="n">
-        <v>7001058</v>
+        <v>7001443</v>
       </c>
       <c r="S60" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7799,6 +7779,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8821,10 +8821,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127155980</v>
+        <v>127162146</v>
       </c>
       <c r="B69" t="n">
-        <v>98473</v>
+        <v>98471</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8832,56 +8832,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>539933</v>
+        <v>540106</v>
       </c>
       <c r="R69" t="n">
-        <v>7001238</v>
+        <v>7001407</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8942,7 +8928,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127162549</v>
+        <v>127155980</v>
       </c>
       <c r="B70" t="n">
         <v>98473</v>
@@ -8970,25 +8956,39 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540212</v>
+        <v>539933</v>
       </c>
       <c r="R70" t="n">
-        <v>7001230</v>
+        <v>7001238</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9028,6 +9028,11 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9044,10 +9049,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127164741</v>
+        <v>127162549</v>
       </c>
       <c r="B71" t="n">
-        <v>98367</v>
+        <v>98473</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9055,21 +9060,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9080,17 +9085,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540004</v>
+        <v>540212</v>
       </c>
       <c r="R71" t="n">
-        <v>7001090</v>
+        <v>7001230</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9146,10 +9151,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127162146</v>
+        <v>127164741</v>
       </c>
       <c r="B72" t="n">
-        <v>98471</v>
+        <v>98367</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9157,42 +9162,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540106</v>
+        <v>540004</v>
       </c>
       <c r="R72" t="n">
-        <v>7001407</v>
+        <v>7001090</v>
       </c>
       <c r="S72" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9232,11 +9237,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9253,53 +9253,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127153185</v>
+        <v>127158202</v>
       </c>
       <c r="B73" t="n">
-        <v>98783</v>
+        <v>91350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>539835</v>
+        <v>540038</v>
       </c>
       <c r="R73" t="n">
-        <v>7001233</v>
+        <v>7001306</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9331,6 +9331,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På fyndplatsen finns rikliga mängder död ved.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9343,6 +9348,16 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9487,53 +9502,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127158202</v>
+        <v>127153185</v>
       </c>
       <c r="B75" t="n">
-        <v>91350</v>
+        <v>98783</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540038</v>
+        <v>539835</v>
       </c>
       <c r="R75" t="n">
-        <v>7001306</v>
+        <v>7001233</v>
       </c>
       <c r="S75" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9565,11 +9580,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På fyndplatsen finns rikliga mängder död ved.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9582,16 +9592,6 @@
       <c r="AH75" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -9949,48 +9949,67 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127161443</v>
+        <v>127154216</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540137</v>
+        <v>539858</v>
       </c>
       <c r="R79" t="n">
-        <v>7001432</v>
+        <v>7001227</v>
       </c>
       <c r="S79" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10024,7 +10043,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
+          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10039,26 +10058,6 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10076,7 +10075,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127156896</v>
+        <v>127161443</v>
       </c>
       <c r="B80" t="n">
         <v>79020</v>
@@ -10105,24 +10104,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>539983</v>
+        <v>540137</v>
       </c>
       <c r="R80" t="n">
-        <v>7001163</v>
+        <v>7001432</v>
       </c>
       <c r="S80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10156,7 +10150,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Långväxta och fertila bålar på flera granar.</t>
+          <t>Relativt rikligt på flertalet granar. Bitvis långväxta bålar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10208,7 +10202,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127160558</v>
+        <v>127156896</v>
       </c>
       <c r="B81" t="n">
         <v>79020</v>
@@ -10237,19 +10231,24 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540205</v>
+        <v>539983</v>
       </c>
       <c r="R81" t="n">
-        <v>7001321</v>
+        <v>7001163</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10279,6 +10278,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10330,10 +10334,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127157972</v>
+        <v>127160558</v>
       </c>
       <c r="B82" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10341,47 +10345,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540038</v>
+        <v>540205</v>
       </c>
       <c r="R82" t="n">
-        <v>7001245</v>
+        <v>7001321</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10413,11 +10407,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10444,12 +10433,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10467,47 +10456,38 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127154216</v>
+        <v>127157972</v>
       </c>
       <c r="B83" t="n">
-        <v>98450</v>
+        <v>57660</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -10517,17 +10497,17 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>539858</v>
+        <v>540038</v>
       </c>
       <c r="R83" t="n">
-        <v>7001227</v>
+        <v>7001245</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10561,7 +10541,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
+          <t>Färska och äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10576,6 +10556,26 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10719,48 +10719,62 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127164354</v>
+        <v>127160670</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>98473</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540166</v>
+        <v>540195</v>
       </c>
       <c r="R85" t="n">
-        <v>7001045</v>
+        <v>7001331</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10792,6 +10806,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10804,26 +10823,6 @@
       <c r="AH85" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10841,10 +10840,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127160670</v>
+        <v>127155804</v>
       </c>
       <c r="B86" t="n">
-        <v>98473</v>
+        <v>98471</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10852,48 +10851,44 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540195</v>
+        <v>539886</v>
       </c>
       <c r="R86" t="n">
-        <v>7001331</v>
+        <v>7001291</v>
       </c>
       <c r="S86" t="n">
         <v>9</v>
@@ -10928,11 +10923,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10941,11 +10931,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10962,7 +10947,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127155804</v>
+        <v>127163738</v>
       </c>
       <c r="B87" t="n">
         <v>98471</v>
@@ -10993,27 +10978,22 @@
       <c r="I87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>539886</v>
+        <v>540308</v>
       </c>
       <c r="R87" t="n">
-        <v>7001291</v>
+        <v>7001066</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11069,53 +11049,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127163738</v>
+        <v>127164354</v>
       </c>
       <c r="B88" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540308</v>
+        <v>540166</v>
       </c>
       <c r="R88" t="n">
-        <v>7001066</v>
+        <v>7001045</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11155,6 +11130,31 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -12069,67 +12069,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127160071</v>
+        <v>127160214</v>
       </c>
       <c r="B96" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540115</v>
+        <v>540081</v>
       </c>
       <c r="R96" t="n">
-        <v>7001289</v>
+        <v>7001299</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12161,11 +12142,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -12178,6 +12154,26 @@
       <c r="AH96" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -12195,48 +12191,67 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127160214</v>
+        <v>127160071</v>
       </c>
       <c r="B97" t="n">
-        <v>80123</v>
+        <v>98450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540081</v>
+        <v>540115</v>
       </c>
       <c r="R97" t="n">
-        <v>7001299</v>
+        <v>7001289</v>
       </c>
       <c r="S97" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12268,6 +12283,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -12280,26 +12300,6 @@
       <c r="AH97" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,55 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127153536</v>
+        <v>127161646</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539859</v>
+        <v>540139</v>
       </c>
       <c r="R2" t="n">
-        <v>7001178</v>
+        <v>7001452</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +764,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127158784</v>
+        <v>127160294</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,32 +807,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540039</v>
+        <v>540092</v>
       </c>
       <c r="R3" t="n">
         <v>7001341</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,26 +869,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -906,22 +890,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,53 +923,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127162604</v>
+        <v>127164710</v>
       </c>
       <c r="B4" t="n">
-        <v>98367</v>
+        <v>80123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540240</v>
+        <v>540011</v>
       </c>
       <c r="R4" t="n">
-        <v>7001210</v>
+        <v>7001079</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,6 +1001,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1025,6 +1014,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1041,53 +1055,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127163443</v>
+        <v>127162096</v>
       </c>
       <c r="B5" t="n">
-        <v>98473</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540255</v>
+        <v>540104</v>
       </c>
       <c r="R5" t="n">
-        <v>7001070</v>
+        <v>7001431</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,6 +1133,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på två sälgar.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1127,6 +1146,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1143,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127162418</v>
+        <v>127162017</v>
       </c>
       <c r="B6" t="n">
-        <v>98783</v>
+        <v>80158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,27 +1198,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219880</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540127</v>
+        <v>540111</v>
       </c>
       <c r="R6" t="n">
-        <v>7001264</v>
+        <v>7001420</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,6 +1277,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1250,10 +1314,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127164710</v>
+        <v>127153536</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,42 +1325,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540011</v>
+        <v>539859</v>
       </c>
       <c r="R7" t="n">
-        <v>7001079</v>
+        <v>7001178</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,7 +1399,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
+          <t>Äldre rejäla hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,26 +1414,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1382,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127162096</v>
+        <v>127158784</v>
       </c>
       <c r="B8" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,27 +1442,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,13 +1476,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540104</v>
+        <v>540039</v>
       </c>
       <c r="R8" t="n">
-        <v>7001431</v>
+        <v>7001341</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,14 +1509,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,22 +1545,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1514,38 +1578,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127160294</v>
+        <v>127162604</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>98373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1554,10 +1618,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540092</v>
+        <v>540240</v>
       </c>
       <c r="R9" t="n">
-        <v>7001341</v>
+        <v>7001210</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1600,31 +1664,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1641,10 +1680,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127162017</v>
+        <v>127163443</v>
       </c>
       <c r="B10" t="n">
-        <v>80158</v>
+        <v>98479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,42 +1691,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540111</v>
+        <v>540255</v>
       </c>
       <c r="R10" t="n">
-        <v>7001420</v>
+        <v>7001070</v>
       </c>
       <c r="S10" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1727,31 +1766,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1768,47 +1782,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127161646</v>
+        <v>127162418</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98789</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1817,13 +1822,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540139</v>
+        <v>540127</v>
       </c>
       <c r="R11" t="n">
-        <v>7001452</v>
+        <v>7001264</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1853,11 +1858,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,10 +1889,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127160359</v>
+        <v>127154593</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,51 +1900,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540139</v>
+        <v>539874</v>
       </c>
       <c r="R12" t="n">
-        <v>7001298</v>
+        <v>7001234</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1971,24 +1962,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>19:34</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2003,6 +1984,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2020,47 +2021,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127155767</v>
+        <v>127160359</v>
       </c>
       <c r="B13" t="n">
-        <v>98367</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2070,17 +2066,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539895</v>
+        <v>540139</v>
       </c>
       <c r="R13" t="n">
-        <v>7001284</v>
+        <v>7001298</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2107,14 +2103,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växer i ett fuktstråk intill guckusko.</t>
+          <t>Minst 1 talltita hördes i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2146,53 +2152,62 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127154593</v>
+        <v>127162375</v>
       </c>
       <c r="B14" t="n">
-        <v>80123</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539874</v>
+        <v>540115</v>
       </c>
       <c r="R14" t="n">
-        <v>7001234</v>
+        <v>7001309</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2226,7 +2241,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
+          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2241,26 +2256,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2278,37 +2273,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127162375</v>
+        <v>127155767</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2318,22 +2313,27 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540115</v>
+        <v>539895</v>
       </c>
       <c r="R15" t="n">
-        <v>7001309</v>
+        <v>7001284</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 4 blomställningar inom ca 1 m2 yta.</t>
+          <t>Växer i ett fuktstråk intill guckusko.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2399,7 +2399,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127161347</v>
+        <v>127160480</v>
       </c>
       <c r="B16" t="n">
         <v>79020</v>
@@ -2428,24 +2428,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540157</v>
+        <v>540188</v>
       </c>
       <c r="R16" t="n">
-        <v>7001411</v>
+        <v>7001269</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2475,11 +2470,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2531,7 +2521,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127160480</v>
+        <v>127161347</v>
       </c>
       <c r="B17" t="n">
         <v>79020</v>
@@ -2560,19 +2550,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540188</v>
+        <v>540157</v>
       </c>
       <c r="R17" t="n">
-        <v>7001269</v>
+        <v>7001411</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2602,6 +2597,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2800,7 +2800,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127164774</v>
+        <v>127153666</v>
       </c>
       <c r="B19" t="n">
         <v>79020</v>
@@ -2831,17 +2831,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540022</v>
+        <v>539888</v>
       </c>
       <c r="R19" t="n">
-        <v>7001093</v>
+        <v>7001166</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127163769</v>
+        <v>127164774</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540285</v>
+        <v>540022</v>
       </c>
       <c r="R20" t="n">
-        <v>7001071</v>
+        <v>7001093</v>
       </c>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127153666</v>
+        <v>127163769</v>
       </c>
       <c r="B21" t="n">
         <v>79020</v>
@@ -3075,17 +3075,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>539888</v>
+        <v>540285</v>
       </c>
       <c r="R21" t="n">
-        <v>7001166</v>
+        <v>7001071</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3169,7 +3169,7 @@
         <v>127160270</v>
       </c>
       <c r="B22" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>127163626</v>
       </c>
       <c r="B23" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>127152848</v>
       </c>
       <c r="B24" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>127158356</v>
       </c>
       <c r="B26" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>127155997</v>
       </c>
       <c r="B27" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>127153897</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4514,53 +4514,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127163212</v>
+        <v>127161738</v>
       </c>
       <c r="B33" t="n">
-        <v>98473</v>
+        <v>80123</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540253</v>
+        <v>540129</v>
       </c>
       <c r="R33" t="n">
-        <v>7001109</v>
+        <v>7001452</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4592,6 +4592,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4604,6 +4609,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4621,10 +4646,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127158834</v>
+        <v>127161580</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4632,34 +4657,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540033</v>
+        <v>540152</v>
       </c>
       <c r="R34" t="n">
-        <v>7001311</v>
+        <v>7001464</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4694,6 +4724,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4710,22 +4745,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4743,7 +4778,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127161738</v>
+        <v>127164937</v>
       </c>
       <c r="B35" t="n">
         <v>80123</v>
@@ -4779,17 +4814,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540129</v>
+        <v>539990</v>
       </c>
       <c r="R35" t="n">
-        <v>7001452</v>
+        <v>7001113</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4823,7 +4858,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglavsbålar längs flera meter på en gammal sälg.</t>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4875,10 +4910,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127161580</v>
+        <v>127158834</v>
       </c>
       <c r="B36" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4886,39 +4921,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540152</v>
+        <v>540033</v>
       </c>
       <c r="R36" t="n">
-        <v>7001464</v>
+        <v>7001311</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4953,11 +4983,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på en grovbarkad gammal högväxt sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4974,22 +4999,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5007,38 +5032,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127164937</v>
+        <v>127163212</v>
       </c>
       <c r="B37" t="n">
-        <v>80123</v>
+        <v>98479</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5047,13 +5072,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>539990</v>
+        <v>540253</v>
       </c>
       <c r="R37" t="n">
-        <v>7001113</v>
+        <v>7001109</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5085,11 +5110,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5102,26 +5122,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5657,38 +5657,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127164613</v>
+        <v>127163137</v>
       </c>
       <c r="B42" t="n">
-        <v>80123</v>
+        <v>98456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540079</v>
+        <v>540285</v>
       </c>
       <c r="R42" t="n">
-        <v>7001087</v>
+        <v>7001126</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5743,31 +5743,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5784,10 +5759,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127158031</v>
+        <v>127162701</v>
       </c>
       <c r="B43" t="n">
-        <v>98367</v>
+        <v>98477</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5795,33 +5770,24 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -5829,17 +5795,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540047</v>
+        <v>540246</v>
       </c>
       <c r="R43" t="n">
-        <v>7001245</v>
+        <v>7001169</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5869,11 +5835,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Vid en bäck på en gammal väg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5905,10 +5866,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127163976</v>
+        <v>127158031</v>
       </c>
       <c r="B44" t="n">
-        <v>98473</v>
+        <v>98373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5916,24 +5877,33 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -5941,17 +5911,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540285</v>
+        <v>540047</v>
       </c>
       <c r="R44" t="n">
-        <v>7001072</v>
+        <v>7001245</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5983,6 +5953,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Vid en bäck på en gammal väg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5991,6 +5966,11 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6007,48 +5987,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127162532</v>
+        <v>127163976</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>98479</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540214</v>
+        <v>540285</v>
       </c>
       <c r="R45" t="n">
-        <v>7001228</v>
+        <v>7001072</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6088,31 +6073,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6129,53 +6089,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127163137</v>
+        <v>127162532</v>
       </c>
       <c r="B46" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540285</v>
+        <v>540214</v>
       </c>
       <c r="R46" t="n">
-        <v>7001126</v>
+        <v>7001228</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6215,6 +6170,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6231,38 +6211,38 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127162701</v>
+        <v>127164613</v>
       </c>
       <c r="B47" t="n">
-        <v>98471</v>
+        <v>80123</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6271,13 +6251,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540246</v>
+        <v>540079</v>
       </c>
       <c r="R47" t="n">
-        <v>7001169</v>
+        <v>7001087</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6321,6 +6301,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
         <v>127153495</v>
       </c>
       <c r="B49" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>127152890</v>
       </c>
       <c r="B50" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>127160120</v>
       </c>
       <c r="B51" t="n">
-        <v>98783</v>
+        <v>98789</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>127164902</v>
       </c>
       <c r="B52" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6907,62 +6907,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127163731</v>
+        <v>127162675</v>
       </c>
       <c r="B53" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540303</v>
+        <v>540237</v>
       </c>
       <c r="R53" t="n">
-        <v>7001059</v>
+        <v>7001188</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7006,6 +6992,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7023,53 +7029,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127164425</v>
+        <v>127161775</v>
       </c>
       <c r="B54" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540128</v>
+        <v>540092</v>
       </c>
       <c r="R54" t="n">
-        <v>7001058</v>
+        <v>7001443</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7113,6 +7114,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7130,58 +7151,62 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127159734</v>
+        <v>127163731</v>
       </c>
       <c r="B55" t="n">
-        <v>98367</v>
+        <v>98456</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540115</v>
+        <v>540303</v>
       </c>
       <c r="R55" t="n">
-        <v>7001344</v>
+        <v>7001059</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7224,7 +7249,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7242,10 +7267,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127156042</v>
+        <v>127164425</v>
       </c>
       <c r="B56" t="n">
-        <v>98473</v>
+        <v>98477</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7253,56 +7278,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>539924</v>
+        <v>540128</v>
       </c>
       <c r="R56" t="n">
-        <v>7001238</v>
+        <v>7001058</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7345,7 +7356,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7363,10 +7374,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127162577</v>
+        <v>127159734</v>
       </c>
       <c r="B57" t="n">
-        <v>98473</v>
+        <v>98373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7374,21 +7385,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7397,19 +7408,24 @@
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540238</v>
+        <v>540115</v>
       </c>
       <c r="R57" t="n">
-        <v>7001222</v>
+        <v>7001344</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7449,6 +7465,11 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7465,10 +7486,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127160489</v>
+        <v>127156042</v>
       </c>
       <c r="B58" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7493,25 +7514,39 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540171</v>
+        <v>539924</v>
       </c>
       <c r="R58" t="n">
-        <v>7001276</v>
+        <v>7001238</v>
       </c>
       <c r="S58" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7554,7 +7589,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7572,48 +7607,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127162675</v>
+        <v>127162577</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>98479</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540237</v>
+        <v>540238</v>
       </c>
       <c r="R59" t="n">
-        <v>7001188</v>
+        <v>7001222</v>
       </c>
       <c r="S59" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7653,31 +7693,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7694,48 +7709,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127161775</v>
+        <v>127160489</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>98479</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540092</v>
+        <v>540171</v>
       </c>
       <c r="R60" t="n">
-        <v>7001443</v>
+        <v>7001276</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7779,26 +7799,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8210,7 +8210,7 @@
         <v>127158943</v>
       </c>
       <c r="B64" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>127163069</v>
       </c>
       <c r="B65" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>127160440</v>
       </c>
       <c r="B66" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>127160736</v>
       </c>
       <c r="B67" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8699,48 +8699,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127160774</v>
+        <v>127162146</v>
       </c>
       <c r="B68" t="n">
-        <v>80123</v>
+        <v>98477</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540203</v>
+        <v>540106</v>
       </c>
       <c r="R68" t="n">
-        <v>7001394</v>
+        <v>7001407</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8784,26 +8789,6 @@
       <c r="AH68" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8821,10 +8806,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127162146</v>
+        <v>127155980</v>
       </c>
       <c r="B69" t="n">
-        <v>98471</v>
+        <v>98479</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8832,42 +8817,56 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540106</v>
+        <v>539933</v>
       </c>
       <c r="R69" t="n">
-        <v>7001407</v>
+        <v>7001238</v>
       </c>
       <c r="S69" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8928,10 +8927,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127155980</v>
+        <v>127162549</v>
       </c>
       <c r="B70" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8956,39 +8955,25 @@
           <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>539933</v>
+        <v>540212</v>
       </c>
       <c r="R70" t="n">
-        <v>7001238</v>
+        <v>7001230</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9028,11 +9013,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -9049,10 +9029,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127162549</v>
+        <v>127164741</v>
       </c>
       <c r="B71" t="n">
-        <v>98473</v>
+        <v>98373</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9060,21 +9040,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9085,17 +9065,17 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540212</v>
+        <v>540004</v>
       </c>
       <c r="R71" t="n">
-        <v>7001230</v>
+        <v>7001090</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9151,53 +9131,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127164741</v>
+        <v>127160774</v>
       </c>
       <c r="B72" t="n">
-        <v>98367</v>
+        <v>80123</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540004</v>
+        <v>540203</v>
       </c>
       <c r="R72" t="n">
-        <v>7001090</v>
+        <v>7001394</v>
       </c>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9237,6 +9212,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Salix caprea</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9256,7 +9256,7 @@
         <v>127158202</v>
       </c>
       <c r="B73" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>127153185</v>
       </c>
       <c r="B75" t="n">
-        <v>98783</v>
+        <v>98789</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9609,48 +9609,62 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127154622</v>
+        <v>127162730</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>98373</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>539897</v>
+        <v>540258</v>
       </c>
       <c r="R76" t="n">
-        <v>7001240</v>
+        <v>7001179</v>
       </c>
       <c r="S76" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9694,26 +9708,6 @@
       <c r="AH76" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9731,10 +9725,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127162730</v>
+        <v>127163162</v>
       </c>
       <c r="B77" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9759,16 +9753,7 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -9776,17 +9761,17 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540258</v>
+        <v>540247</v>
       </c>
       <c r="R77" t="n">
-        <v>7001179</v>
+        <v>7001094</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9826,11 +9811,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9847,53 +9827,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127163162</v>
+        <v>127154622</v>
       </c>
       <c r="B78" t="n">
-        <v>98367</v>
+        <v>79020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540247</v>
+        <v>539897</v>
       </c>
       <c r="R78" t="n">
-        <v>7001094</v>
+        <v>7001240</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9933,6 +9908,31 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9949,67 +9949,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127154216</v>
+        <v>127156896</v>
       </c>
       <c r="B79" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>539858</v>
+        <v>539983</v>
       </c>
       <c r="R79" t="n">
-        <v>7001227</v>
+        <v>7001163</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10043,7 +10029,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
+          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10058,6 +10044,26 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10202,7 +10208,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127156896</v>
+        <v>127160558</v>
       </c>
       <c r="B81" t="n">
         <v>79020</v>
@@ -10231,24 +10237,19 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>539983</v>
+        <v>540205</v>
       </c>
       <c r="R81" t="n">
-        <v>7001163</v>
+        <v>7001321</v>
       </c>
       <c r="S81" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10278,11 +10279,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Långväxta och fertila bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10334,45 +10330,64 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127160558</v>
+        <v>127155895</v>
       </c>
       <c r="B82" t="n">
-        <v>79020</v>
+        <v>98373</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540205</v>
+        <v>539912</v>
       </c>
       <c r="R82" t="n">
-        <v>7001321</v>
+        <v>7001269</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10407,6 +10422,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10419,26 +10439,6 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10593,37 +10593,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127155895</v>
+        <v>127154216</v>
       </c>
       <c r="B84" t="n">
-        <v>98367</v>
+        <v>98456</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -10647,10 +10647,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>539912</v>
+        <v>539858</v>
       </c>
       <c r="R84" t="n">
-        <v>7001269</v>
+        <v>7001227</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Minst 9 plantor inom ca 1 m2 yta i ett fuktstråk.</t>
+          <t>Minst 330 plantor och 2 vinterståndare inom ca 2,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10719,10 +10719,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127160670</v>
+        <v>127155804</v>
       </c>
       <c r="B85" t="n">
-        <v>98473</v>
+        <v>98477</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10730,48 +10730,44 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540195</v>
+        <v>539886</v>
       </c>
       <c r="R85" t="n">
-        <v>7001331</v>
+        <v>7001291</v>
       </c>
       <c r="S85" t="n">
         <v>9</v>
@@ -10806,11 +10802,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10819,11 +10810,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10840,10 +10826,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127155804</v>
+        <v>127163738</v>
       </c>
       <c r="B86" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10871,27 +10857,22 @@
       <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>539886</v>
+        <v>540308</v>
       </c>
       <c r="R86" t="n">
-        <v>7001291</v>
+        <v>7001066</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10947,53 +10928,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127163738</v>
+        <v>127164354</v>
       </c>
       <c r="B87" t="n">
-        <v>98471</v>
+        <v>79020</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540308</v>
+        <v>540166</v>
       </c>
       <c r="R87" t="n">
-        <v>7001066</v>
+        <v>7001045</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11033,6 +11009,31 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11049,48 +11050,62 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127164354</v>
+        <v>127160670</v>
       </c>
       <c r="B88" t="n">
-        <v>79020</v>
+        <v>98479</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540166</v>
+        <v>540195</v>
       </c>
       <c r="R88" t="n">
-        <v>7001045</v>
+        <v>7001331</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11122,6 +11137,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom 1 m2 yta i ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -11134,26 +11154,6 @@
       <c r="AH88" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
         <v>127159714</v>
       </c>
       <c r="B89" t="n">
-        <v>98448</v>
+        <v>98454</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>127157856</v>
       </c>
       <c r="B90" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>127157226</v>
       </c>
       <c r="B91" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>127159972</v>
       </c>
       <c r="B92" t="n">
-        <v>98448</v>
+        <v>98454</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>127155729</v>
       </c>
       <c r="B93" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>127174668</v>
       </c>
       <c r="B94" t="n">
-        <v>90877</v>
+        <v>90883</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>127157050</v>
       </c>
       <c r="B95" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>127160071</v>
       </c>
       <c r="B97" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>127155870</v>
       </c>
       <c r="B98" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>127164256</v>
       </c>
       <c r="B99" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>127157299</v>
       </c>
       <c r="B100" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>127162786</v>
       </c>
       <c r="B101" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 32651-2025 artfynd.xlsx
+++ b/artfynd/A 32651-2025 artfynd.xlsx
@@ -675,62 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127161646</v>
+        <v>127164710</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>80126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540139</v>
+        <v>540011</v>
       </c>
       <c r="R2" t="n">
-        <v>7001452</v>
+        <v>7001079</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
+          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,6 +770,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127160294</v>
+        <v>127162096</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,7 +838,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540092</v>
+        <v>540104</v>
       </c>
       <c r="R3" t="n">
-        <v>7001341</v>
+        <v>7001431</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,6 +885,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på två sälgar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -900,12 +916,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127164710</v>
+        <v>127160294</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,17 +975,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540011</v>
+        <v>540092</v>
       </c>
       <c r="R4" t="n">
-        <v>7001079</v>
+        <v>7001341</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,11 +1017,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Här växer lunglaven på en grovbarkad gammal skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1032,12 +1043,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1055,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127162096</v>
+        <v>127158784</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,27 +1077,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1095,13 +1111,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540104</v>
+        <v>540039</v>
       </c>
       <c r="R5" t="n">
-        <v>7001431</v>
+        <v>7001341</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,14 +1144,24 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fertil lunglav på två sälgar.</t>
+          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,22 +1180,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1190,7 +1216,7 @@
         <v>127162017</v>
       </c>
       <c r="B6" t="n">
-        <v>80158</v>
+        <v>80161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1317,7 +1343,7 @@
         <v>127153536</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,43 +1457,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127158784</v>
+        <v>127161646</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1476,13 +1506,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540039</v>
+        <v>540139</v>
       </c>
       <c r="R8" t="n">
-        <v>7001341</v>
+        <v>7001452</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,24 +1539,14 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre i riklig mängd högt upp på två granar i kanten mot yngre skog.</t>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,26 +1561,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         <v>127162604</v>
       </c>
       <c r="B9" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>127163443</v>
       </c>
       <c r="B10" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>127162418</v>
       </c>
       <c r="B11" t="n">
-        <v>98789</v>
+        <v>98792</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>127154593</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>127160359</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>127162375</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>127155767</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127160480</v>
+        <v>127161347</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,19 +2428,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540188</v>
+        <v>540157</v>
       </c>
       <c r="R16" t="n">
-        <v>7001269</v>
+        <v>7001411</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2470,6 +2475,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2521,10 +2531,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127161347</v>
+        <v>127160480</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2550,24 +2560,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540157</v>
+        <v>540188</v>
       </c>
       <c r="R17" t="n">
-        <v>7001411</v>
+        <v>7001269</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2597,11 +2602,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fertil garnlav å gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2656,7 +2656,7 @@
         <v>127159187</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2800,48 +2800,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127153666</v>
+        <v>127160270</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>98480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>539888</v>
+        <v>540095</v>
       </c>
       <c r="R19" t="n">
-        <v>7001166</v>
+        <v>7001315</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2885,26 +2890,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2925,7 +2910,7 @@
         <v>127164774</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3044,10 +3029,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127163769</v>
+        <v>127153666</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3075,17 +3060,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540285</v>
+        <v>539888</v>
       </c>
       <c r="R21" t="n">
-        <v>7001071</v>
+        <v>7001166</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3143,12 +3128,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3166,53 +3151,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127160270</v>
+        <v>127163769</v>
       </c>
       <c r="B22" t="n">
-        <v>98477</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540095</v>
+        <v>540285</v>
       </c>
       <c r="R22" t="n">
-        <v>7001315</v>
+        <v>7001071</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3256,6 +3236,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3276,7 +3276,7 @@
         <v>127163626</v>
       </c>
       <c r="B23" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>127152848</v>
       </c>
       <c r="B24" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3510,48 +3510,67 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127163495</v>
+        <v>127155997</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>98376</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540258</v>
+        <v>539924</v>
       </c>
       <c r="R25" t="n">
-        <v>7001065</v>
+        <v>7001238</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3594,27 +3613,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3635,7 +3634,7 @@
         <v>127158356</v>
       </c>
       <c r="B26" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,67 +3758,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127155997</v>
+        <v>127163495</v>
       </c>
       <c r="B27" t="n">
-        <v>98373</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>539924</v>
+        <v>540258</v>
       </c>
       <c r="R27" t="n">
-        <v>7001238</v>
+        <v>7001065</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3862,7 +3842,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3880,48 +3880,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127153018</v>
+        <v>127153641</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>80155</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539829</v>
+        <v>539864</v>
       </c>
       <c r="R28" t="n">
-        <v>7001270</v>
+        <v>7001177</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3969,22 +3974,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4002,53 +4007,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127153641</v>
+        <v>127153018</v>
       </c>
       <c r="B29" t="n">
-        <v>80152</v>
+        <v>79023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>539864</v>
+        <v>539829</v>
       </c>
       <c r="R29" t="n">
-        <v>7001177</v>
+        <v>7001270</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4096,22 +4096,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4132,7 +4132,7 @@
         <v>127153581</v>
       </c>
       <c r="B30" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>127160821</v>
       </c>
       <c r="B31" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>127153897</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>127161738</v>
       </c>
       <c r="B33" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>127161580</v>
       </c>
       <c r="B34" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4778,10 +4778,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127164937</v>
+        <v>127158834</v>
       </c>
       <c r="B35" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4789,39 +4789,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Björnflon, Björnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>539990</v>
+        <v>540033</v>
       </c>
       <c r="R35" t="n">
-        <v>7001113</v>
+        <v>7001311</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4856,11 +4851,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4877,22 +4867,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4910,10 +4900,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127158834</v>
+        <v>127164937</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>80126</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4921,34 +4911,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Björnflon, Björnflon, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540033</v>
+        <v>539990</v>
       </c>
       <c r="R36" t="n">
-        <v>7001311</v>
+        <v>7001113</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4983,6 +4978,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på en grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4999,22 +4999,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5035,7 +5035,7 @@
         <v>127163212</v>
       </c>
       <c r="B37" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5139,10 +5139,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127164541</v>
+        <v>127154714</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>80126</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5150,37 +5150,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540113</v>
+        <v>539872</v>
       </c>
       <c r="R38" t="n">
-        <v>7001087</v>
+        <v>7001243</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5212,6 +5217,11 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 gamla sälgar.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5228,22 +5238,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5261,10 +5271,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127154714</v>
+        <v>127164835</v>
       </c>
       <c r="B39" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5297,17 +5307,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>539872</v>
+        <v>539992</v>
       </c>
       <c r="R39" t="n">
-        <v>7001243</v>
+        <v>7001093</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5341,7 +5351,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Lunglav på 3 gamla sälgar.</t>
+          <t>Växer här på en grov gammal sälg (värdeträd).</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5393,10 +5403,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127164835</v>
+        <v>127153765</v>
       </c>
       <c r="B40" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5424,22 +5434,22 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
+          <t>Harbäcken, Harbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>539992</v>
+        <v>539879</v>
       </c>
       <c r="R40" t="n">
-        <v>7001093</v>
+        <v>7001196</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5473,7 +5483,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Växer här på en grov gammal sälg (värdeträd).</t>
+          <t>Fertil lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5525,10 +5535,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127153765</v>
+        <v>127164541</v>
       </c>
       <c r="B41" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5536,42 +5546,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Harbäcken, Harbäcken, Jmt</t>
+          <t>Blomsterdalen, Blomsterdalen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>539879</v>
+        <v>540113</v>
       </c>
       <c r="R41" t="n">
-        <v>7001196</v>
+        <v>7001087</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5603,11 +5608,6 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5624,22 +5624,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
   